--- a/実装メモ.xlsx
+++ b/実装メモ.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\docker_cms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161F1EE0-9279-407E-AB97-3D6016A85EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23106A4-28C6-454A-9BF3-40A7BFB9A79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
   </bookViews>
   <sheets>
     <sheet name="アンケート機能_概要" sheetId="2" r:id="rId1"/>
     <sheet name="アンケート機能_マイグレーション" sheetId="3" r:id="rId2"/>
     <sheet name="アンケート機能_model" sheetId="4" r:id="rId3"/>
     <sheet name="アンケート機能_フロント" sheetId="5" r:id="rId4"/>
+    <sheet name="番外編" sheetId="6" r:id="rId5"/>
+    <sheet name="アンケート結果_管理画面" sheetId="7" r:id="rId6"/>
+    <sheet name="filmentの構造に関する疑問" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="470">
   <si>
     <t>Route::get('/survey/{id}', [SurveyController::class, 'show']);</t>
   </si>
@@ -798,12 +801,1353 @@
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>app/Models以下</t>
+    <rPh sb="10" eb="12">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ファイル作成</t>
+    <rPh sb="4" eb="6">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>app\Filament\Resources 以下</t>
+    <rPh sb="23" eb="25">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>デバッグ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>php artisan tinker</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>App/Models/SurveyOption::where('survey_id', 1)-&gt;get();</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>選択肢が表示される。</t>
+    <rPh sb="0" eb="3">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>App\Models\SurveyOption::all();</t>
+  </si>
+  <si>
+    <t>全部見る</t>
+    <rPh sb="0" eb="3">
+      <t>ゼンブミ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>コントローラーのこういう、エラーメッセージは</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>return</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD2A8FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>back</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>()-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD2A8FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>with</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'error'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'期限切れ'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>例）app\Http\Controllers\SurveyController.php</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ブレードに以下のように書かないと画面にでない。</t>
+    <rPh sb="5" eb="7">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>    @if (session('error'))</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>div</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>style</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"color:red;"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>        {{ session('error') }}</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7EE787"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>div</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>    @endif</t>
+  </si>
+  <si>
+    <t>例）resources\views\survey.blade.php</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>★セッションに入れるエラー表示</t>
+    <rPh sb="7" eb="8">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>★ターミナルでデバッグ表示</t>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ALTER TABLE survey_votes</t>
+  </si>
+  <si>
+    <t>DROP INDEX survey_votes_survey_id_user_ip_unique;</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>★ユニークを削除</t>
+    </r>
+    <rPh sb="6" eb="8">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>php artisan make:migration drop_unique_from_survey_votes_table</t>
+  </si>
+  <si>
+    <t>作成されたファイルに以下の記述</t>
+    <rPh sb="0" eb="2">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キジュツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>use Illuminate\Database\Migrations\Migration;</t>
+  </si>
+  <si>
+    <t>use Illuminate\Database\Schema\Blueprint;</t>
+  </si>
+  <si>
+    <t>use Illuminate\Support\Facades\Schema;</t>
+  </si>
+  <si>
+    <t>return new class extends Migration {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public function up(): void</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Schema::table('survey_votes', function (Blueprint $table) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            $table-&gt;dropUnique(['survey_id', 'user_ip']);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        });</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public function down(): void</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            $table-&gt;unique(['survey_id', 'user_ip']);</t>
+  </si>
+  <si>
+    <t>};</t>
+  </si>
+  <si>
+    <t>・マイグレーションでやるには以下</t>
+    <rPh sb="14" eb="16">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>$table-&gt;unique(['survey_id', 'user_ip']); // 重複防止</t>
+  </si>
+  <si>
+    <t>DB作成時のmigrateにあった以下の制約を消したい。</t>
+    <rPh sb="2" eb="5">
+      <t>サクセイジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セイヤク</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>コマンド</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>php artisan migrate</t>
+  </si>
+  <si>
+    <t>・SQLでDBに直接は以下。</t>
+    <rPh sb="8" eb="10">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>↓実行したら以下のえらー</t>
+    <rPh sb="1" eb="3">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>DROP FOREIGN KEY survey_votes_survey_id_foreign;</t>
+  </si>
+  <si>
+    <t>#1553 - Cannot drop index 'survey_votes_survey_id_user_ip_unique': needed in a foreign key constraint</t>
+  </si>
+  <si>
+    <t>原因は外部キーが絡んでいるため、</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カラ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>この順番じゃないとダメ👇</t>
+  </si>
+  <si>
+    <t>1. 外部キー削除</t>
+  </si>
+  <si>
+    <t>2. インデックス削除</t>
+  </si>
+  <si>
+    <t>3. 外部キー再作成</t>
+  </si>
+  <si>
+    <t>ADD CONSTRAINT survey_votes_survey_id_foreign</t>
+  </si>
+  <si>
+    <t>FOREIGN KEY (survey_id) REFERENCES surveys(id)</t>
+  </si>
+  <si>
+    <t>ON DELETE CASCADE;</t>
+  </si>
+  <si>
+    <t>👉 そして migration を修正</t>
+  </si>
+  <si>
+    <t>// これ削除</t>
+  </si>
+  <si>
+    <t>$table-&gt;unique(['survey_id', 'user_ip']);</t>
+  </si>
+  <si>
+    <t>php artisan migrate:fresh</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>migrate:fresh</t>
+  </si>
+  <si>
+    <r>
+      <t>全テーブルをドロップしてから </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.65"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>up()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> を実行する。 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.65"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>down()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> は実行されない。</t>
+    </r>
+  </si>
+  <si>
+    <t>migrate:refresh</t>
+  </si>
+  <si>
+    <r>
+      <t>down()</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> を実行してから up() を実行する。なので down() の内容によっては up() の処理に影響を与える可能性がある。1</t>
+    </r>
+  </si>
+  <si>
+    <t>補足として以下のコマンドとの違い</t>
+    <rPh sb="0" eb="2">
+      <t>ホソク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>チガ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>→登録データ消えるぜ</t>
+    <rPh sb="1" eb="3">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>★開発環境であれば、（データ全消しなのでやめとけ）</t>
+    <rPh sb="1" eb="5">
+      <t>カイハツカンキョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゼンケ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MySQLは👇の仕様</t>
+  </si>
+  <si>
+    <t>外部キーはインデックス必須</t>
+  </si>
+  <si>
+    <t>既存インデックスを流用することがある</t>
+  </si>
+  <si>
+    <t>👉 今回は</t>
+  </si>
+  <si>
+    <t>「ユニークインデックスが外部キー用として使われている」</t>
+  </si>
+  <si>
+    <t>なぜこうなる？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>① Viewページ作成</t>
+  </si>
+  <si>
+    <t>アンケート結果_管理画面</t>
+  </si>
+  <si>
+    <t>php artisan make:filament-page ViewSurveyResults --resource=SurveyResource --type=ViewRecord</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>app/Filament/Resources/SurveyResource/Pages/ViewSurveyResults.php</t>
+  </si>
+  <si>
+    <t>ファイル編集</t>
+    <rPh sb="4" eb="6">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>中身</t>
+    <rPh sb="0" eb="2">
+      <t>ナカミ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>&lt;?php</t>
+  </si>
+  <si>
+    <t>namespace App\Filament\Resources\SurveyResource\Pages;</t>
+  </si>
+  <si>
+    <t>use Filament\Resources\Pages\ViewRecord;</t>
+  </si>
+  <si>
+    <t>use App\Filament\Resources\SurveyResource;</t>
+  </si>
+  <si>
+    <t>class ViewSurveyResults extends ViewRecord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    protected static string $resource = SurveyResource::class;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    protected function getViewData(): array</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        $survey = $this-&gt;record;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        $results = $survey-&gt;options-&gt;map(function ($option) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            return [</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                'text' =&gt; $option-&gt;option_text,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                'count' =&gt; $option-&gt;votes()-&gt;count(),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            ];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        $comments = $survey-&gt;comments()-&gt;latest()-&gt;get();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return [</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            'survey' =&gt; $survey,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            'results' =&gt; $results,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            'comments' =&gt; $comments,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        ];</t>
+  </si>
+  <si>
+    <t>※これをエクスプローラー上で編集するには以下のコマンドで権限を変える必要がある。</t>
+    <rPh sb="12" eb="13">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>④ Blade作成</t>
+  </si>
+  <si>
+    <t>resources/views/filament/resources/survey-resource/pages/view-survey-results.blade.php</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※このディレクトリは自作になる。</t>
+    <rPh sb="10" eb="12">
+      <t>ジサク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>クラス名: ViewSurveyResults</t>
+  </si>
+  <si>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>view-survey-results.blade.php</t>
+  </si>
+  <si>
+    <t>filmentのルール上以下のような規則がある。</t>
+    <rPh sb="11" eb="12">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キソク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">👉 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ケバブケースになる</t>
+    </r>
+  </si>
+  <si>
+    <t>💡 なぜこのパス？</t>
+  </si>
+  <si>
+    <t>Filamentは内部で👇を探してます</t>
+  </si>
+  <si>
+    <t>filament.resources.{resource-name}.pages.{page-name}</t>
+  </si>
+  <si>
+    <t>今回👇</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">resource: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>SurveyResource</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>survey-resource</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">page: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>ViewSurveyResults</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>view-survey-results</t>
+    </r>
+  </si>
+  <si>
+    <t>④Blade作成 のパスはあってますでしょうか？ resources/views/filament/resources/survey-resource/ というディレクトリはありませんが</t>
+  </si>
+  <si>
+    <t>いいところに気づいてます 👍</t>
+  </si>
+  <si>
+    <t>結論から言うと👇</t>
+  </si>
+  <si>
+    <t>❗ 結論</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">👉 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>そのディレクトリは自動では作られません</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">👉 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>自分で作る必要があります</t>
+    </r>
+  </si>
+  <si>
+    <t>✅ 正しい対応</t>
+  </si>
+  <si>
+    <t>① ディレクトリを作成</t>
+  </si>
+  <si>
+    <t>resources/views/filament/resources/survey-resource/pages/</t>
+  </si>
+  <si>
+    <t>👉 手動で作ってOKです</t>
+  </si>
+  <si>
+    <t>② Bladeファイル作成</t>
+  </si>
+  <si>
+    <t>🔥 超重要（ここハマりポイント）</t>
+  </si>
+  <si>
+    <t>Filamentの命名ルール👇</t>
+  </si>
+  <si>
+    <t>❗ よくあるミス</t>
+  </si>
+  <si>
+    <t>❌ 間違い</t>
+  </si>
+  <si>
+    <t>ViewSurveyResults.blade.php</t>
+  </si>
+  <si>
+    <t>views/pages/viewSurveyResults.blade.php</t>
+  </si>
+  <si>
+    <t>✅ 正解</t>
+  </si>
+  <si>
+    <t>views/filament/resources/survey-resource/pages/view-survey-results.blade.php</t>
+  </si>
+  <si>
+    <t>🎯 まとめ</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>ディレクトリ</t>
+  </si>
+  <si>
+    <t>手動作成</t>
+  </si>
+  <si>
+    <t>パス</t>
+  </si>
+  <si>
+    <t>filament/resources/survey-resource/pages</t>
+  </si>
+  <si>
+    <t>ファイル名</t>
+  </si>
+  <si>
+    <t>🚀 もし表示されない場合</t>
+  </si>
+  <si>
+    <t>そのときは👇チェック</t>
+  </si>
+  <si>
+    <r>
+      <t>1. getPages()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> に登録してるか</t>
+    </r>
+  </si>
+  <si>
+    <t>2. URLが正しいか</t>
+  </si>
+  <si>
+    <t>3. キャッシュクリア</t>
+  </si>
+  <si>
+    <t>php artisan optimize:clear</t>
+  </si>
+  <si>
+    <t>これまでMENUやTAGのページを作るときに filament.resources.{resource-name}.pages.{page-name} のようなケバブケースでディレクトリを作ることはありませんでした。 なぜでしょう？</t>
+  </si>
+  <si>
+    <t>めちゃくちゃ良いところに気づいてます 👍</t>
+  </si>
+  <si>
+    <r>
+      <t>ここ、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Filamentの仕組みの核心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+  </si>
+  <si>
+    <t>🎯 結論</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">👉 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>通常のResourceページは「Blade不要」だからです</t>
+    </r>
+  </si>
+  <si>
+    <t>🔥 なぜ今だけ必要なのか？</t>
+  </si>
+  <si>
+    <t>✔️ これまで（Menu / Tag）</t>
+  </si>
+  <si>
+    <t>ListRecords</t>
+  </si>
+  <si>
+    <t>CreateRecord</t>
+  </si>
+  <si>
+    <t>EditRecord</t>
+  </si>
+  <si>
+    <t>👉 Filamentが用意してる「既製ページ」</t>
+  </si>
+  <si>
+    <t>つまり👇</t>
+  </si>
+  <si>
+    <t>Bladeを自動生成してる</t>
+  </si>
+  <si>
+    <t>内部ビューを使ってる</t>
+  </si>
+  <si>
+    <t>自分で view を作らない</t>
+  </si>
+  <si>
+    <t>✔️ 今回（ViewSurveyResults）</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">👉 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>カスタムページ</t>
+    </r>
+  </si>
+  <si>
+    <t>💡 違いを図で</t>
+  </si>
+  <si>
+    <t>① 今まで</t>
+  </si>
+  <si>
+    <t>Filament標準ページ</t>
+  </si>
+  <si>
+    <t>内部Blade（vendor内）</t>
+  </si>
+  <si>
+    <t>自動表示</t>
+  </si>
+  <si>
+    <t>👉 自分でBlade作らない</t>
+  </si>
+  <si>
+    <t>② 今回</t>
+  </si>
+  <si>
+    <t>自作ページ</t>
+  </si>
+  <si>
+    <t>Filament「viewを探す」</t>
+  </si>
+  <si>
+    <t>無い → エラー</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">👉 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>だから自分で作る必要がある</t>
+    </r>
+  </si>
+  <si>
+    <t>🔍 さらに深く理解</t>
+  </si>
+  <si>
+    <t>Filamentは内部で👇してます</t>
+  </si>
+  <si>
+    <t>return view('filament.resources.survey-resource.pages.view-survey-results');</t>
+  </si>
+  <si>
+    <t>👉 つまり</t>
+  </si>
+  <si>
+    <t>viewファイルが必要</t>
+  </si>
+  <si>
+    <t>無いと表示できない</t>
+  </si>
+  <si>
+    <t>🎯 なぜMenuやTagでは不要だったか</t>
+  </si>
+  <si>
+    <t>👉 あなたがやっていたのは全部これ👇</t>
+  </si>
+  <si>
+    <t>-&gt;form()</t>
+  </si>
+  <si>
+    <t>-&gt;table()</t>
+  </si>
+  <si>
+    <t>👉 UIは全部Filamentが自動生成</t>
+  </si>
+  <si>
+    <t>🚀 今回は何が違う？</t>
+  </si>
+  <si>
+    <t>今回やってるのは👇</t>
+  </si>
+  <si>
+    <t>「独自の画面を作る」</t>
+  </si>
+  <si>
+    <t>だから👇</t>
+  </si>
+  <si>
+    <t>HTMLも自分で書く</t>
+  </si>
+  <si>
+    <t>Bladeも必要</t>
+  </si>
+  <si>
+    <t>👍 まとめ</t>
+  </si>
+  <si>
+    <t>種類</t>
+  </si>
+  <si>
+    <t>Blade必要？</t>
+  </si>
+  <si>
+    <t>理由</t>
+  </si>
+  <si>
+    <t>List / Create / Edit</t>
+  </si>
+  <si>
+    <t>❌ 不要</t>
+  </si>
+  <si>
+    <t>Filamentが持ってる</t>
+  </si>
+  <si>
+    <t>カスタムPage</t>
+  </si>
+  <si>
+    <t>✅ 必要</t>
+  </si>
+  <si>
+    <t>自分でUI作る</t>
+  </si>
+  <si>
+    <t>💡 補足（プロ視点）</t>
+  </si>
+  <si>
+    <t>Filamentは2層構造👇</t>
+  </si>
+  <si>
+    <t>① 宣言型UI（今まで）</t>
+  </si>
+  <si>
+    <t>TextInput::make('title')</t>
+  </si>
+  <si>
+    <t>👉 楽・速い</t>
+  </si>
+  <si>
+    <t>② カスタムUI（今回）</t>
+  </si>
+  <si>
+    <t>&lt;h1&gt;自由に書く&lt;/h1&gt;</t>
+  </si>
+  <si>
+    <t>👉 自由・強力</t>
+  </si>
+  <si>
+    <t>？疑問</t>
+    <rPh sb="1" eb="3">
+      <t>ギモン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>&lt;x-filament::page&gt;
+    &lt;h2&gt;投票結果&lt;/h2&gt;
+    &lt;table&gt;
+        &lt;thead&gt;
+            &lt;tr&gt;
+                &lt;th&gt;選択肢&lt;/th&gt;
+                &lt;th&gt;票数&lt;/th&gt;
+            &lt;/tr&gt;
+        &lt;/thead&gt;
+        &lt;tbody&gt;
+            @foreach($results as $result)
+                &lt;tr&gt;
+                    &lt;td&gt;{{ $result['text'] }}&lt;/td&gt;
+                    &lt;td&gt;{{ $result['count'] }}&lt;/td&gt;
+                &lt;/tr&gt;
+            @endforeach
+        &lt;/tbody&gt;
+    &lt;/table&gt;
+    &lt;hr&gt;</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;h2&gt;コメント一覧&lt;/h2&gt;
+    @foreach($comments as $comment)
+        &lt;div style="border-bottom:1px solid #ccc; padding:5px;"&gt;
+            {{ $comment-&gt;comment }}
+        &lt;/div&gt;
+    @endforeach
+&lt;/x-filament::page&gt;</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>resources/views/filament/resources/survey-resource/pages/view-survey-results.blade.php
+↓</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>app/Filament/Resources/SurveyResource.php</t>
+  </si>
+  <si>
+    <t>⑥ Resourceにボタン追加</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>use Filament\Tables\Actions\Action;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    -&gt;label('結果')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    -&gt;url(fn ($record) =&gt; static::getUrl('viewSurveyResults', ['record' =&gt; $record]))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    -&gt;icon('heroicon-o-chart-bar'),</t>
+  </si>
+  <si>
+    <t>⑦ ページ登録</t>
+  </si>
+  <si>
+    <t>public static function getPages(): array</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return [</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        'index' =&gt; Pages\ListSurveys::route('/'),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        'create' =&gt; Pages\CreateSurvey::route('/create'),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        'edit' =&gt; Pages\EditSurvey::route('/{record}/edit'),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        'viewSurveyResults' =&gt; Pages\ViewSurveyResults::route('/{record}/results'),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ];</t>
+  </si>
+  <si>
+    <t>Action::make('results')</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>table()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> の actions に追加</t>
+    </r>
+  </si>
+  <si>
+    <t>chmod -R 777 bootstrap/cache</t>
+  </si>
+  <si>
+    <t>chmod -R 777 storage</t>
+  </si>
+  <si>
+    <t>chown -R 1000:1000 *</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -861,6 +2205,167 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFBBBEBF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC586C0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD2A8FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA5D6FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7EE787"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9CDCFE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF8B949E"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF444444"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18.149999999999999"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.65"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -870,7 +2375,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -878,13 +2383,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -903,8 +2420,96 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1872,7 +3477,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E709E9D4-AB6E-4CC2-8E0F-A5793B336BEE}">
-  <dimension ref="A1:A151"/>
+  <dimension ref="A1:A149"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:1" ht="39.75">
@@ -1880,6 +3485,11 @@
         <v>120</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>240</v>
+      </c>
+    </row>
     <row r="3" spans="1:1" ht="30">
       <c r="A3" s="5" t="s">
         <v>121</v>
@@ -2105,8 +3715,18 @@
         <v>145</v>
       </c>
     </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>242</v>
+      </c>
+    </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="2" t="s">
+      <c r="A71" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="2" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2171,224 +3791,218 @@
     <row r="90" spans="1:1" ht="30">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" ht="30">
-      <c r="A91" s="5"/>
-    </row>
-    <row r="92" spans="1:1" ht="30">
-      <c r="A92" s="5"/>
+    <row r="92" spans="1:1">
+      <c r="A92" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="2" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="2" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="30">
-      <c r="A116" s="5" t="s">
+    <row r="114" spans="1:1" ht="30">
+      <c r="A114" s="5" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="2" t="s">
-        <v>1</v>
+        <v>164</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2751,4 +4365,1453 @@
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626DB163-BD8B-468F-83A9-4D70FEBCA709}">
+  <dimension ref="A3:A124"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="25.5">
+      <c r="A11" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="25.5">
+      <c r="A24" s="8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="25.5">
+      <c r="A38" s="8"/>
+    </row>
+    <row r="39" spans="1:1" ht="25.5">
+      <c r="A39" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="11" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="3"/>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="3"/>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="3"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="3"/>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="3"/>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="17" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="2"/>
+    </row>
+    <row r="112" spans="1:1" ht="26.25">
+      <c r="A112" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="13" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="16" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="13"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="26.25">
+      <c r="A117" s="12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="13"/>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="13"/>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <hyperlinks>
+    <hyperlink ref="A118" r:id="rId1" location="fn-1" display="https://qiita.com/sskre/items/0bd048744ea2f830682e - fn-1" xr:uid="{047BE0B8-9A0D-4A1E-802F-7EEE2BF06DA7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA8CB5A-8AF9-428F-BF72-A4650EA2714E}">
+  <dimension ref="A1:B108"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="80.125" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.75" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="22" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="30">
+      <c r="A3" s="23" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="24" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="24"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="24" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="24"/>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="24"/>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="22" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="22" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="22" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="22" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="22" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="22" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="22" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="22" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="22" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="22" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="22" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="22" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="22" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="22" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="22" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="22" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="22" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="22" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="22" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="22" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="22" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="22" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="22" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="30">
+      <c r="A50" s="23" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="24" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="25" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="22" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="22" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="22" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="22" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="22" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="39.75">
+      <c r="A60" s="26" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="22" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="24" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="22" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="27" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="60.75" customHeight="1">
+      <c r="A67" s="34" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="234" customHeight="1">
+      <c r="A68" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="B68" s="32"/>
+    </row>
+    <row r="69" spans="1:2" ht="164.25" customHeight="1">
+      <c r="A69" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="B69" s="29"/>
+    </row>
+    <row r="70" spans="1:2" ht="18.75" customHeight="1"/>
+    <row r="71" spans="1:2" ht="18.75" customHeight="1"/>
+    <row r="72" spans="1:2" ht="18.75" customHeight="1">
+      <c r="A72" s="28" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="22" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="2"/>
+    </row>
+    <row r="76" spans="1:2" ht="19.5" thickBot="1">
+      <c r="A76" s="31" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="30"/>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="22" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="22" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="22" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="22" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="22" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="22" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="22" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="22" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="22" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="22" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="22" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="22" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="22" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="22" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="22" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="22" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="22" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="22" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A68:B68"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED49263E-B0E6-4B40-8C98-8489AC780DBF}">
+  <dimension ref="A1:C219"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="21" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="39.75">
+      <c r="A8" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="39.75">
+      <c r="A15" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="30">
+      <c r="A17" s="5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="30">
+      <c r="A25" s="5" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="39.75">
+      <c r="A31" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="39.75">
+      <c r="A43" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="22.5">
+      <c r="A45" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="22.5">
+      <c r="A49" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="39.75">
+      <c r="A55" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="39.75">
+      <c r="A61" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3"/>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="39.75">
+      <c r="A74" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="37.5">
+      <c r="A77" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="93.75">
+      <c r="A78" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="75">
+      <c r="A79" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="39.75">
+      <c r="A82" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="3"/>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="20" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="25.5">
+      <c r="A93" s="8" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="17" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="39.75">
+      <c r="A101" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="39.75">
+      <c r="A107" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="30">
+      <c r="A109" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="3"/>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="30">
+      <c r="A125" s="5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="39.75">
+      <c r="A133" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="30">
+      <c r="A135" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="30">
+      <c r="A147" s="5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="39.75">
+      <c r="A159" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="3"/>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="39.75">
+      <c r="A172" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" ht="39.75">
+      <c r="A183" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="3"/>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="39.75">
+      <c r="A196" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="36">
+      <c r="A198" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="B198" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="C198" s="18" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="56.25">
+      <c r="A199" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="B199" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="C199" s="19" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="37.5">
+      <c r="A200" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="B200" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="C200" s="19" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="39.75">
+      <c r="A203" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="22.5">
+      <c r="A207" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" ht="22.5">
+      <c r="A215" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" t="s">
+        <v>446</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/実装メモ.xlsx
+++ b/実装メモ.xlsx
@@ -2,24 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\docker_cms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23106A4-28C6-454A-9BF3-40A7BFB9A79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E245D286-C5D0-4D62-8FA2-1AEC2BEDD400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
   </bookViews>
   <sheets>
-    <sheet name="アンケート機能_概要" sheetId="2" r:id="rId1"/>
-    <sheet name="アンケート機能_マイグレーション" sheetId="3" r:id="rId2"/>
-    <sheet name="アンケート機能_model" sheetId="4" r:id="rId3"/>
-    <sheet name="アンケート機能_フロント" sheetId="5" r:id="rId4"/>
-    <sheet name="番外編" sheetId="6" r:id="rId5"/>
-    <sheet name="アンケート結果_管理画面" sheetId="7" r:id="rId6"/>
-    <sheet name="filmentの構造に関する疑問" sheetId="8" r:id="rId7"/>
+    <sheet name="構成図" sheetId="9" r:id="rId1"/>
+    <sheet name="アンケート機能_概要" sheetId="2" r:id="rId2"/>
+    <sheet name="アンケート機能_マイグレーション" sheetId="3" r:id="rId3"/>
+    <sheet name="アンケート機能_model" sheetId="4" r:id="rId4"/>
+    <sheet name="アンケート機能_フロント" sheetId="5" r:id="rId5"/>
+    <sheet name="番外編" sheetId="6" r:id="rId6"/>
+    <sheet name="アンケート結果_管理画面" sheetId="7" r:id="rId7"/>
+    <sheet name="filmentの構造に関する疑問" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="619">
   <si>
     <t>Route::get('/survey/{id}', [SurveyController::class, 'show']);</t>
   </si>
@@ -2142,12 +2143,540 @@
   <si>
     <t>chown -R 1000:1000 *</t>
   </si>
+  <si>
+    <t>ファイル</t>
+  </si>
+  <si>
+    <t>\\wsl.localhost\Ubuntu\home\docker_cms\src\cms</t>
+  </si>
+  <si>
+    <t>├─</t>
+  </si>
+  <si>
+    <t>app</t>
+  </si>
+  <si>
+    <t>│</t>
+  </si>
+  <si>
+    <t>Pages</t>
+  </si>
+  <si>
+    <t>└─</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CategoryResource</t>
+  </si>
+  <si>
+    <t>MenuItemResource</t>
+  </si>
+  <si>
+    <t>MenuResource</t>
+  </si>
+  <si>
+    <t>NewsResource</t>
+  </si>
+  <si>
+    <t>PageResource</t>
+  </si>
+  <si>
+    <t>SurveyResource</t>
+  </si>
+  <si>
+    <t>TagResource</t>
+  </si>
+  <si>
+    <t>UserResource</t>
+  </si>
+  <si>
+    <t>survey-resource</t>
+  </si>
+  <si>
+    <t>cache</t>
+  </si>
+  <si>
+    <t>public</t>
+  </si>
+  <si>
+    <t>css</t>
+  </si>
+  <si>
+    <t>filament</t>
+  </si>
+  <si>
+    <t>forms</t>
+  </si>
+  <si>
+    <t>support</t>
+  </si>
+  <si>
+    <t>js</t>
+  </si>
+  <si>
+    <t>components</t>
+  </si>
+  <si>
+    <t>notifications</t>
+  </si>
+  <si>
+    <t>tables</t>
+  </si>
+  <si>
+    <t>widgets</t>
+  </si>
+  <si>
+    <t>stats-overview</t>
+  </si>
+  <si>
+    <t>resources</t>
+  </si>
+  <si>
+    <t>views</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>layouts</t>
+  </si>
+  <si>
+    <t>news</t>
+  </si>
+  <si>
+    <t>routes</t>
+  </si>
+  <si>
+    <t>storage</t>
+  </si>
+  <si>
+    <t>livewire-tmp</t>
+  </si>
+  <si>
+    <t>private</t>
+  </si>
+  <si>
+    <t>logos</t>
+  </si>
+  <si>
+    <t>site</t>
+  </si>
+  <si>
+    <t>framework</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>sessions</t>
+  </si>
+  <si>
+    <t>testing</t>
+  </si>
+  <si>
+    <t>logs</t>
+  </si>
+  <si>
+    <t>tests</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>├─</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>auth.php</t>
+  </si>
+  <si>
+    <t>columns.php</t>
+  </si>
+  <si>
+    <t>models.php</t>
+  </si>
+  <si>
+    <t>pagination.php</t>
+  </si>
+  <si>
+    <t>passwords.php</t>
+  </si>
+  <si>
+    <t>validation.php</t>
+  </si>
+  <si>
+    <t>Filament</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SiteSetting.php</t>
+  </si>
+  <si>
+    <t>Resources</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>CreateCategory.php</t>
+  </si>
+  <si>
+    <t>EditCategory.php</t>
+  </si>
+  <si>
+    <t>ListCategories.php</t>
+  </si>
+  <si>
+    <t>CreateMenuItem.php</t>
+  </si>
+  <si>
+    <t>EditMenuItem.php</t>
+  </si>
+  <si>
+    <t>ListMenuItems.php</t>
+  </si>
+  <si>
+    <t>CreateMenu.php</t>
+  </si>
+  <si>
+    <t>EditMenu.php</t>
+  </si>
+  <si>
+    <t>ListMenus.php</t>
+  </si>
+  <si>
+    <t>CreateNews.php</t>
+  </si>
+  <si>
+    <t>EditNews.php</t>
+  </si>
+  <si>
+    <t>ListNews.php</t>
+  </si>
+  <si>
+    <t>CreatePage.php</t>
+  </si>
+  <si>
+    <t>EditPage.php</t>
+  </si>
+  <si>
+    <t>ListPages.php</t>
+  </si>
+  <si>
+    <t>CreateSurvey.php</t>
+  </si>
+  <si>
+    <t>EditSurvey.php</t>
+  </si>
+  <si>
+    <t>ListSurveys.php</t>
+  </si>
+  <si>
+    <t>ViewSurveyResults.php</t>
+  </si>
+  <si>
+    <t>CreateTag.php</t>
+  </si>
+  <si>
+    <t>EditTag.php</t>
+  </si>
+  <si>
+    <t>ListTags.php</t>
+  </si>
+  <si>
+    <t>CreateUser.php</t>
+  </si>
+  <si>
+    <t>EditUser.php</t>
+  </si>
+  <si>
+    <t>ListUsers.php</t>
+  </si>
+  <si>
+    <t>CategoryResource.php</t>
+  </si>
+  <si>
+    <t>MenuItemResource.php</t>
+  </si>
+  <si>
+    <t>MenuResource.php</t>
+  </si>
+  <si>
+    <t>NewsResource.php</t>
+  </si>
+  <si>
+    <t>PageResource.php</t>
+  </si>
+  <si>
+    <t>SurveyResource.php</t>
+  </si>
+  <si>
+    <t>TagResource.php</t>
+  </si>
+  <si>
+    <t>UserResource.php</t>
+  </si>
+  <si>
+    <t>Http</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>DB作成ファイル</t>
+    <rPh sb="2" eb="4">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>データ作成ファイル</t>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Controller.php</t>
+  </si>
+  <si>
+    <t>SurveyController.php</t>
+  </si>
+  <si>
+    <t>Controllers</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>├─</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>Filament</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>Category.php</t>
+  </si>
+  <si>
+    <t>Menu.php</t>
+  </si>
+  <si>
+    <t>MenuItem.php</t>
+  </si>
+  <si>
+    <t>News.php</t>
+  </si>
+  <si>
+    <t>Page.php</t>
+  </si>
+  <si>
+    <t>Setting.php</t>
+  </si>
+  <si>
+    <t>Tag.php</t>
+  </si>
+  <si>
+    <t>User.php</t>
+  </si>
+  <si>
+    <t>Providers</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>bootstrap</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>cache</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>config</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>database</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>factories</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>migrations</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>seeders</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>lang</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>ja</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>Models</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>Category.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>Menu.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>MenuItem.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>News.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>Page.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>Setting.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>SiteSetting.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>Survey.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>SurveyComment.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>SurveyOption.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>SurveyVote.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>Tag.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>User.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>その他言語ファイルが多数あり</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゲンゴ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タスウ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>console.php</t>
+  </si>
+  <si>
+    <t>web.php</t>
+  </si>
+  <si>
+    <t>resources</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>app.css</t>
+  </si>
+  <si>
+    <t>app.js</t>
+  </si>
+  <si>
+    <t>bootstrap.js</t>
+  </si>
+  <si>
+    <t>site-setting.blade.php</t>
+  </si>
+  <si>
+    <t>app.blade.php</t>
+  </si>
+  <si>
+    <t>header.blade.php</t>
+  </si>
+  <si>
+    <t>index.blade.php</t>
+  </si>
+  <si>
+    <t>show.blade.php</t>
+  </si>
+  <si>
+    <t>survey.blade.php</t>
+  </si>
+  <si>
+    <t>top.blade.php</t>
+  </si>
+  <si>
+    <t>welcome.blade.php</t>
+  </si>
+  <si>
+    <t>デフォルトでテンプレが無いので、自分で実装する必要がある。</t>
+    <rPh sb="11" eb="12">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>一覧ページ→詳細の構成</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>単ページの構成</t>
+    <rPh sb="0" eb="1">
+      <t>タン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2366,6 +2895,58 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="20"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="12"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color indexed="20"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF002060"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2375,7 +2956,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2392,16 +2973,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2499,20 +3155,1565 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="35" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="2" xr:uid="{F19A6957-2B34-4EDC-A43E-1512F220B8B2}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="217">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="17"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2841,7 +5042,4572 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13CDE890-F993-425A-B129-8B17D7811949}">
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:X451"/>
+  <sheetFormatPr defaultColWidth="4.375" defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="4.375" style="38" customWidth="1"/>
+    <col min="2" max="251" width="4.375" style="35"/>
+    <col min="252" max="252" width="4.375" style="35" customWidth="1"/>
+    <col min="253" max="507" width="4.375" style="35"/>
+    <col min="508" max="508" width="4.375" style="35" customWidth="1"/>
+    <col min="509" max="763" width="4.375" style="35"/>
+    <col min="764" max="764" width="4.375" style="35" customWidth="1"/>
+    <col min="765" max="1019" width="4.375" style="35"/>
+    <col min="1020" max="1020" width="4.375" style="35" customWidth="1"/>
+    <col min="1021" max="1275" width="4.375" style="35"/>
+    <col min="1276" max="1276" width="4.375" style="35" customWidth="1"/>
+    <col min="1277" max="1531" width="4.375" style="35"/>
+    <col min="1532" max="1532" width="4.375" style="35" customWidth="1"/>
+    <col min="1533" max="1787" width="4.375" style="35"/>
+    <col min="1788" max="1788" width="4.375" style="35" customWidth="1"/>
+    <col min="1789" max="2043" width="4.375" style="35"/>
+    <col min="2044" max="2044" width="4.375" style="35" customWidth="1"/>
+    <col min="2045" max="2299" width="4.375" style="35"/>
+    <col min="2300" max="2300" width="4.375" style="35" customWidth="1"/>
+    <col min="2301" max="2555" width="4.375" style="35"/>
+    <col min="2556" max="2556" width="4.375" style="35" customWidth="1"/>
+    <col min="2557" max="2811" width="4.375" style="35"/>
+    <col min="2812" max="2812" width="4.375" style="35" customWidth="1"/>
+    <col min="2813" max="3067" width="4.375" style="35"/>
+    <col min="3068" max="3068" width="4.375" style="35" customWidth="1"/>
+    <col min="3069" max="3323" width="4.375" style="35"/>
+    <col min="3324" max="3324" width="4.375" style="35" customWidth="1"/>
+    <col min="3325" max="3579" width="4.375" style="35"/>
+    <col min="3580" max="3580" width="4.375" style="35" customWidth="1"/>
+    <col min="3581" max="3835" width="4.375" style="35"/>
+    <col min="3836" max="3836" width="4.375" style="35" customWidth="1"/>
+    <col min="3837" max="4091" width="4.375" style="35"/>
+    <col min="4092" max="4092" width="4.375" style="35" customWidth="1"/>
+    <col min="4093" max="4347" width="4.375" style="35"/>
+    <col min="4348" max="4348" width="4.375" style="35" customWidth="1"/>
+    <col min="4349" max="4603" width="4.375" style="35"/>
+    <col min="4604" max="4604" width="4.375" style="35" customWidth="1"/>
+    <col min="4605" max="4859" width="4.375" style="35"/>
+    <col min="4860" max="4860" width="4.375" style="35" customWidth="1"/>
+    <col min="4861" max="5115" width="4.375" style="35"/>
+    <col min="5116" max="5116" width="4.375" style="35" customWidth="1"/>
+    <col min="5117" max="5371" width="4.375" style="35"/>
+    <col min="5372" max="5372" width="4.375" style="35" customWidth="1"/>
+    <col min="5373" max="5627" width="4.375" style="35"/>
+    <col min="5628" max="5628" width="4.375" style="35" customWidth="1"/>
+    <col min="5629" max="5883" width="4.375" style="35"/>
+    <col min="5884" max="5884" width="4.375" style="35" customWidth="1"/>
+    <col min="5885" max="6139" width="4.375" style="35"/>
+    <col min="6140" max="6140" width="4.375" style="35" customWidth="1"/>
+    <col min="6141" max="6395" width="4.375" style="35"/>
+    <col min="6396" max="6396" width="4.375" style="35" customWidth="1"/>
+    <col min="6397" max="6651" width="4.375" style="35"/>
+    <col min="6652" max="6652" width="4.375" style="35" customWidth="1"/>
+    <col min="6653" max="6907" width="4.375" style="35"/>
+    <col min="6908" max="6908" width="4.375" style="35" customWidth="1"/>
+    <col min="6909" max="7163" width="4.375" style="35"/>
+    <col min="7164" max="7164" width="4.375" style="35" customWidth="1"/>
+    <col min="7165" max="7419" width="4.375" style="35"/>
+    <col min="7420" max="7420" width="4.375" style="35" customWidth="1"/>
+    <col min="7421" max="7675" width="4.375" style="35"/>
+    <col min="7676" max="7676" width="4.375" style="35" customWidth="1"/>
+    <col min="7677" max="7931" width="4.375" style="35"/>
+    <col min="7932" max="7932" width="4.375" style="35" customWidth="1"/>
+    <col min="7933" max="8187" width="4.375" style="35"/>
+    <col min="8188" max="8188" width="4.375" style="35" customWidth="1"/>
+    <col min="8189" max="8443" width="4.375" style="35"/>
+    <col min="8444" max="8444" width="4.375" style="35" customWidth="1"/>
+    <col min="8445" max="8699" width="4.375" style="35"/>
+    <col min="8700" max="8700" width="4.375" style="35" customWidth="1"/>
+    <col min="8701" max="8955" width="4.375" style="35"/>
+    <col min="8956" max="8956" width="4.375" style="35" customWidth="1"/>
+    <col min="8957" max="9211" width="4.375" style="35"/>
+    <col min="9212" max="9212" width="4.375" style="35" customWidth="1"/>
+    <col min="9213" max="9467" width="4.375" style="35"/>
+    <col min="9468" max="9468" width="4.375" style="35" customWidth="1"/>
+    <col min="9469" max="9723" width="4.375" style="35"/>
+    <col min="9724" max="9724" width="4.375" style="35" customWidth="1"/>
+    <col min="9725" max="9979" width="4.375" style="35"/>
+    <col min="9980" max="9980" width="4.375" style="35" customWidth="1"/>
+    <col min="9981" max="10235" width="4.375" style="35"/>
+    <col min="10236" max="10236" width="4.375" style="35" customWidth="1"/>
+    <col min="10237" max="10491" width="4.375" style="35"/>
+    <col min="10492" max="10492" width="4.375" style="35" customWidth="1"/>
+    <col min="10493" max="10747" width="4.375" style="35"/>
+    <col min="10748" max="10748" width="4.375" style="35" customWidth="1"/>
+    <col min="10749" max="11003" width="4.375" style="35"/>
+    <col min="11004" max="11004" width="4.375" style="35" customWidth="1"/>
+    <col min="11005" max="11259" width="4.375" style="35"/>
+    <col min="11260" max="11260" width="4.375" style="35" customWidth="1"/>
+    <col min="11261" max="11515" width="4.375" style="35"/>
+    <col min="11516" max="11516" width="4.375" style="35" customWidth="1"/>
+    <col min="11517" max="11771" width="4.375" style="35"/>
+    <col min="11772" max="11772" width="4.375" style="35" customWidth="1"/>
+    <col min="11773" max="12027" width="4.375" style="35"/>
+    <col min="12028" max="12028" width="4.375" style="35" customWidth="1"/>
+    <col min="12029" max="12283" width="4.375" style="35"/>
+    <col min="12284" max="12284" width="4.375" style="35" customWidth="1"/>
+    <col min="12285" max="12539" width="4.375" style="35"/>
+    <col min="12540" max="12540" width="4.375" style="35" customWidth="1"/>
+    <col min="12541" max="12795" width="4.375" style="35"/>
+    <col min="12796" max="12796" width="4.375" style="35" customWidth="1"/>
+    <col min="12797" max="13051" width="4.375" style="35"/>
+    <col min="13052" max="13052" width="4.375" style="35" customWidth="1"/>
+    <col min="13053" max="13307" width="4.375" style="35"/>
+    <col min="13308" max="13308" width="4.375" style="35" customWidth="1"/>
+    <col min="13309" max="13563" width="4.375" style="35"/>
+    <col min="13564" max="13564" width="4.375" style="35" customWidth="1"/>
+    <col min="13565" max="13819" width="4.375" style="35"/>
+    <col min="13820" max="13820" width="4.375" style="35" customWidth="1"/>
+    <col min="13821" max="14075" width="4.375" style="35"/>
+    <col min="14076" max="14076" width="4.375" style="35" customWidth="1"/>
+    <col min="14077" max="14331" width="4.375" style="35"/>
+    <col min="14332" max="14332" width="4.375" style="35" customWidth="1"/>
+    <col min="14333" max="14587" width="4.375" style="35"/>
+    <col min="14588" max="14588" width="4.375" style="35" customWidth="1"/>
+    <col min="14589" max="14843" width="4.375" style="35"/>
+    <col min="14844" max="14844" width="4.375" style="35" customWidth="1"/>
+    <col min="14845" max="15099" width="4.375" style="35"/>
+    <col min="15100" max="15100" width="4.375" style="35" customWidth="1"/>
+    <col min="15101" max="15355" width="4.375" style="35"/>
+    <col min="15356" max="15356" width="4.375" style="35" customWidth="1"/>
+    <col min="15357" max="15611" width="4.375" style="35"/>
+    <col min="15612" max="15612" width="4.375" style="35" customWidth="1"/>
+    <col min="15613" max="15867" width="4.375" style="35"/>
+    <col min="15868" max="15868" width="4.375" style="35" customWidth="1"/>
+    <col min="15869" max="16123" width="4.375" style="35"/>
+    <col min="16124" max="16124" width="4.375" style="35" customWidth="1"/>
+    <col min="16125" max="16384" width="4.375" style="35"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" ht="19.5" thickBot="1">
+      <c r="A1" s="34"/>
+    </row>
+    <row r="2" spans="1:24" ht="19.5" thickBot="1">
+      <c r="A2" s="39" t="s">
+        <v>470</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="42" t="s">
+        <v>372</v>
+      </c>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="43"/>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3" s="34"/>
+      <c r="B3" s="36" t="s">
+        <v>471</v>
+      </c>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4" s="34"/>
+      <c r="B4" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="A5" s="34"/>
+      <c r="B5" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6" s="34"/>
+      <c r="B6" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>475</v>
+      </c>
+      <c r="S6" s="35" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7" s="34"/>
+      <c r="B7" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8" s="34"/>
+      <c r="B8" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>527</v>
+      </c>
+      <c r="S8" s="35" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" s="34"/>
+      <c r="B9" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" s="34"/>
+      <c r="B10" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" s="34"/>
+      <c r="B11" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G11" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H11" s="35" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" s="34"/>
+      <c r="B12" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H12" s="35" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13" s="34"/>
+      <c r="B13" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="A14" s="34"/>
+      <c r="B14" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15" s="34"/>
+      <c r="B15" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
+      <c r="A16" s="34"/>
+      <c r="B16" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G16" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H16" s="35" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="34"/>
+      <c r="B17" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H17" s="35" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="34"/>
+      <c r="B18" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="34"/>
+      <c r="B19" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="34"/>
+      <c r="B20" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G20" s="35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="34"/>
+      <c r="B21" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H21" s="35" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="34"/>
+      <c r="B22" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H22" s="35" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="34"/>
+      <c r="B23" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G23" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H23" s="35" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="34"/>
+      <c r="B24" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="34"/>
+      <c r="B25" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D25" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F25" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G25" s="35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="34"/>
+      <c r="B26" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E26" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G26" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H26" s="35" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="34"/>
+      <c r="B27" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G27" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H27" s="35" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="34"/>
+      <c r="B28" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G28" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H28" s="35" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="34"/>
+      <c r="B29" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="34"/>
+      <c r="B30" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G30" s="35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="34"/>
+      <c r="B31" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E31" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G31" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H31" s="35" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="34"/>
+      <c r="B32" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E32" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F32" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G32" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H32" s="35" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="34"/>
+      <c r="B33" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F33" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G33" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="34"/>
+      <c r="B34" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E34" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F34" s="35" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="34"/>
+      <c r="B35" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E35" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F35" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G35" s="35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="34"/>
+      <c r="B36" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E36" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F36" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G36" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H36" s="35" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="34"/>
+      <c r="B37" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E37" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F37" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G37" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H37" s="35" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="34"/>
+      <c r="B38" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E38" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F38" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G38" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H38" s="35" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="34"/>
+      <c r="B39" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E39" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F39" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G39" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H39" s="35" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="34"/>
+      <c r="B40" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E40" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F40" s="35" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="34"/>
+      <c r="B41" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E41" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F41" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G41" s="35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="34"/>
+      <c r="B42" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E42" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F42" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G42" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H42" s="35" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="34"/>
+      <c r="B43" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C43" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F43" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G43" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H43" s="35" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="34"/>
+      <c r="B44" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C44" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E44" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F44" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G44" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H44" s="35" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="34"/>
+      <c r="B45" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C45" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E45" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F45" s="35" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="34"/>
+      <c r="B46" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E46" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F46" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G46" s="35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="34"/>
+      <c r="B47" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F47" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G47" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H47" s="35" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="34"/>
+      <c r="B48" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E48" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F48" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G48" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="H48" s="35" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
+      <c r="A49" s="34"/>
+      <c r="B49" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E49" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F49" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G49" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H49" s="35" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19">
+      <c r="A50" s="34"/>
+      <c r="B50" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E50" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F50" s="35" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19">
+      <c r="A51" s="34"/>
+      <c r="B51" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E51" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F51" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G51" s="35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19">
+      <c r="A52" s="34"/>
+      <c r="B52" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E52" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F52" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G52" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H52" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="S52" s="35" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19">
+      <c r="A53" s="34"/>
+      <c r="B53" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E53" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F53" s="46" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19">
+      <c r="A54" s="34"/>
+      <c r="B54" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C54" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E54" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F54" s="46" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19">
+      <c r="A55" s="34"/>
+      <c r="B55" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E55" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F55" s="46" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19">
+      <c r="A56" s="34"/>
+      <c r="B56" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C56" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E56" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F56" s="46" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19">
+      <c r="A57" s="34"/>
+      <c r="B57" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C57" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E57" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F57" s="46" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19">
+      <c r="A58" s="34"/>
+      <c r="B58" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C58" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E58" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F58" s="46" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19">
+      <c r="A59" s="34"/>
+      <c r="B59" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C59" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E59" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F59" s="46" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19">
+      <c r="A60" s="34"/>
+      <c r="B60" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C60" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E60" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F60" s="46" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19">
+      <c r="A61" s="34"/>
+      <c r="B61" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C61" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D61" s="35" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19">
+      <c r="A62" s="34"/>
+      <c r="B62" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C62" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D62" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E62" s="35" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" s="34"/>
+      <c r="B63" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C63" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D63" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E63" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F63" s="35" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
+      <c r="A64" s="34"/>
+      <c r="B64" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C64" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D64" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E64" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F64" s="45" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="34"/>
+      <c r="B65" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="34"/>
+      <c r="B66" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C66" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D66" s="35" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="34"/>
+      <c r="B67" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C67" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D67" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E67" s="35" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="34"/>
+      <c r="B68" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C68" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D68" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E68" s="35" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="34"/>
+      <c r="B69" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C69" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D69" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E69" s="35" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="34"/>
+      <c r="B70" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C70" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D70" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E70" s="35" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="34"/>
+      <c r="B71" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C71" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D71" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E71" s="35" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="34"/>
+      <c r="B72" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C72" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D72" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E72" s="35" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="34"/>
+      <c r="B73" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C73" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D73" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E73" s="35" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="34"/>
+      <c r="B74" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C74" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D74" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E74" s="45" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="34"/>
+      <c r="B75" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C75" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D75" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E75" s="45" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="34"/>
+      <c r="B76" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C76" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D76" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E76" s="45" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="34"/>
+      <c r="B77" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C77" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D77" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E77" s="45" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="34"/>
+      <c r="B78" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C78" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D78" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E78" s="35" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="34"/>
+      <c r="B79" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C79" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D79" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E79" s="35" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="34"/>
+      <c r="B80" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C80" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D80" s="35" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="34"/>
+      <c r="B81" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C81" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D81" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E81" s="35" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="34"/>
+      <c r="B82" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E82" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F82" s="35" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="34"/>
+      <c r="B83" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E83" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F83" s="35" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="34"/>
+      <c r="B84" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E84" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F84" s="35" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="34"/>
+      <c r="B85" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E85" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F85" s="35" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="34"/>
+      <c r="B86" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E86" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F86" s="35" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="34"/>
+      <c r="B87" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E87" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F87" s="35" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="34"/>
+      <c r="B88" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E88" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F88" s="35" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="34"/>
+      <c r="B89" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E89" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F89" s="35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="34"/>
+      <c r="B90" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E90" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F90" s="35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="34"/>
+      <c r="B91" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E91" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F91" s="35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="34"/>
+      <c r="B92" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E92" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F92" s="35" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="34"/>
+      <c r="B93" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E93" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F93" s="35" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="34"/>
+      <c r="B94" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E94" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F94" s="35" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="34"/>
+      <c r="B95" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="C95" s="35" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="34"/>
+      <c r="B96" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C96" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D96" s="35" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19">
+      <c r="A97" s="34"/>
+      <c r="B97" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="C97" s="35" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19">
+      <c r="A98" s="34"/>
+      <c r="B98" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="C98" s="35" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q98" s="34"/>
+    </row>
+    <row r="99" spans="1:19">
+      <c r="A99" s="34"/>
+      <c r="B99" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C99" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="D99" s="35" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19">
+      <c r="A100" s="34"/>
+      <c r="B100" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C100" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="D100" s="35" t="s">
+        <v>583</v>
+      </c>
+      <c r="S100" s="35" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19">
+      <c r="A101" s="34"/>
+      <c r="B101" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C101" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D101" s="35" t="s">
+        <v>584</v>
+      </c>
+      <c r="S101" s="35" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19">
+      <c r="A102" s="34"/>
+      <c r="B102" s="35" t="s">
+        <v>518</v>
+      </c>
+      <c r="C102" s="35" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19">
+      <c r="A103" s="34"/>
+      <c r="B103" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C103" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D103" s="35" t="s">
+        <v>586</v>
+      </c>
+      <c r="S103" s="35" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19">
+      <c r="A104" s="34"/>
+      <c r="B104" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D104" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E104" s="35" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19">
+      <c r="A105" s="34"/>
+      <c r="B105" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D105" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E105" s="35" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19">
+      <c r="A106" s="34"/>
+      <c r="B106" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D106" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E106" s="35" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19">
+      <c r="A107" s="34"/>
+      <c r="B107" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D107" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E107" s="35" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19">
+      <c r="A108" s="34"/>
+      <c r="B108" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D108" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E108" s="35" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19">
+      <c r="A109" s="34"/>
+      <c r="B109" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D109" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E109" s="35" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19">
+      <c r="A110" s="34"/>
+      <c r="B110" s="35" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19">
+      <c r="A111" s="34"/>
+      <c r="B111" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="C111" s="35" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19">
+      <c r="A112" s="34"/>
+      <c r="B112" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C112" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D112" s="35" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="34"/>
+      <c r="B113" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C113" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D113" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E113" s="35" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="34"/>
+      <c r="B114" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C114" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D114" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E114" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F114" s="35" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="34"/>
+      <c r="B115" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C115" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D115" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E115" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F115" s="35" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="34"/>
+      <c r="B116" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C116" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D116" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E116" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F116" s="35" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="34"/>
+      <c r="B117" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C117" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D117" s="35" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="34"/>
+      <c r="B118" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C118" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D118" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E118" s="35" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="34"/>
+      <c r="B119" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C119" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D119" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E119" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F119" s="35" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="34"/>
+      <c r="B120" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C120" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D120" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E120" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F120" s="35" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="34"/>
+      <c r="B121" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C121" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D121" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E121" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F121" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G121" s="35" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="34"/>
+      <c r="B122" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C122" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D122" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E122" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F122" s="35" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="34"/>
+      <c r="B123" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C123" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D123" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E123" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F123" s="35" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="34"/>
+      <c r="B124" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C124" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D124" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E124" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F124" s="35" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="34"/>
+      <c r="B125" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C125" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D125" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E125" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F125" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G125" s="35" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="34"/>
+      <c r="B126" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C126" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D126" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E126" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F126" s="35" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="34"/>
+      <c r="B127" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C127" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D127" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E127" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="F127" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G127" s="35" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="34"/>
+      <c r="B128" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C128" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D128" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E128" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="F128" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G128" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H128" s="35" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="34"/>
+      <c r="B129" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C129" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D129" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E129" s="35" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" s="34"/>
+      <c r="B130" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="C130" s="35" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="34"/>
+      <c r="B131" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C131" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D131" s="35" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="34"/>
+      <c r="B132" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C132" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D132" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E132" s="35" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="34"/>
+      <c r="B133" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C133" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D133" s="35" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="34"/>
+      <c r="B134" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C134" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D134" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E134" s="35" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" s="34"/>
+      <c r="B135" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C135" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D135" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E135" s="35" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" s="34"/>
+      <c r="B136" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C136" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D136" s="35" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" s="34"/>
+      <c r="B137" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C137" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D137" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E137" s="35" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="34"/>
+      <c r="B138" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C138" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D138" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E138" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F138" s="35" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="34"/>
+      <c r="B139" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C139" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D139" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E139" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F139" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G139" s="35" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" s="34"/>
+      <c r="B140" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C140" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D140" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E140" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F140" s="35" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="34"/>
+      <c r="B141" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C141" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D141" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E141" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="F141" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G141" s="35" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" s="34"/>
+      <c r="B142" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C142" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D142" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E142" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="F142" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G142" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H142" s="35" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" s="34"/>
+      <c r="B143" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C143" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D143" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E143" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="F143" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G143" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="H143" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="I143" s="45" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" s="34"/>
+      <c r="B144" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C144" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D144" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E144" s="35" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" s="34"/>
+      <c r="B145" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C145" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D145" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E145" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F145" s="35" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" s="34"/>
+      <c r="B146" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C146" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D146" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E146" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F146" s="35" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" s="34"/>
+      <c r="B147" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C147" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D147" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E147" s="35" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" s="34"/>
+      <c r="B148" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C148" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D148" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E148" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F148" s="35" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" s="34"/>
+      <c r="B149" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C149" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D149" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E149" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F149" s="35" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="34"/>
+      <c r="B150" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C150" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D150" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E150" s="35" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="34"/>
+      <c r="B151" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C151" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D151" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E151" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F151" s="35" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="34"/>
+      <c r="B152" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C152" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D152" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E152" s="45" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="34"/>
+      <c r="B153" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C153" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D153" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E153" s="35" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="34"/>
+      <c r="B154" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C154" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D154" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E154" s="35" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="34"/>
+      <c r="B155" s="35" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="34"/>
+      <c r="B156" s="35" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="34"/>
+      <c r="B157" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="C157" s="35" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="34"/>
+      <c r="B158" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C158" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D158" s="35" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="34"/>
+      <c r="B159" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C159" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D159" s="35" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="34"/>
+      <c r="B160" s="35" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" s="34"/>
+      <c r="B161" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="C161" s="35" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" s="34"/>
+      <c r="B162" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C162" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D162" s="35" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" s="34"/>
+      <c r="B163" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C163" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D163" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E163" s="35" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" s="34"/>
+      <c r="B164" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C164" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D164" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E164" s="35" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" s="34"/>
+      <c r="B165" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C165" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D165" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E165" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F165" s="35" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" s="34"/>
+      <c r="B166" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C166" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D166" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E166" s="35" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" s="34"/>
+      <c r="B167" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C167" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D167" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E167" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F167" s="35" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" s="34"/>
+      <c r="B168" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C168" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D168" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E168" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F168" s="35" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" s="34"/>
+      <c r="B169" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C169" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D169" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E169" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F169" s="35" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" s="34"/>
+      <c r="B170" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C170" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D170" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E170" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F170" s="35" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" s="34"/>
+      <c r="B171" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C171" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D171" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E171" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F171" s="35" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" s="34"/>
+      <c r="B172" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C172" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D172" s="35" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" s="34"/>
+      <c r="B173" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C173" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D173" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E173" s="35" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" s="34"/>
+      <c r="B174" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C174" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D174" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E174" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F174" s="35" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" s="34"/>
+      <c r="B175" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C175" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D175" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E175" s="35" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" s="34"/>
+      <c r="B176" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C176" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D176" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E176" s="35" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="34"/>
+      <c r="B177" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C177" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D177" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E177" s="35" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="34"/>
+      <c r="B178" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C178" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D178" s="35" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="34"/>
+      <c r="B179" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="C179" s="35" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="34"/>
+      <c r="B180" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="C180" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D180" s="35" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="34"/>
+      <c r="B181" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="C181" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D181" s="35" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="34"/>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="34"/>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="34"/>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="34"/>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="34"/>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="34"/>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="34"/>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="34"/>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="34"/>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="34"/>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="34"/>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="34"/>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="34"/>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="34"/>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="34"/>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="34"/>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="34"/>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="34"/>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="34"/>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="34"/>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="34"/>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="34"/>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="34"/>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="34"/>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="34"/>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="34"/>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="34"/>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="34"/>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="34"/>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="34"/>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="34"/>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="34"/>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="34"/>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="34"/>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="34"/>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="34"/>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="34"/>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="34"/>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="34"/>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="34"/>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="34"/>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="34"/>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="34"/>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="34"/>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="34"/>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="34"/>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="34"/>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="34"/>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="34"/>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="34"/>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="34"/>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="34"/>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="34"/>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="34"/>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="34"/>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="34"/>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="34"/>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="34"/>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="34"/>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="34"/>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="34"/>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="34"/>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="34"/>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="34"/>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="34"/>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="34"/>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="34"/>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="34"/>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="34"/>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="34"/>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="34"/>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="34"/>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="34"/>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="34"/>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="34"/>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="34"/>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="34"/>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="34"/>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="34"/>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="34"/>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="34"/>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="34"/>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="34"/>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="34"/>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="34"/>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="34"/>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="34"/>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="34"/>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="34"/>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="34"/>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="34"/>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="34"/>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="34"/>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="34"/>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="34"/>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="34"/>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="34"/>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="34"/>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="34"/>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="34"/>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="34"/>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="34"/>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="34"/>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="34"/>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="34"/>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" s="34"/>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="34"/>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" s="34"/>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" s="34"/>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" s="34"/>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" s="34"/>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="34"/>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" s="34"/>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" s="34"/>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" s="34"/>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" s="34"/>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" s="34"/>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" s="34"/>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" s="34"/>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" s="34"/>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" s="34"/>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" s="34"/>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" s="34"/>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" s="34"/>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" s="34"/>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" s="34"/>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" s="34"/>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" s="34"/>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" s="34"/>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" s="34"/>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312" s="34"/>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313" s="34"/>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314" s="34"/>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" s="34"/>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" s="34"/>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" s="34"/>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" s="34"/>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" s="34"/>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" s="34"/>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321" s="34"/>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" s="34"/>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" s="34"/>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" s="34"/>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" s="34"/>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" s="34"/>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" s="34"/>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" s="34"/>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329" s="34"/>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" s="34"/>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" s="34"/>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" s="34"/>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" s="34"/>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" s="34"/>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" s="34"/>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" s="34"/>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" s="34"/>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" s="34"/>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" s="34"/>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" s="34"/>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" s="34"/>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" s="34"/>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" s="34"/>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" s="34"/>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" s="34"/>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" s="34"/>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" s="34"/>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" s="34"/>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" s="34"/>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" s="34"/>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" s="34"/>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" s="34"/>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" s="34"/>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" s="34"/>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" s="34"/>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" s="34"/>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" s="34"/>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" s="34"/>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" s="34"/>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" s="34"/>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" s="34"/>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" s="34"/>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" s="34"/>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" s="34"/>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" s="34"/>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" s="34"/>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" s="34"/>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368" s="34"/>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" s="34"/>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" s="34"/>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" s="34"/>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" s="34"/>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" s="34"/>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" s="34"/>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" s="34"/>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" s="34"/>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" s="34"/>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" s="34"/>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" s="34"/>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" s="34"/>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" s="34"/>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" s="34"/>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" s="34"/>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" s="34"/>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" s="34"/>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" s="34"/>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" s="34"/>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" s="34"/>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" s="34"/>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" s="34"/>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" s="34"/>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" s="34"/>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" s="34"/>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394" s="34"/>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" s="34"/>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" s="34"/>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397" s="34"/>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" s="34"/>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399" s="34"/>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" s="34"/>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" s="34"/>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402" s="34"/>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403" s="34"/>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404" s="34"/>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405" s="34"/>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406" s="34"/>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407" s="34"/>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408" s="34"/>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409" s="34"/>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410" s="34"/>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411" s="34"/>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412" s="34"/>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413" s="34"/>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414" s="34"/>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415" s="34"/>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416" s="34"/>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" s="34"/>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" s="34"/>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419" s="34"/>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" s="34"/>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" s="34"/>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422" s="34"/>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" s="34"/>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" s="34"/>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425" s="34"/>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" s="34"/>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" s="34"/>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428" s="34"/>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" s="34"/>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" s="34"/>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431" s="34"/>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" s="34"/>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" s="34"/>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434" s="34"/>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435" s="34"/>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436" s="34"/>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437" s="34"/>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438" s="34"/>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439" s="34"/>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440" s="34"/>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441" s="34"/>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442" s="34"/>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443" s="34"/>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444" s="34"/>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445" s="34"/>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446" s="34"/>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447" s="34"/>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448" s="34"/>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" s="34"/>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" s="34"/>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" s="34"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="S2:X2"/>
+  </mergeCells>
+  <phoneticPr fontId="34"/>
+  <conditionalFormatting sqref="A183:A202">
+    <cfRule type="expression" dxfId="216" priority="1332" stopIfTrue="1">
+      <formula>OR($B164="├─",$B164="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A184:A185 A187 A193">
+    <cfRule type="expression" dxfId="215" priority="1226" stopIfTrue="1">
+      <formula>OR($B165="├─",$B165="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="214" priority="1227" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="213" priority="1228" stopIfTrue="1">
+      <formula>OR($B165="├─",$B165="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="212" priority="1229" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="211" priority="1230" stopIfTrue="1">
+      <formula>OR($B165="├─",$B165="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="210" priority="1231" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="209" priority="1232" stopIfTrue="1">
+      <formula>OR($B165="├─",$B165="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="208" priority="1233" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="207" priority="1234" stopIfTrue="1">
+      <formula>OR($B165="├─",$B165="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="206" priority="1235" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="205" priority="1224" stopIfTrue="1">
+      <formula>OR($B165="├─",$B165="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="204" priority="1225" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A184:A185 A187:A188 A190:A197">
+    <cfRule type="expression" dxfId="203" priority="1237" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="202" priority="1236" stopIfTrue="1">
+      <formula>OR($B165="├─",$B165="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A188 A190:A197">
+    <cfRule type="expression" dxfId="201" priority="1343" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A188 A196:A197">
+    <cfRule type="expression" dxfId="200" priority="1342" stopIfTrue="1">
+      <formula>OR($B169="├─",$B169="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="199" priority="1341" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="198" priority="1340" stopIfTrue="1">
+      <formula>OR($B169="├─",$B169="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="197" priority="1339" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="196" priority="1338" stopIfTrue="1">
+      <formula>OR($B169="├─",$B169="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="195" priority="1337" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="194" priority="1336" stopIfTrue="1">
+      <formula>OR($B169="├─",$B169="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="193" priority="1335" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="192" priority="1334" stopIfTrue="1">
+      <formula>OR($B169="├─",$B169="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="191" priority="1333" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A188">
+    <cfRule type="expression" dxfId="190" priority="1344" stopIfTrue="1">
+      <formula>OR($B169="├─",$B169="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="189" priority="1345" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A192">
+    <cfRule type="expression" dxfId="188" priority="1410" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="187" priority="1411" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="186" priority="1401" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="185" priority="1402" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="184" priority="1403" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="183" priority="1404" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="182" priority="1405" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="181" priority="1406" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="180" priority="1407" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="179" priority="1408" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="178" priority="1409" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="177" priority="1400" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="176" priority="1392" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="175" priority="1393" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="174" priority="1394" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="173" priority="1395" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="172" priority="1396" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="171" priority="1397" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="170" priority="1398" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="169" priority="1399" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A192:A193">
+    <cfRule type="expression" dxfId="168" priority="1432" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="167" priority="1433" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="166" priority="1434" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="165" priority="1435" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="164" priority="1436" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="163" priority="1437" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A192:A194">
+    <cfRule type="expression" dxfId="162" priority="1439" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="161" priority="1438" stopIfTrue="1">
+      <formula>OR($B173="├─",$B173="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A194">
+    <cfRule type="expression" dxfId="160" priority="1502" stopIfTrue="1">
+      <formula>OR($B175="├─",$B175="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="159" priority="1520" stopIfTrue="1">
+      <formula>OR($B175="├─",$B175="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="158" priority="1516" stopIfTrue="1">
+      <formula>OR($B175="├─",$B175="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="157" priority="1517" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="156" priority="1515" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="155" priority="1514" stopIfTrue="1">
+      <formula>OR($B175="├─",$B175="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="154" priority="1513" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="153" priority="1512" stopIfTrue="1">
+      <formula>OR($B175="├─",$B175="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="152" priority="1511" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="151" priority="1510" stopIfTrue="1">
+      <formula>OR($B175="├─",$B175="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="150" priority="1509" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="149" priority="1508" stopIfTrue="1">
+      <formula>OR($B175="├─",$B175="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="148" priority="1507" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="147" priority="1506" stopIfTrue="1">
+      <formula>OR($B175="├─",$B175="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="146" priority="1505" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="145" priority="1504" stopIfTrue="1">
+      <formula>OR($B175="├─",$B175="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="144" priority="1503" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="143" priority="1518" stopIfTrue="1">
+      <formula>OR($B175="├─",$B175="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="142" priority="1519" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="141" priority="1521" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A196">
+    <cfRule type="expression" dxfId="140" priority="1580" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="139" priority="1581" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="138" priority="1582" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="137" priority="1583" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="136" priority="1584" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="135" priority="1585" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="134" priority="1586" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="133" priority="1587" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="132" priority="1566" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="131" priority="1567" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="130" priority="1568" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="129" priority="1569" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="128" priority="1570" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="127" priority="1571" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="126" priority="1572" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="125" priority="1573" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="124" priority="1574" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="123" priority="1575" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="122" priority="1576" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="121" priority="1577" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="120" priority="1578" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="119" priority="1579" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A196:A197">
+    <cfRule type="expression" dxfId="118" priority="1588" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="117" priority="1589" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="116" priority="1330" stopIfTrue="1">
+      <formula>OR($B177="├─",$B177="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="115" priority="1331" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A197">
+    <cfRule type="expression" dxfId="114" priority="1662" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="113" priority="1663" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="112" priority="1664" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="111" priority="1665" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="110" priority="1666" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="109" priority="1667" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="1668" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="1669" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="1670" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="1671" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="1673" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="1674" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="1675" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="1679" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="1676" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="1677" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="1678" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="1689" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="1688" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="95" priority="1687" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="94" priority="1686" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="93" priority="1685" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="92" priority="1684" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="91" priority="1683" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="90" priority="1682" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="1681" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="1680" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="87" priority="1672" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="1650" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="1651" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="1652" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="1653" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="1654" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="1655" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="1656" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="1657" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="1658" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="1659" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="1660" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="1661" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A197:A198">
+    <cfRule type="expression" dxfId="74" priority="1748" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="1747" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="1746" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="1745" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="1744" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="69" priority="1743" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="1741" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="1740" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="1739" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="1738" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="1737" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="1736" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="1735" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="1734" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="1733" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="1732" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="1742" stopIfTrue="1">
+      <formula>OR($B178="├─",$B178="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="1749" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A198">
+    <cfRule type="expression" dxfId="56" priority="1785" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="1768" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="1769" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="1770" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="1771" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="1772" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="1773" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="1774" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="1775" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="47" priority="1776" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="1777" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="1778" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="1779" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="1780" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="1781" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="1782" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="1783" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="1784" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="1786" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="1787" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="1788" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="1789" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="1790" stopIfTrue="1">
+      <formula>OR($B179="├─",$B179="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="1791" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A200 B194:E442">
+    <cfRule type="expression" dxfId="32" priority="1365" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A200">
+    <cfRule type="expression" dxfId="31" priority="1364" stopIfTrue="1">
+      <formula>OR($B181="├─",$B181="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="1363" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A203:A451">
+    <cfRule type="expression" dxfId="29" priority="2069" stopIfTrue="1">
+      <formula>OR($B194="├─",$B194="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A204:A205 A207:A208 A213:A226">
+    <cfRule type="expression" dxfId="28" priority="1919" stopIfTrue="1">
+      <formula>OR($B195="├─",$B195="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="1920" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A222:A224">
+    <cfRule type="expression" dxfId="26" priority="2045" stopIfTrue="1">
+      <formula>OR($B213="├─",$B213="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="2046" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="2047" stopIfTrue="1">
+      <formula>OR($B213="├─",$B213="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="2048" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A98:AN98 A4:X97">
+    <cfRule type="expression" dxfId="22" priority="802" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="801" stopIfTrue="1">
+      <formula>OR($B4="├─",$B4="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A99:X182">
+    <cfRule type="expression" dxfId="20" priority="1" stopIfTrue="1">
+      <formula>OR($B99="├─",$B99="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B204:C217 Y65:AK65 B195:C196 B198:C199">
+    <cfRule type="expression" dxfId="18" priority="881" stopIfTrue="1">
+      <formula>OR($B65="├─",$B65="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B213:C215">
+    <cfRule type="expression" dxfId="17" priority="820" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="819" stopIfTrue="1">
+      <formula>OR($B213="├─",$B213="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="824" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="823" stopIfTrue="1">
+      <formula>OR($B213="├─",$B213="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B183:E183 A183:A451">
+    <cfRule type="expression" dxfId="13" priority="890" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B194:E442 B183:E183">
+    <cfRule type="expression" dxfId="12" priority="889" stopIfTrue="1">
+      <formula>OR($B183="├─",$B183="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:R1 T1:X1 A1:A3 S1:S3 B3:R3 T3:X3">
+    <cfRule type="expression" dxfId="11" priority="895" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="894" stopIfTrue="1">
+      <formula>OR($B1="├─",$B1="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F198:F429">
+    <cfRule type="expression" dxfId="9" priority="939" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="938" stopIfTrue="1">
+      <formula>OR($B211="├─",$B211="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G427:X65621 F430:F65624 B443:E65637">
+    <cfRule type="expression" dxfId="7" priority="893" stopIfTrue="1">
+      <formula>OR(B427="│",B427="├─",B427="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K183:X197 G198:X426">
+    <cfRule type="expression" dxfId="6" priority="376" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="375" stopIfTrue="1">
+      <formula>OR($B199="├─",$B199="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y95:Z95">
+    <cfRule type="expression" dxfId="4" priority="356" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="355" stopIfTrue="1">
+      <formula>OR($B141="├─",$B141="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y65:AK65 B195:C196 B198:C199 B204:C217">
+    <cfRule type="expression" dxfId="2" priority="882" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA95:AK95">
+    <cfRule type="expression" dxfId="1" priority="2077" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2076" stopIfTrue="1">
+      <formula>OR(#REF!="├─",#REF!="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;06( \\wsl.localhost\Ubuntu\home\docker_cms\src\cms 配下)</oddHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5CDBE3-750C-4C0D-8AAF-43745D6A6F72}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:A126"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -3251,222 +10017,6 @@
     <row r="126" spans="1:1">
       <c r="A126" s="2" t="s">
         <v>90</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F76542-7475-450B-8480-EFB6EF4C355E}">
-  <dimension ref="A1:A61"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="39.75">
-      <c r="A7" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="30">
-      <c r="A16" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="30">
-      <c r="A28" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" ht="30">
-      <c r="A40" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="30">
-      <c r="A54" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -3476,534 +10026,214 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E709E9D4-AB6E-4CC2-8E0F-A5793B336BEE}">
-  <dimension ref="A1:A149"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F76542-7475-450B-8480-EFB6EF4C355E}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="39.75">
-      <c r="A1" s="1" t="s">
-        <v>120</v>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="30">
-      <c r="A3" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="2" t="s">
-        <v>123</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="39.75">
+      <c r="A7" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="2" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="2" t="s">
-        <v>127</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="30">
+      <c r="A16" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="2" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="30">
-      <c r="A27" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="30">
+      <c r="A28" s="5" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="2" t="s">
-        <v>1</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="2" t="s">
-        <v>134</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="2" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="2" t="s">
-        <v>127</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="30">
+      <c r="A40" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" ht="30">
-      <c r="A46" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="2" t="s">
-        <v>138</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="2" t="s">
-        <v>1</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="2" t="s">
-        <v>127</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="30">
+      <c r="A54" s="5" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" ht="30">
-      <c r="A60" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="39.75">
-      <c r="A69" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" ht="30">
-      <c r="A75" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" ht="30">
-      <c r="A76" s="5"/>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" ht="39.75">
-      <c r="A81" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" ht="30">
-      <c r="A90" s="5"/>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" ht="30">
-      <c r="A114" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="2" t="s">
-        <v>2</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -4013,352 +10243,535 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5098A92-C5C0-4353-AB1F-30D7DE2F67BE}">
-  <dimension ref="A2:I93"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E709E9D4-AB6E-4CC2-8E0F-A5793B336BEE}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:A149"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="1:9" ht="39.75">
-      <c r="A2" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="30">
-      <c r="A4" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+    <row r="1" spans="1:1" ht="39.75">
+      <c r="A1" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="30">
+      <c r="A3" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="39.75">
-      <c r="A9" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="39.75">
-      <c r="A15" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="I18" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="I19" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="I20" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="30">
-      <c r="A21" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="30">
+      <c r="A27" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:1">
       <c r="A31" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="2" t="s">
-        <v>195</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="2" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="2" t="s">
-        <v>198</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="2" t="s">
-        <v>199</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="2" t="s">
-        <v>200</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>201</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="2" t="s">
-        <v>207</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="30">
+      <c r="A46" s="5" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="2" t="s">
-        <v>198</v>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="2" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>210</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="2" t="s">
-        <v>211</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="2" t="s">
-        <v>212</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="2" t="s">
-        <v>216</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="30">
+      <c r="A60" s="5" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="2" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="2" t="s">
-        <v>198</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="2" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:1" ht="30">
-      <c r="A71" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="2" t="s">
-        <v>5</v>
-      </c>
+    <row r="69" spans="1:1" ht="39.75">
+      <c r="A69" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="30">
+      <c r="A75" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="30">
+      <c r="A76" s="5"/>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="2" t="s">
-        <v>6</v>
+        <v>229</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="2" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="2" t="s">
-        <v>10</v>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="39.75">
+      <c r="A81" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="2" t="s">
-        <v>12</v>
+      <c r="A83" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="2" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="2" t="s">
-        <v>13</v>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="30">
+      <c r="A90" s="5"/>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="2" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="2" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="30">
+      <c r="A114" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4368,7 +10781,364 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5098A92-C5C0-4353-AB1F-30D7DE2F67BE}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A2:I93"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="1:9" ht="39.75">
+      <c r="A2" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="30">
+      <c r="A4" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="39.75">
+      <c r="A9" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="39.75">
+      <c r="A15" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="I18" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="I19" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="I20" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="30">
+      <c r="A21" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="30">
+      <c r="A71" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626DB163-BD8B-468F-83A9-4D70FEBCA709}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A3:A124"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -4816,8 +11586,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA8CB5A-8AF9-428F-BF72-A4650EA2714E}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
@@ -5061,18 +11832,18 @@
       </c>
     </row>
     <row r="67" spans="1:2" ht="60.75" customHeight="1">
-      <c r="A67" s="34" t="s">
+      <c r="A67" s="33" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="234" customHeight="1">
-      <c r="A68" s="32" t="s">
+      <c r="A68" s="44" t="s">
         <v>448</v>
       </c>
-      <c r="B68" s="32"/>
+      <c r="B68" s="44"/>
     </row>
     <row r="69" spans="1:2" ht="164.25" customHeight="1">
-      <c r="A69" s="33" t="s">
+      <c r="A69" s="32" t="s">
         <v>449</v>
       </c>
       <c r="B69" s="29"/>
@@ -5235,8 +12006,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED49263E-B0E6-4B40-8C98-8489AC780DBF}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C219"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>

--- a/実装メモ.xlsx
+++ b/実装メモ.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\docker_cms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E245D286-C5D0-4D62-8FA2-1AEC2BEDD400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE810CB-774A-46CF-84F0-E05D9D725BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
   </bookViews>
   <sheets>
     <sheet name="構成図" sheetId="9" r:id="rId1"/>
-    <sheet name="アンケート機能_概要" sheetId="2" r:id="rId2"/>
-    <sheet name="アンケート機能_マイグレーション" sheetId="3" r:id="rId3"/>
-    <sheet name="アンケート機能_model" sheetId="4" r:id="rId4"/>
-    <sheet name="アンケート機能_フロント" sheetId="5" r:id="rId5"/>
-    <sheet name="番外編" sheetId="6" r:id="rId6"/>
-    <sheet name="アンケート結果_管理画面" sheetId="7" r:id="rId7"/>
-    <sheet name="filmentの構造に関する疑問" sheetId="8" r:id="rId8"/>
+    <sheet name="投票コメントテーブルに投票IDを加える変更" sheetId="12" r:id="rId2"/>
+    <sheet name="入力チェック(Livewire)" sheetId="10" r:id="rId3"/>
+    <sheet name="エラー文言" sheetId="11" r:id="rId4"/>
+    <sheet name="アンケート機能_概要" sheetId="2" r:id="rId5"/>
+    <sheet name="アンケート機能_マイグレーション" sheetId="3" r:id="rId6"/>
+    <sheet name="アンケート機能_model" sheetId="4" r:id="rId7"/>
+    <sheet name="アンケート機能_フロント" sheetId="5" r:id="rId8"/>
+    <sheet name="番外編" sheetId="6" r:id="rId9"/>
+    <sheet name="アンケート結果_管理画面" sheetId="7" r:id="rId10"/>
+    <sheet name="filmentの構造に関する疑問" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="696">
   <si>
     <t>Route::get('/survey/{id}', [SurveyController::class, 'show']);</t>
   </si>
@@ -2671,12 +2674,384 @@
     </rPh>
     <phoneticPr fontId="34"/>
   </si>
+  <si>
+    <t>「フロント / Livewire 共通」＝ LivewireコンポーネントのPHPファイル</t>
+  </si>
+  <si>
+    <t>app/Livewire/SurveyVote.php</t>
+  </si>
+  <si>
+    <t>または</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>app/Http/Livewire/SurveyVote.php</t>
+  </si>
+  <si>
+    <t>Livewireは👇の構造</t>
+  </si>
+  <si>
+    <t>役割</t>
+  </si>
+  <si>
+    <t>Blade</t>
+  </si>
+  <si>
+    <t>UI（入力欄）</t>
+  </si>
+  <si>
+    <t>PHP（Livewire）</t>
+  </si>
+  <si>
+    <t>ロジック（バリデーション・保存）</t>
+  </si>
+  <si>
+    <t>※今回はアンケート(Survey)にて管理もフロントも同じ選択肢を追加させないロジックを入れるという課題</t>
+    <rPh sb="1" eb="3">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>カダイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>重要な整理</t>
+  </si>
+  <si>
+    <t>場所</t>
+  </si>
+  <si>
+    <t>書く内容</t>
+  </si>
+  <si>
+    <t>Livewire PHP</t>
+  </si>
+  <si>
+    <t>rules(), 保存処理</t>
+  </si>
+  <si>
+    <t>入力欄 + エラー表示</t>
+  </si>
+  <si>
+    <t>Filament</t>
+  </si>
+  <si>
+    <t>別途 rule()</t>
+  </si>
+  <si>
+    <t>❗ よくある勘違い</t>
+  </si>
+  <si>
+    <t>❌ Controllerに書く？</t>
+  </si>
+  <si>
+    <t>→ 今回は使ってない（Livewireだから）</t>
+  </si>
+  <si>
+    <t>❌ Bladeに書く？</t>
+  </si>
+  <si>
+    <t>→ 書けない（ロジックはPHP側）</t>
+  </si>
+  <si>
+    <t>以下のコマンドで自動生成される。</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ジドウセイセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>php artisan make:livewire SurveyVote</t>
+  </si>
+  <si>
+    <t>自動で以下のファイルを作成する</t>
+    <rPh sb="0" eb="2">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>CLASS: app/Livewire/SurveyVote.php</t>
+  </si>
+  <si>
+    <t>VIEW:  resources/views/livewire/survey-vote.blade.php</t>
+  </si>
+  <si>
+    <t>Livewire</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SureveyVote.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>livewire</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>survey-vote.blade.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>テーブル毎の入力(request)の許可</t>
+    <rPh sb="4" eb="5">
+      <t>マイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キョカ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>アンケート画面のフロント表示</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>dd($request-&gt;all()); // 送信されたデータを確認するためのデバッグコード。これを使用して、フォームから正しいデータが送信されているかを確認できます。</t>
+  </si>
+  <si>
+    <t>PHPソースデバッグ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>🎯 判断基準（今回のケース）</t>
+  </si>
+  <si>
+    <t>あなたの構成は今こう👇</t>
+  </si>
+  <si>
+    <t>フロント：フォーム送信（POST /survey/vote）</t>
+  </si>
+  <si>
+    <t>バック：Controllerで保存</t>
+  </si>
+  <si>
+    <t>Filament：管理画面</t>
+  </si>
+  <si>
+    <t>👉 この場合</t>
+  </si>
+  <si>
+    <t>✅ Controllerが向いている理由</t>
+  </si>
+  <si>
+    <t>投票は「1回のPOSTで完結する処理」</t>
+  </si>
+  <si>
+    <t>トランザクション的（選択肢追加 → 投票 → コメント）</t>
+  </si>
+  <si>
+    <t>バリデーションも一括でOK</t>
+  </si>
+  <si>
+    <t>デバッグしやすい（今まさにやってる通り）</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">👉 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>シンプルで正解ルート</t>
+    </r>
+  </si>
+  <si>
+    <t>🤔 Livewireが向いているケース</t>
+  </si>
+  <si>
+    <t>逆にLivewireが強いのは👇</t>
+  </si>
+  <si>
+    <t>入力中にリアルタイムバリデーション</t>
+  </si>
+  <si>
+    <t>「新しい選択肢」入力した瞬間に重複チェック</t>
+  </si>
+  <si>
+    <t>Ajaxでページリロードなし</t>
+  </si>
+  <si>
+    <t>UIリッチ化（動的フォーム）</t>
+  </si>
+  <si>
+    <t>lang\ja\validation.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        </t>
+  </si>
+  <si>
+    <t>    ],</t>
+  </si>
+  <si>
+    <t>   'attributes' =&gt; [</t>
+  </si>
+  <si>
+    <t>        'new_option' =&gt; '選択肢',</t>
+  </si>
+  <si>
+    <t>        'comment' =&gt; 'コメント',</t>
+  </si>
+  <si>
+    <t>'unique'                 =&gt; '指定の:attributeは既に使用されています。',</t>
+  </si>
+  <si>
+    <t>フロントより何をインサートするかの定義、バリデーション定義</t>
+    <rPh sb="6" eb="7">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>管理画面＞アンケート＞アンケート結果</t>
+    <rPh sb="0" eb="4">
+      <t>カンリガメン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>ライブワイヤー、不要</t>
+    <rPh sb="8" eb="10">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>不要・アンケート追加選択肢の重複を防止(動的な動作の場合必要、POST処理のみの場合、Controllerで制御すれば良い)</t>
+    <rPh sb="0" eb="2">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジュウフク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ボウシ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ドウテキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>php artisan make:migration add_vote_id_to_survey_comments_table</t>
+  </si>
+  <si>
+    <t>public function up()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Schema::table('survey_comments', function (Blueprint $table) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        $table-&gt;foreignId('vote_id')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            -&gt;after('id')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            -&gt;constrained('survey_votes')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            -&gt;cascadeOnDelete();</t>
+  </si>
+  <si>
+    <t>public function down()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        $table-&gt;dropForeign(['vote_id']);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        $table-&gt;dropColumn('vote_id');</t>
+  </si>
+  <si>
+    <t>テーブル変更マイグレ</t>
+    <rPh sb="4" eb="6">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2947,6 +3322,20 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3057,7 +3446,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3167,6 +3556,14 @@
     <xf numFmtId="1" fontId="35" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="32" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3185,15 +3582,20 @@
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{F19A6957-2B34-4EDC-A43E-1512F220B8B2}"/>
   </cellStyles>
-  <dxfs count="217">
+  <dxfs count="215">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3211,6 +3613,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3218,14 +3627,14 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3253,6 +3662,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3260,6 +3676,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3344,6 +3767,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3351,6 +3781,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3358,6 +3795,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3365,6 +3809,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3379,6 +3830,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3400,6 +3858,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3428,6 +3893,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3470,6 +3942,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3491,6 +3970,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3519,6 +4005,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3526,6 +4019,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3561,6 +4061,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3610,6 +4117,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3680,6 +4194,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3687,6 +4208,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3708,6 +4243,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3729,6 +4271,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3778,6 +4327,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3806,6 +4362,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3911,6 +4474,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3932,6 +4502,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3988,6 +4565,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4030,6 +4614,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4079,6 +4670,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4156,6 +4761,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4170,6 +4782,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4191,6 +4810,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4226,6 +4852,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4240,6 +4873,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4247,6 +4887,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4296,6 +4943,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4310,6 +4964,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4317,6 +4978,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4324,6 +4999,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4331,6 +5020,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4380,329 +5076,14 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5044,7 +5425,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13CDE890-F993-425A-B129-8B17D7811949}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:X451"/>
+  <dimension ref="A1:X458"/>
   <sheetFormatPr defaultColWidth="4.375" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.375" style="38" customWidth="1"/>
@@ -5181,34 +5562,34 @@
       <c r="A1" s="34"/>
     </row>
     <row r="2" spans="1:24" ht="19.5" thickBot="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="43" t="s">
         <v>470</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="42" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="46" t="s">
         <v>372</v>
       </c>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="43"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="47"/>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="34"/>
@@ -5275,7 +5656,7 @@
       <c r="E7" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="F7" s="46" t="s">
+      <c r="F7" s="40" t="s">
         <v>526</v>
       </c>
     </row>
@@ -6190,7 +6571,7 @@
       <c r="G52" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="H52" s="45" t="s">
+      <c r="H52" s="39" t="s">
         <v>342</v>
       </c>
       <c r="S52" s="35" t="s">
@@ -6208,7 +6589,7 @@
       <c r="E53" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="F53" s="46" t="s">
+      <c r="F53" s="40" t="s">
         <v>553</v>
       </c>
     </row>
@@ -6223,7 +6604,7 @@
       <c r="E54" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="F54" s="46" t="s">
+      <c r="F54" s="40" t="s">
         <v>554</v>
       </c>
     </row>
@@ -6238,7 +6619,7 @@
       <c r="E55" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="F55" s="46" t="s">
+      <c r="F55" s="40" t="s">
         <v>555</v>
       </c>
     </row>
@@ -6253,7 +6634,7 @@
       <c r="E56" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="F56" s="46" t="s">
+      <c r="F56" s="40" t="s">
         <v>556</v>
       </c>
     </row>
@@ -6268,7 +6649,7 @@
       <c r="E57" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="F57" s="46" t="s">
+      <c r="F57" s="40" t="s">
         <v>557</v>
       </c>
     </row>
@@ -6283,7 +6664,7 @@
       <c r="E58" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="F58" s="46" t="s">
+      <c r="F58" s="39" t="s">
         <v>558</v>
       </c>
     </row>
@@ -6298,7 +6679,7 @@
       <c r="E59" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="F59" s="46" t="s">
+      <c r="F59" s="40" t="s">
         <v>559</v>
       </c>
     </row>
@@ -6313,7 +6694,7 @@
       <c r="E60" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="F60" s="46" t="s">
+      <c r="F60" s="40" t="s">
         <v>560</v>
       </c>
     </row>
@@ -6326,8 +6707,9 @@
         <v>472</v>
       </c>
       <c r="D61" s="35" t="s">
-        <v>561</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="F61" s="40"/>
     </row>
     <row r="62" spans="1:19">
       <c r="A62" s="34"/>
@@ -6340,8 +6722,11 @@
       <c r="D62" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="E62" s="35" t="s">
-        <v>566</v>
+      <c r="E62" s="39" t="s">
+        <v>649</v>
+      </c>
+      <c r="S62" s="35" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -6352,15 +6737,7 @@
       <c r="C63" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="D63" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="E63" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F63" s="35" t="s">
-        <v>564</v>
-      </c>
+      <c r="F63" s="40"/>
     </row>
     <row r="64" spans="1:19">
       <c r="A64" s="34"/>
@@ -6368,19 +6745,13 @@
         <v>474</v>
       </c>
       <c r="C64" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D64" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="E64" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="F64" s="45" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19">
       <c r="A65" s="34"/>
       <c r="B65" s="35" t="s">
         <v>474</v>
@@ -6388,20 +6759,32 @@
       <c r="C65" s="35" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="D65" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E65" s="35" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19">
       <c r="A66" s="34"/>
       <c r="B66" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D66" s="35" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>477</v>
+      </c>
+      <c r="E66" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F66" s="35" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19">
       <c r="A67" s="34"/>
       <c r="B67" s="35" t="s">
         <v>474</v>
@@ -6410,13 +6793,19 @@
         <v>474</v>
       </c>
       <c r="D67" s="35" t="s">
-        <v>567</v>
+        <v>477</v>
       </c>
       <c r="E67" s="35" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>476</v>
+      </c>
+      <c r="F67" s="39" t="s">
+        <v>565</v>
+      </c>
+      <c r="S67" s="35" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19">
       <c r="A68" s="34"/>
       <c r="B68" s="35" t="s">
         <v>474</v>
@@ -6424,29 +6813,20 @@
       <c r="C68" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="D68" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="E68" s="35" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+    </row>
+    <row r="69" spans="1:19">
       <c r="A69" s="34"/>
       <c r="B69" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C69" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D69" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="E69" s="35" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19">
       <c r="A70" s="34"/>
       <c r="B70" s="35" t="s">
         <v>474</v>
@@ -6458,10 +6838,10 @@
         <v>567</v>
       </c>
       <c r="E70" s="35" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19">
       <c r="A71" s="34"/>
       <c r="B71" s="35" t="s">
         <v>474</v>
@@ -6473,10 +6853,10 @@
         <v>567</v>
       </c>
       <c r="E71" s="35" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19">
       <c r="A72" s="34"/>
       <c r="B72" s="35" t="s">
         <v>474</v>
@@ -6488,10 +6868,10 @@
         <v>567</v>
       </c>
       <c r="E72" s="35" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19">
       <c r="A73" s="34"/>
       <c r="B73" s="35" t="s">
         <v>474</v>
@@ -6503,10 +6883,10 @@
         <v>567</v>
       </c>
       <c r="E73" s="35" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19">
       <c r="A74" s="34"/>
       <c r="B74" s="35" t="s">
         <v>474</v>
@@ -6517,11 +6897,11 @@
       <c r="D74" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E74" s="45" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+      <c r="E74" s="35" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19">
       <c r="A75" s="34"/>
       <c r="B75" s="35" t="s">
         <v>474</v>
@@ -6532,11 +6912,11 @@
       <c r="D75" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E75" s="45" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+      <c r="E75" s="35" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19">
       <c r="A76" s="34"/>
       <c r="B76" s="35" t="s">
         <v>474</v>
@@ -6547,11 +6927,11 @@
       <c r="D76" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E76" s="45" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+      <c r="E76" s="35" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19">
       <c r="A77" s="34"/>
       <c r="B77" s="35" t="s">
         <v>474</v>
@@ -6562,11 +6942,11 @@
       <c r="D77" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E77" s="45" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+      <c r="E77" s="39" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
       <c r="A78" s="34"/>
       <c r="B78" s="35" t="s">
         <v>474</v>
@@ -6577,11 +6957,14 @@
       <c r="D78" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E78" s="35" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="E78" s="39" t="s">
+        <v>596</v>
+      </c>
+      <c r="S78" s="35" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79" s="34"/>
       <c r="B79" s="35" t="s">
         <v>474</v>
@@ -6590,22 +6973,25 @@
         <v>474</v>
       </c>
       <c r="D79" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="E79" s="35" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>567</v>
+      </c>
+      <c r="E79" s="39" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19">
       <c r="A80" s="34"/>
       <c r="B80" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D80" s="35" t="s">
-        <v>577</v>
+        <v>567</v>
+      </c>
+      <c r="E80" s="39" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -6614,13 +7000,13 @@
         <v>474</v>
       </c>
       <c r="C81" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D81" s="35" t="s">
-        <v>476</v>
+        <v>567</v>
       </c>
       <c r="E81" s="35" t="s">
-        <v>568</v>
+        <v>599</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -6628,11 +7014,14 @@
       <c r="B82" s="35" t="s">
         <v>474</v>
       </c>
+      <c r="C82" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D82" s="35" t="s">
+        <v>476</v>
+      </c>
       <c r="E82" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F82" s="35" t="s">
-        <v>569</v>
+        <v>600</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -6640,11 +7029,11 @@
       <c r="B83" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="E83" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F83" s="35" t="s">
-        <v>570</v>
+      <c r="C83" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D83" s="35" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6652,11 +7041,14 @@
       <c r="B84" s="35" t="s">
         <v>474</v>
       </c>
+      <c r="C84" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D84" s="35" t="s">
+        <v>476</v>
+      </c>
       <c r="E84" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F84" s="35" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -6668,7 +7060,7 @@
         <v>567</v>
       </c>
       <c r="F85" s="35" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -6680,7 +7072,7 @@
         <v>567</v>
       </c>
       <c r="F86" s="35" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -6692,7 +7084,7 @@
         <v>567</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -6704,7 +7096,7 @@
         <v>567</v>
       </c>
       <c r="F88" s="35" t="s">
-        <v>526</v>
+        <v>572</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -6716,7 +7108,7 @@
         <v>567</v>
       </c>
       <c r="F89" s="35" t="s">
-        <v>121</v>
+        <v>573</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -6728,7 +7120,7 @@
         <v>567</v>
       </c>
       <c r="F90" s="35" t="s">
-        <v>142</v>
+        <v>574</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -6740,7 +7132,7 @@
         <v>567</v>
       </c>
       <c r="F91" s="35" t="s">
-        <v>132</v>
+        <v>526</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -6752,7 +7144,7 @@
         <v>567</v>
       </c>
       <c r="F92" s="35" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -6764,7 +7156,7 @@
         <v>567</v>
       </c>
       <c r="F93" s="35" t="s">
-        <v>575</v>
+        <v>142</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -6773,19 +7165,22 @@
         <v>474</v>
       </c>
       <c r="E94" s="35" t="s">
-        <v>476</v>
+        <v>567</v>
       </c>
       <c r="F94" s="35" t="s">
-        <v>576</v>
+        <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="34"/>
       <c r="B95" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="C95" s="35" t="s">
-        <v>578</v>
+        <v>474</v>
+      </c>
+      <c r="E95" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F95" s="35" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -6793,20 +7188,23 @@
       <c r="B96" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C96" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="D96" s="35" t="s">
-        <v>579</v>
+      <c r="E96" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="F96" s="35" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="97" spans="1:19">
       <c r="A97" s="34"/>
       <c r="B97" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="C97" s="35" t="s">
-        <v>580</v>
+        <v>474</v>
+      </c>
+      <c r="E97" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F97" s="35" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="98" spans="1:19">
@@ -6815,9 +7213,8 @@
         <v>472</v>
       </c>
       <c r="C98" s="35" t="s">
-        <v>581</v>
-      </c>
-      <c r="Q98" s="34"/>
+        <v>578</v>
+      </c>
     </row>
     <row r="99" spans="1:19">
       <c r="A99" s="34"/>
@@ -6825,49 +7222,41 @@
         <v>474</v>
       </c>
       <c r="C99" s="35" t="s">
-        <v>567</v>
+        <v>476</v>
       </c>
       <c r="D99" s="35" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="100" spans="1:19">
       <c r="A100" s="34"/>
       <c r="B100" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C100" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="D100" s="35" t="s">
-        <v>583</v>
-      </c>
-      <c r="S100" s="35" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
     </row>
     <row r="101" spans="1:19">
       <c r="A101" s="34"/>
       <c r="B101" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C101" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="D101" s="35" t="s">
-        <v>584</v>
-      </c>
-      <c r="S101" s="35" t="s">
-        <v>563</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="Q101" s="34"/>
     </row>
     <row r="102" spans="1:19">
       <c r="A102" s="34"/>
       <c r="B102" s="35" t="s">
-        <v>518</v>
+        <v>474</v>
       </c>
       <c r="C102" s="35" t="s">
-        <v>585</v>
+        <v>567</v>
+      </c>
+      <c r="D102" s="35" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -6876,13 +7265,13 @@
         <v>474</v>
       </c>
       <c r="C103" s="35" t="s">
-        <v>476</v>
+        <v>567</v>
       </c>
       <c r="D103" s="35" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="S103" s="35" t="s">
-        <v>601</v>
+        <v>562</v>
       </c>
     </row>
     <row r="104" spans="1:19">
@@ -6890,23 +7279,23 @@
       <c r="B104" s="35" t="s">
         <v>474</v>
       </c>
+      <c r="C104" s="35" t="s">
+        <v>476</v>
+      </c>
       <c r="D104" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="E104" s="35" t="s">
-        <v>519</v>
+        <v>584</v>
+      </c>
+      <c r="S104" s="35" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="105" spans="1:19">
       <c r="A105" s="34"/>
       <c r="B105" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="D105" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="E105" s="35" t="s">
-        <v>520</v>
+        <v>518</v>
+      </c>
+      <c r="C105" s="35" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6914,11 +7303,14 @@
       <c r="B106" s="35" t="s">
         <v>474</v>
       </c>
+      <c r="C106" s="35" t="s">
+        <v>476</v>
+      </c>
       <c r="D106" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="E106" s="35" t="s">
-        <v>521</v>
+        <v>586</v>
+      </c>
+      <c r="S106" s="35" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="107" spans="1:19">
@@ -6927,10 +7319,10 @@
         <v>474</v>
       </c>
       <c r="D107" s="35" t="s">
-        <v>472</v>
+        <v>567</v>
       </c>
       <c r="E107" s="35" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="108" spans="1:19">
@@ -6939,10 +7331,10 @@
         <v>474</v>
       </c>
       <c r="D108" s="35" t="s">
-        <v>472</v>
+        <v>567</v>
       </c>
       <c r="E108" s="35" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="109" spans="1:19">
@@ -6951,10 +7343,10 @@
         <v>474</v>
       </c>
       <c r="D109" s="35" t="s">
-        <v>476</v>
+        <v>567</v>
       </c>
       <c r="E109" s="35" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="110" spans="1:19">
@@ -6962,14 +7354,23 @@
       <c r="B110" s="35" t="s">
         <v>474</v>
       </c>
+      <c r="D110" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E110" s="35" t="s">
+        <v>522</v>
+      </c>
     </row>
     <row r="111" spans="1:19">
       <c r="A111" s="34"/>
       <c r="B111" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D111" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="C111" s="35" t="s">
-        <v>488</v>
+      <c r="E111" s="35" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -6977,65 +7378,41 @@
       <c r="B112" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C112" s="35" t="s">
-        <v>472</v>
-      </c>
       <c r="D112" s="35" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
+        <v>476</v>
+      </c>
+      <c r="E112" s="35" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" s="34"/>
       <c r="B113" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C113" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="D113" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="E113" s="35" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" s="34"/>
       <c r="B114" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C114" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="D114" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="E114" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="F114" s="35" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" s="34"/>
       <c r="B115" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C115" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D115" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="E115" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="F115" s="35" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" s="34"/>
       <c r="B116" s="35" t="s">
         <v>474</v>
@@ -7044,79 +7421,79 @@
         <v>474</v>
       </c>
       <c r="D116" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E116" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="F116" s="35" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" s="34"/>
       <c r="B117" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C117" s="35" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D117" s="35" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
+        <v>477</v>
+      </c>
+      <c r="E117" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F117" s="35" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
       <c r="A118" s="34"/>
       <c r="B118" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C118" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D118" s="35" t="s">
         <v>477</v>
       </c>
-      <c r="D118" s="35" t="s">
-        <v>476</v>
-      </c>
       <c r="E118" s="35" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
+        <v>472</v>
+      </c>
+      <c r="F118" s="35" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" s="34"/>
       <c r="B119" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C119" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D119" s="35" t="s">
         <v>477</v>
       </c>
       <c r="E119" s="35" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F119" s="35" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
       <c r="A120" s="34"/>
       <c r="B120" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C120" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D120" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="E120" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="F120" s="35" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" s="34"/>
       <c r="B121" s="35" t="s">
         <v>474</v>
@@ -7125,19 +7502,13 @@
         <v>477</v>
       </c>
       <c r="D121" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E121" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="F121" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="G121" s="35" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" s="34"/>
       <c r="B122" s="35" t="s">
         <v>474</v>
@@ -7152,10 +7523,10 @@
         <v>472</v>
       </c>
       <c r="F122" s="35" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" s="34"/>
       <c r="B123" s="35" t="s">
         <v>474</v>
@@ -7170,10 +7541,10 @@
         <v>472</v>
       </c>
       <c r="F123" s="35" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" s="34"/>
       <c r="B124" s="35" t="s">
         <v>474</v>
@@ -7185,13 +7556,16 @@
         <v>477</v>
       </c>
       <c r="E124" s="35" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F124" s="35" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
+        <v>476</v>
+      </c>
+      <c r="G124" s="35" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" s="34"/>
       <c r="B125" s="35" t="s">
         <v>474</v>
@@ -7203,16 +7577,13 @@
         <v>477</v>
       </c>
       <c r="E125" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F125" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="G125" s="35" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" s="34"/>
       <c r="B126" s="35" t="s">
         <v>474</v>
@@ -7224,13 +7595,13 @@
         <v>477</v>
       </c>
       <c r="E126" s="35" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F126" s="35" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" s="34"/>
       <c r="B127" s="35" t="s">
         <v>474</v>
@@ -7242,16 +7613,13 @@
         <v>477</v>
       </c>
       <c r="E127" s="35" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="F127" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="G127" s="35" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" s="34"/>
       <c r="B128" s="35" t="s">
         <v>474</v>
@@ -7263,19 +7631,16 @@
         <v>477</v>
       </c>
       <c r="E128" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F128" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G128" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="H128" s="35" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" s="34"/>
       <c r="B129" s="35" t="s">
         <v>474</v>
@@ -7287,73 +7652,94 @@
         <v>477</v>
       </c>
       <c r="E129" s="35" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9">
+        <v>476</v>
+      </c>
+      <c r="F129" s="35" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130" s="34"/>
       <c r="B130" s="35" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C130" s="35" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9">
+        <v>477</v>
+      </c>
+      <c r="D130" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E130" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="F130" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G130" s="35" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" s="34"/>
       <c r="B131" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C131" s="35" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D131" s="35" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9">
+        <v>477</v>
+      </c>
+      <c r="E131" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="F131" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G131" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H131" s="35" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" s="34"/>
       <c r="B132" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C132" s="35" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D132" s="35" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E132" s="35" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133" s="34"/>
       <c r="B133" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C133" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="D133" s="35" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134" s="34"/>
       <c r="B134" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C134" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D134" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="E134" s="35" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" s="34"/>
       <c r="B135" s="35" t="s">
         <v>474</v>
@@ -7365,76 +7751,64 @@
         <v>476</v>
       </c>
       <c r="E135" s="35" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136" s="34"/>
       <c r="B136" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C136" s="35" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D136" s="35" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" s="34"/>
       <c r="B137" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C137" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D137" s="35" t="s">
         <v>472</v>
       </c>
       <c r="E137" s="35" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" s="34"/>
       <c r="B138" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C138" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D138" s="35" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E138" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="F138" s="35" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
       <c r="A139" s="34"/>
       <c r="B139" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C139" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D139" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="E139" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="F139" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="G139" s="35" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140" s="34"/>
       <c r="B140" s="35" t="s">
         <v>474</v>
@@ -7443,16 +7817,13 @@
         <v>477</v>
       </c>
       <c r="D140" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E140" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="F140" s="35" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" s="34"/>
       <c r="B141" s="35" t="s">
         <v>474</v>
@@ -7464,16 +7835,13 @@
         <v>474</v>
       </c>
       <c r="E141" s="35" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="F141" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="G141" s="35" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142" s="34"/>
       <c r="B142" s="35" t="s">
         <v>474</v>
@@ -7485,19 +7853,16 @@
         <v>474</v>
       </c>
       <c r="E142" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F142" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G142" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="H142" s="35" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143" s="34"/>
       <c r="B143" s="35" t="s">
         <v>474</v>
@@ -7509,22 +7874,13 @@
         <v>474</v>
       </c>
       <c r="E143" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F143" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="G143" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="H143" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="I143" s="45" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
       <c r="A144" s="34"/>
       <c r="B144" s="35" t="s">
         <v>474</v>
@@ -7533,13 +7889,19 @@
         <v>477</v>
       </c>
       <c r="D144" s="35" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E144" s="35" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
+        <v>477</v>
+      </c>
+      <c r="F144" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="G144" s="35" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19">
       <c r="A145" s="34"/>
       <c r="B145" s="35" t="s">
         <v>474</v>
@@ -7551,13 +7913,19 @@
         <v>474</v>
       </c>
       <c r="E145" s="35" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F145" s="35" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
+        <v>477</v>
+      </c>
+      <c r="G145" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H145" s="35" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19">
       <c r="A146" s="34"/>
       <c r="B146" s="35" t="s">
         <v>474</v>
@@ -7569,13 +7937,25 @@
         <v>474</v>
       </c>
       <c r="E146" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="F146" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G146" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="H146" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="F146" s="35" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+      <c r="I146" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="S146" s="35" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19">
       <c r="A147" s="34"/>
       <c r="B147" s="35" t="s">
         <v>474</v>
@@ -7587,10 +7967,10 @@
         <v>472</v>
       </c>
       <c r="E147" s="35" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19">
       <c r="A148" s="34"/>
       <c r="B148" s="35" t="s">
         <v>474</v>
@@ -7605,10 +7985,10 @@
         <v>472</v>
       </c>
       <c r="F148" s="35" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19">
       <c r="A149" s="34"/>
       <c r="B149" s="35" t="s">
         <v>474</v>
@@ -7623,73 +8003,58 @@
         <v>476</v>
       </c>
       <c r="F149" s="35" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19">
       <c r="A150" s="34"/>
       <c r="B150" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C150" s="35" t="s">
-        <v>477</v>
-      </c>
       <c r="D150" s="35" t="s">
         <v>472</v>
       </c>
       <c r="E150" s="35" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19">
       <c r="A151" s="34"/>
       <c r="B151" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C151" s="35" t="s">
-        <v>477</v>
-      </c>
       <c r="D151" s="35" t="s">
         <v>474</v>
       </c>
       <c r="E151" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="F151" s="35" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
+      <c r="F151" s="39" t="s">
+        <v>651</v>
+      </c>
+      <c r="S151" s="35" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19">
       <c r="A152" s="34"/>
       <c r="B152" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C152" s="35" t="s">
-        <v>477</v>
-      </c>
       <c r="D152" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="E152" s="45" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19">
       <c r="A153" s="34"/>
       <c r="B153" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C153" s="35" t="s">
-        <v>477</v>
-      </c>
       <c r="D153" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="E153" s="35" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19">
       <c r="A154" s="34"/>
       <c r="B154" s="35" t="s">
         <v>474</v>
@@ -7698,70 +8063,127 @@
         <v>477</v>
       </c>
       <c r="D154" s="35" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E154" s="35" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19">
       <c r="A155" s="34"/>
       <c r="B155" s="35" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="156" spans="1:6">
+      <c r="C155" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D155" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E155" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="F155" s="35" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19">
       <c r="A156" s="34"/>
       <c r="B156" s="35" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="157" spans="1:6">
+      <c r="C156" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D156" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E156" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F156" s="35" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19">
       <c r="A157" s="34"/>
       <c r="B157" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C157" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D157" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="C157" s="35" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
+      <c r="E157" s="35" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19">
       <c r="A158" s="34"/>
       <c r="B158" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C158" s="35" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D158" s="35" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
+        <v>474</v>
+      </c>
+      <c r="E158" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F158" s="35" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19">
       <c r="A159" s="34"/>
       <c r="B159" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C159" s="35" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D159" s="35" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
+        <v>472</v>
+      </c>
+      <c r="E159" s="39" t="s">
+        <v>613</v>
+      </c>
+      <c r="S159" s="35" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19">
       <c r="A160" s="34"/>
       <c r="B160" s="35" t="s">
         <v>474</v>
+      </c>
+      <c r="C160" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D160" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E160" s="35" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="34"/>
       <c r="B161" s="35" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C161" s="35" t="s">
-        <v>505</v>
+        <v>477</v>
+      </c>
+      <c r="D161" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E161" s="35" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -7769,41 +8191,20 @@
       <c r="B162" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C162" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="D162" s="35" t="s">
-        <v>473</v>
-      </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="34"/>
       <c r="B163" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C163" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="D163" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="E163" s="35" t="s">
-        <v>506</v>
-      </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="34"/>
       <c r="B164" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C164" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="D164" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="E164" s="35" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -7812,16 +8213,10 @@
         <v>474</v>
       </c>
       <c r="C165" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D165" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="E165" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="F165" s="35" t="s">
-        <v>506</v>
+        <v>602</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -7830,13 +8225,10 @@
         <v>474</v>
       </c>
       <c r="C166" s="35" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D166" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="E166" s="35" t="s">
-        <v>488</v>
+        <v>603</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -7844,35 +8236,14 @@
       <c r="B167" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C167" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="D167" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="E167" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="F167" s="35" t="s">
-        <v>506</v>
-      </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="34"/>
       <c r="B168" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C168" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="D168" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="E168" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="F168" s="35" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -7881,16 +8252,10 @@
         <v>474</v>
       </c>
       <c r="C169" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D169" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="E169" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="F169" s="35" t="s">
-        <v>503</v>
+        <v>473</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -7902,13 +8267,10 @@
         <v>474</v>
       </c>
       <c r="D170" s="35" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E170" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="F170" s="35" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -7920,13 +8282,10 @@
         <v>474</v>
       </c>
       <c r="D171" s="35" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E171" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="F171" s="35" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -7935,10 +8294,16 @@
         <v>474</v>
       </c>
       <c r="C172" s="35" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D172" s="35" t="s">
-        <v>510</v>
+        <v>474</v>
+      </c>
+      <c r="E172" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F172" s="35" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -7950,10 +8315,10 @@
         <v>474</v>
       </c>
       <c r="D173" s="35" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E173" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -7965,13 +8330,13 @@
         <v>474</v>
       </c>
       <c r="D174" s="35" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E174" s="35" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F174" s="35" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -7983,10 +8348,13 @@
         <v>474</v>
       </c>
       <c r="D175" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E175" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="E175" s="35" t="s">
-        <v>512</v>
+      <c r="F175" s="35" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -7998,13 +8366,16 @@
         <v>474</v>
       </c>
       <c r="D176" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E176" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="E176" s="35" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
+      <c r="F176" s="35" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
       <c r="A177" s="34"/>
       <c r="B177" s="35" t="s">
         <v>474</v>
@@ -8013,88 +8384,178 @@
         <v>474</v>
       </c>
       <c r="D177" s="35" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E177" s="35" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
+        <v>472</v>
+      </c>
+      <c r="F177" s="35" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
       <c r="A178" s="34"/>
       <c r="B178" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C178" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D178" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E178" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="D178" s="35" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
+      <c r="F178" s="35" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
       <c r="A179" s="34"/>
       <c r="B179" s="35" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C179" s="35" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
+        <v>472</v>
+      </c>
+      <c r="D179" s="35" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
       <c r="A180" s="34"/>
       <c r="B180" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C180" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D180" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="D180" s="35" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
+      <c r="E180" s="35" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
       <c r="A181" s="34"/>
       <c r="B181" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C181" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D181" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="E181" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="F181" s="35" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" s="34"/>
+      <c r="B182" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C182" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D182" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E182" s="35" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" s="34"/>
+      <c r="B183" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C183" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D183" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E183" s="35" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" s="34"/>
+      <c r="B184" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C184" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D184" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E184" s="35" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" s="34"/>
+      <c r="B185" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C185" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D185" s="35" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" s="34"/>
+      <c r="B186" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="C186" s="35" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" s="34"/>
+      <c r="B187" s="35" t="s">
         <v>477</v>
       </c>
-      <c r="C181" s="35" t="s">
+      <c r="C187" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D187" s="35" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" s="34"/>
+      <c r="B188" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="C188" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="D181" s="35" t="s">
+      <c r="D188" s="35" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
-      <c r="A182" s="34"/>
-    </row>
-    <row r="183" spans="1:5">
-      <c r="A183" s="34"/>
-    </row>
-    <row r="184" spans="1:5">
-      <c r="A184" s="34"/>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185" s="34"/>
-    </row>
-    <row r="186" spans="1:5">
-      <c r="A186" s="34"/>
-    </row>
-    <row r="187" spans="1:5">
-      <c r="A187" s="34"/>
-    </row>
-    <row r="188" spans="1:5">
-      <c r="A188" s="34"/>
-    </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:6">
       <c r="A189" s="34"/>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:6">
       <c r="A190" s="34"/>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:6">
       <c r="A191" s="34"/>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:6">
       <c r="A192" s="34"/>
     </row>
     <row r="193" spans="1:1">
@@ -8873,6 +9334,27 @@
     </row>
     <row r="451" spans="1:1">
       <c r="A451" s="34"/>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" s="34"/>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" s="34"/>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454" s="34"/>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" s="34"/>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" s="34"/>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457" s="34"/>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8880,721 +9362,713 @@
     <mergeCell ref="S2:X2"/>
   </mergeCells>
   <phoneticPr fontId="34"/>
-  <conditionalFormatting sqref="A183:A202">
-    <cfRule type="expression" dxfId="216" priority="1332" stopIfTrue="1">
-      <formula>OR($B164="├─",$B164="└─")</formula>
+  <conditionalFormatting sqref="A190:A209">
+    <cfRule type="expression" dxfId="214" priority="1332" stopIfTrue="1">
+      <formula>OR($B171="├─",$B171="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A184:A185 A187 A193">
-    <cfRule type="expression" dxfId="215" priority="1226" stopIfTrue="1">
-      <formula>OR($B165="├─",$B165="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="214" priority="1227" stopIfTrue="1">
+  <conditionalFormatting sqref="A191:A192 A194 A200">
+    <cfRule type="expression" dxfId="213" priority="1233" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="213" priority="1228" stopIfTrue="1">
-      <formula>OR($B165="├─",$B165="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="212" priority="1229" stopIfTrue="1">
+    <cfRule type="expression" dxfId="212" priority="1224" stopIfTrue="1">
+      <formula>OR($B172="├─",$B172="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="211" priority="1226" stopIfTrue="1">
+      <formula>OR($B172="├─",$B172="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="210" priority="1227" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="211" priority="1230" stopIfTrue="1">
-      <formula>OR($B165="├─",$B165="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="210" priority="1231" stopIfTrue="1">
+    <cfRule type="expression" dxfId="209" priority="1228" stopIfTrue="1">
+      <formula>OR($B172="├─",$B172="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="208" priority="1229" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="209" priority="1232" stopIfTrue="1">
-      <formula>OR($B165="├─",$B165="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="208" priority="1233" stopIfTrue="1">
+    <cfRule type="expression" dxfId="207" priority="1230" stopIfTrue="1">
+      <formula>OR($B172="├─",$B172="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="206" priority="1225" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="207" priority="1234" stopIfTrue="1">
-      <formula>OR($B165="├─",$B165="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="206" priority="1235" stopIfTrue="1">
+    <cfRule type="expression" dxfId="205" priority="1231" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="205" priority="1224" stopIfTrue="1">
-      <formula>OR($B165="├─",$B165="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="204" priority="1225" stopIfTrue="1">
+    <cfRule type="expression" dxfId="204" priority="1232" stopIfTrue="1">
+      <formula>OR($B172="├─",$B172="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="203" priority="1234" stopIfTrue="1">
+      <formula>OR($B172="├─",$B172="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="202" priority="1235" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A184:A185 A187:A188 A190:A197">
-    <cfRule type="expression" dxfId="203" priority="1237" stopIfTrue="1">
+  <conditionalFormatting sqref="A191:A192 A194:A195 A197:A204">
+    <cfRule type="expression" dxfId="201" priority="1237" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="202" priority="1236" stopIfTrue="1">
-      <formula>OR($B165="├─",$B165="└─")</formula>
+    <cfRule type="expression" dxfId="200" priority="1236" stopIfTrue="1">
+      <formula>OR($B172="├─",$B172="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A188 A190:A197">
-    <cfRule type="expression" dxfId="201" priority="1343" stopIfTrue="1">
+  <conditionalFormatting sqref="A195 A197:A204">
+    <cfRule type="expression" dxfId="199" priority="1343" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A188 A196:A197">
-    <cfRule type="expression" dxfId="200" priority="1342" stopIfTrue="1">
-      <formula>OR($B169="├─",$B169="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="199" priority="1341" stopIfTrue="1">
+  <conditionalFormatting sqref="A195 A203:A204">
+    <cfRule type="expression" dxfId="198" priority="1335" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="198" priority="1340" stopIfTrue="1">
-      <formula>OR($B169="├─",$B169="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="197" priority="1339" stopIfTrue="1">
+    <cfRule type="expression" dxfId="197" priority="1336" stopIfTrue="1">
+      <formula>OR($B176="├─",$B176="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="196" priority="1337" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="196" priority="1338" stopIfTrue="1">
-      <formula>OR($B169="├─",$B169="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="195" priority="1337" stopIfTrue="1">
+    <cfRule type="expression" dxfId="195" priority="1338" stopIfTrue="1">
+      <formula>OR($B176="├─",$B176="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="194" priority="1339" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="194" priority="1336" stopIfTrue="1">
-      <formula>OR($B169="├─",$B169="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="193" priority="1335" stopIfTrue="1">
+    <cfRule type="expression" dxfId="193" priority="1340" stopIfTrue="1">
+      <formula>OR($B176="├─",$B176="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="192" priority="1341" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="192" priority="1334" stopIfTrue="1">
-      <formula>OR($B169="├─",$B169="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="191" priority="1333" stopIfTrue="1">
+    <cfRule type="expression" dxfId="191" priority="1342" stopIfTrue="1">
+      <formula>OR($B176="├─",$B176="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="190" priority="1333" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="189" priority="1334" stopIfTrue="1">
+      <formula>OR($B176="├─",$B176="└─")</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A188">
-    <cfRule type="expression" dxfId="190" priority="1344" stopIfTrue="1">
-      <formula>OR($B169="├─",$B169="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="189" priority="1345" stopIfTrue="1">
+  <conditionalFormatting sqref="A195">
+    <cfRule type="expression" dxfId="188" priority="1345" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="187" priority="1344" stopIfTrue="1">
+      <formula>OR($B176="├─",$B176="└─")</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A192">
-    <cfRule type="expression" dxfId="188" priority="1410" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="187" priority="1411" stopIfTrue="1">
+  <conditionalFormatting sqref="A199">
+    <cfRule type="expression" dxfId="186" priority="1409" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="1401" stopIfTrue="1">
+    <cfRule type="expression" dxfId="185" priority="1410" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="184" priority="1392" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="183" priority="1411" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="1402" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="184" priority="1403" stopIfTrue="1">
+    <cfRule type="expression" dxfId="182" priority="1395" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="183" priority="1404" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="182" priority="1405" stopIfTrue="1">
+    <cfRule type="expression" dxfId="181" priority="1396" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="180" priority="1393" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="1406" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="180" priority="1407" stopIfTrue="1">
+    <cfRule type="expression" dxfId="179" priority="1397" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="179" priority="1408" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="178" priority="1409" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="1398" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="177" priority="1399" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="1400" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="176" priority="1392" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="175" priority="1393" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="1400" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="175" priority="1401" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="1394" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="173" priority="1395" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="1402" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="173" priority="1403" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="1396" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="171" priority="1397" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="1404" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="171" priority="1405" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="1398" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="169" priority="1399" stopIfTrue="1">
+    <cfRule type="expression" dxfId="170" priority="1394" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="169" priority="1406" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="168" priority="1407" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="167" priority="1408" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A192:A193">
-    <cfRule type="expression" dxfId="168" priority="1432" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="167" priority="1433" stopIfTrue="1">
+  <conditionalFormatting sqref="A199:A200">
+    <cfRule type="expression" dxfId="166" priority="1432" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="165" priority="1433" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="1434" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="165" priority="1435" stopIfTrue="1">
+    <cfRule type="expression" dxfId="164" priority="1434" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="163" priority="1435" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="1436" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="163" priority="1437" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="1436" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="161" priority="1437" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A192:A194">
-    <cfRule type="expression" dxfId="162" priority="1439" stopIfTrue="1">
+  <conditionalFormatting sqref="A199:A201">
+    <cfRule type="expression" dxfId="160" priority="1438" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="159" priority="1439" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="1438" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A194">
-    <cfRule type="expression" dxfId="160" priority="1502" stopIfTrue="1">
-      <formula>OR($B175="├─",$B175="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="159" priority="1520" stopIfTrue="1">
-      <formula>OR($B175="├─",$B175="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="158" priority="1516" stopIfTrue="1">
-      <formula>OR($B175="├─",$B175="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="157" priority="1517" stopIfTrue="1">
+  <conditionalFormatting sqref="A201">
+    <cfRule type="expression" dxfId="158" priority="1502" stopIfTrue="1">
+      <formula>OR($B182="├─",$B182="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="157" priority="1503" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="156" priority="1515" stopIfTrue="1">
+    <cfRule type="expression" dxfId="156" priority="1504" stopIfTrue="1">
+      <formula>OR($B182="├─",$B182="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="155" priority="1505" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="155" priority="1514" stopIfTrue="1">
-      <formula>OR($B175="├─",$B175="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="154" priority="1513" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="1507" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="1512" stopIfTrue="1">
-      <formula>OR($B175="├─",$B175="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="152" priority="1511" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="1509" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="151" priority="1510" stopIfTrue="1">
-      <formula>OR($B175="├─",$B175="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="150" priority="1509" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="1510" stopIfTrue="1">
+      <formula>OR($B182="├─",$B182="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="151" priority="1511" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="1508" stopIfTrue="1">
-      <formula>OR($B175="├─",$B175="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="148" priority="1507" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="1512" stopIfTrue="1">
+      <formula>OR($B182="├─",$B182="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="149" priority="1513" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="147" priority="1506" stopIfTrue="1">
-      <formula>OR($B175="├─",$B175="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="146" priority="1505" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="1514" stopIfTrue="1">
+      <formula>OR($B182="├─",$B182="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="147" priority="1515" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="1504" stopIfTrue="1">
-      <formula>OR($B175="├─",$B175="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="144" priority="1503" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="1508" stopIfTrue="1">
+      <formula>OR($B182="├─",$B182="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="145" priority="1516" stopIfTrue="1">
+      <formula>OR($B182="├─",$B182="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="144" priority="1517" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="143" priority="1518" stopIfTrue="1">
-      <formula>OR($B175="├─",$B175="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="142" priority="1519" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="1521" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="1520" stopIfTrue="1">
+      <formula>OR($B182="├─",$B182="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="140" priority="1521" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="139" priority="1506" stopIfTrue="1">
+      <formula>OR($B182="├─",$B182="└─")</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A196">
-    <cfRule type="expression" dxfId="140" priority="1580" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="139" priority="1581" stopIfTrue="1">
+  <conditionalFormatting sqref="A203">
+    <cfRule type="expression" dxfId="138" priority="1566" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="137" priority="1567" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="1582" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="137" priority="1583" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="1568" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="135" priority="1569" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="1584" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="135" priority="1585" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="1570" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="133" priority="1571" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="1586" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="133" priority="1587" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="1572" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="131" priority="1573" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="1566" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="131" priority="1567" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="1574" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="129" priority="1575" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="1568" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="129" priority="1569" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="1576" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="127" priority="1577" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="1570" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="127" priority="1571" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="1578" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="125" priority="1579" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="1572" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="125" priority="1573" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="1580" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="123" priority="1581" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="1574" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="123" priority="1575" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="1582" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="121" priority="1583" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="1576" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="121" priority="1577" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="1584" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="119" priority="1585" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="1578" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="119" priority="1579" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="1586" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="117" priority="1587" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A196:A197">
-    <cfRule type="expression" dxfId="118" priority="1588" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="117" priority="1589" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
+  <conditionalFormatting sqref="A203:A204">
     <cfRule type="expression" dxfId="116" priority="1330" stopIfTrue="1">
-      <formula>OR($B177="├─",$B177="└─")</formula>
+      <formula>OR($B184="├─",$B184="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="115" priority="1331" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="114" priority="1588" stopIfTrue="1">
+      <formula>OR($B184="├─",$B184="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="113" priority="1589" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A197">
-    <cfRule type="expression" dxfId="114" priority="1662" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="113" priority="1663" stopIfTrue="1">
+  <conditionalFormatting sqref="A204">
+    <cfRule type="expression" dxfId="112" priority="1654" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="111" priority="1670" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="110" priority="1671" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="1664" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="111" priority="1665" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="1672" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="1673" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="1666" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="109" priority="1667" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="1674" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="1675" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="1668" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="107" priority="1669" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="1684" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="1676" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="1677" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="1670" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="105" priority="1671" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="104" priority="1673" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="103" priority="1674" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="1675" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
+    <cfRule type="expression" dxfId="102" priority="1678" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="1679" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="1676" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="99" priority="1677" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="1680" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="1681" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="1678" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="97" priority="1689" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="1682" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="1683" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="1688" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="95" priority="1687" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="1689" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="1686" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="1685" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="1688" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="94" priority="1687" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="1684" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="1683" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="1686" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="92" priority="1650" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="91" priority="1651" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="1682" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="1681" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="1652" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="1653" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="1680" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="1672" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="1650" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="1651" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="1685" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="1652" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="1653" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="1655" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="1654" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="1655" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="1656" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="1657" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="1656" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="1657" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="1658" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="1659" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="1658" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="1659" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="1660" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="1661" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="1660" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="1661" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="1662" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="1663" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="78" priority="1664" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="1665" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="1666" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="1667" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="1668" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="1669" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A197:A198">
-    <cfRule type="expression" dxfId="74" priority="1748" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="1747" stopIfTrue="1">
+  <conditionalFormatting sqref="A204:A205">
+    <cfRule type="expression" dxfId="72" priority="1745" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="1746" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="1745" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="1744" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="1743" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="1744" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="1743" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
+    <cfRule type="expression" dxfId="69" priority="1742" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="68" priority="1741" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="67" priority="1740" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="1739" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="1738" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="1737" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="1738" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="1737" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="1736" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="1735" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="1736" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="1735" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="1734" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="1733" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="1734" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="1733" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="1739" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="59" priority="1732" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="1742" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="1749" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="1746" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="1747" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="56" priority="1748" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="1749" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A198">
-    <cfRule type="expression" dxfId="56" priority="1785" stopIfTrue="1">
+  <conditionalFormatting sqref="A205">
+    <cfRule type="expression" dxfId="54" priority="1788" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="1768" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="1769" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="1768" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="1769" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="1770" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="1771" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="1770" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="1771" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="1772" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="1773" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="1772" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="1773" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="1774" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="1775" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="1774" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="1775" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="1776" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="1777" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="1776" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="1777" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="1778" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="1779" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="1778" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="1779" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="1780" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="1781" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="1780" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="1781" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="1782" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="1783" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="1782" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="1783" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="1784" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="1785" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="1784" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="1786" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="1787" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="1786" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="1787" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="1788" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="1789" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="1789" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="1790" stopIfTrue="1">
-      <formula>OR($B179="├─",$B179="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="1791" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="1790" stopIfTrue="1">
+      <formula>OR($B186="├─",$B186="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="1791" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A200 B194:E442">
-    <cfRule type="expression" dxfId="32" priority="1365" stopIfTrue="1">
+  <conditionalFormatting sqref="A207 B201:E449">
+    <cfRule type="expression" dxfId="30" priority="1365" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A200">
-    <cfRule type="expression" dxfId="31" priority="1364" stopIfTrue="1">
-      <formula>OR($B181="├─",$B181="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="1363" stopIfTrue="1">
+  <conditionalFormatting sqref="A207">
+    <cfRule type="expression" dxfId="29" priority="1364" stopIfTrue="1">
+      <formula>OR($B188="├─",$B188="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="1363" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A203:A451">
-    <cfRule type="expression" dxfId="29" priority="2069" stopIfTrue="1">
-      <formula>OR($B194="├─",$B194="└─")</formula>
+  <conditionalFormatting sqref="A210:A458">
+    <cfRule type="expression" dxfId="27" priority="2069" stopIfTrue="1">
+      <formula>OR($B201="├─",$B201="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A204:A205 A207:A208 A213:A226">
-    <cfRule type="expression" dxfId="28" priority="1919" stopIfTrue="1">
-      <formula>OR($B195="├─",$B195="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="1920" stopIfTrue="1">
+  <conditionalFormatting sqref="A211:A212 A214:A215 A220:A233">
+    <cfRule type="expression" dxfId="26" priority="1919" stopIfTrue="1">
+      <formula>OR($B202="├─",$B202="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="1920" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A222:A224">
-    <cfRule type="expression" dxfId="26" priority="2045" stopIfTrue="1">
-      <formula>OR($B213="├─",$B213="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="2046" stopIfTrue="1">
+  <conditionalFormatting sqref="A229:A231">
+    <cfRule type="expression" dxfId="24" priority="2045" stopIfTrue="1">
+      <formula>OR($B220="├─",$B220="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="2046" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="2047" stopIfTrue="1">
-      <formula>OR($B213="├─",$B213="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="2048" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="2047" stopIfTrue="1">
+      <formula>OR($B220="├─",$B220="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="2048" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A98:AN98 A4:X97">
-    <cfRule type="expression" dxfId="22" priority="802" stopIfTrue="1">
+  <conditionalFormatting sqref="B211:C224 Y68:AK68 B202:C203 B205:C206">
+    <cfRule type="expression" dxfId="20" priority="881" stopIfTrue="1">
+      <formula>OR($B68="├─",$B68="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B220:C222">
+    <cfRule type="expression" dxfId="19" priority="824" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="801" stopIfTrue="1">
-      <formula>OR($B4="├─",$B4="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A99:X182">
-    <cfRule type="expression" dxfId="20" priority="1" stopIfTrue="1">
-      <formula>OR($B99="├─",$B99="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="2" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B204:C217 Y65:AK65 B195:C196 B198:C199">
-    <cfRule type="expression" dxfId="18" priority="881" stopIfTrue="1">
-      <formula>OR($B65="├─",$B65="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B213:C215">
+    <cfRule type="expression" dxfId="18" priority="823" stopIfTrue="1">
+      <formula>OR($B220="├─",$B220="└─")</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="17" priority="820" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="819" stopIfTrue="1">
-      <formula>OR($B213="├─",$B213="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="824" stopIfTrue="1">
+      <formula>OR($B220="├─",$B220="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B190:E190 A190:A458">
+    <cfRule type="expression" dxfId="15" priority="890" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="823" stopIfTrue="1">
-      <formula>OR($B213="├─",$B213="└─")</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B183:E183 A183:A451">
-    <cfRule type="expression" dxfId="13" priority="890" stopIfTrue="1">
+  <conditionalFormatting sqref="B201:E449 B190:E190">
+    <cfRule type="expression" dxfId="14" priority="889" stopIfTrue="1">
+      <formula>OR($B190="├─",$B190="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:R1 T1:X1 A1:A3 S1:S3 B3:R3 T3:X3 A4:X100 A101:AN101 A102:X150 A151:R151 A152:X158 A159:R159 A160:X189">
+    <cfRule type="expression" dxfId="13" priority="802" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="12" priority="801" stopIfTrue="1">
+      <formula>OR($B1="├─",$B1="└─")</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B194:E442 B183:E183">
-    <cfRule type="expression" dxfId="12" priority="889" stopIfTrue="1">
-      <formula>OR($B183="├─",$B183="└─")</formula>
+  <conditionalFormatting sqref="F205:F436">
+    <cfRule type="expression" dxfId="11" priority="938" stopIfTrue="1">
+      <formula>OR($B218="├─",$B218="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="939" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:R1 T1:X1 A1:A3 S1:S3 B3:R3 T3:X3">
-    <cfRule type="expression" dxfId="11" priority="895" stopIfTrue="1">
+  <conditionalFormatting sqref="G434:X65628 F437:F65631 B450:E65644">
+    <cfRule type="expression" dxfId="9" priority="893" stopIfTrue="1">
+      <formula>OR(B434="│",B434="├─",B434="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K190:X204 G205:X433">
+    <cfRule type="expression" dxfId="8" priority="376" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="894" stopIfTrue="1">
-      <formula>OR($B1="├─",$B1="└─")</formula>
+    <cfRule type="expression" dxfId="7" priority="375" stopIfTrue="1">
+      <formula>OR($B206="├─",$B206="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F198:F429">
-    <cfRule type="expression" dxfId="9" priority="939" stopIfTrue="1">
+  <conditionalFormatting sqref="S159:X159">
+    <cfRule type="expression" dxfId="6" priority="2080" stopIfTrue="1">
+      <formula>OR($B151="├─",$B151="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="2081" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="938" stopIfTrue="1">
-      <formula>OR($B211="├─",$B211="└─")</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G427:X65621 F430:F65624 B443:E65637">
-    <cfRule type="expression" dxfId="7" priority="893" stopIfTrue="1">
-      <formula>OR(B427="│",B427="├─",B427="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K183:X197 G198:X426">
-    <cfRule type="expression" dxfId="6" priority="376" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="375" stopIfTrue="1">
-      <formula>OR($B199="├─",$B199="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y95:Z95">
+  <conditionalFormatting sqref="Y98:Z98">
     <cfRule type="expression" dxfId="4" priority="356" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="355" stopIfTrue="1">
-      <formula>OR($B141="├─",$B141="└─")</formula>
+      <formula>OR($B144="├─",$B144="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y65:AK65 B195:C196 B198:C199 B204:C217">
+  <conditionalFormatting sqref="Y68:AK68 B202:C203 B205:C206 B211:C224">
     <cfRule type="expression" dxfId="2" priority="882" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA95:AK95">
-    <cfRule type="expression" dxfId="1" priority="2077" stopIfTrue="1">
+  <conditionalFormatting sqref="AA98:AK98">
+    <cfRule type="expression" dxfId="1" priority="2076" stopIfTrue="1">
+      <formula>OR(#REF!="├─",#REF!="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2077" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2076" stopIfTrue="1">
-      <formula>OR(#REF!="├─",#REF!="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9605,1988 +10079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5CDBE3-750C-4C0D-8AAF-43745D6A6F72}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:A126"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="39.75">
-      <c r="A13" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="22.5">
-      <c r="A17" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="22.5">
-      <c r="A26" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="22.5">
-      <c r="A34" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="22.5">
-      <c r="A42" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="39.75">
-      <c r="A51" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" ht="30">
-      <c r="A53" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" ht="30">
-      <c r="A61" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="3"/>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" ht="30">
-      <c r="A84" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" ht="30">
-      <c r="A91" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" ht="30">
-      <c r="A105" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F76542-7475-450B-8480-EFB6EF4C355E}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:A61"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="39.75">
-      <c r="A7" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="30">
-      <c r="A16" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="30">
-      <c r="A28" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" ht="30">
-      <c r="A40" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="30">
-      <c r="A54" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E709E9D4-AB6E-4CC2-8E0F-A5793B336BEE}">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:A149"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="1" spans="1:1" ht="39.75">
-      <c r="A1" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="30">
-      <c r="A3" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="30">
-      <c r="A27" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" ht="30">
-      <c r="A46" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" ht="30">
-      <c r="A60" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="39.75">
-      <c r="A69" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" ht="30">
-      <c r="A75" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" ht="30">
-      <c r="A76" s="5"/>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" ht="39.75">
-      <c r="A81" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" ht="30">
-      <c r="A90" s="5"/>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" ht="30">
-      <c r="A114" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5098A92-C5C0-4353-AB1F-30D7DE2F67BE}">
-  <sheetPr codeName="Sheet4"/>
-  <dimension ref="A2:I93"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="2" spans="1:9" ht="39.75">
-      <c r="A2" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="30">
-      <c r="A4" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="39.75">
-      <c r="A9" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="39.75">
-      <c r="A15" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="I18" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="I19" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="I20" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="30">
-      <c r="A21" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" ht="30">
-      <c r="A71" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626DB163-BD8B-468F-83A9-4D70FEBCA709}">
-  <sheetPr codeName="Sheet5"/>
-  <dimension ref="A3:A124"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="25.5">
-      <c r="A11" s="8" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="25.5">
-      <c r="A24" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="7" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" ht="25.5">
-      <c r="A38" s="8"/>
-    </row>
-    <row r="39" spans="1:1" ht="25.5">
-      <c r="A39" s="9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="10" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="11" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="3"/>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="3"/>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="3"/>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="3" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="3"/>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="3"/>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="17" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="2"/>
-    </row>
-    <row r="112" spans="1:1" ht="26.25">
-      <c r="A112" s="12" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="13" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="16" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="13"/>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="15" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" ht="26.25">
-      <c r="A117" s="12" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="14" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="13"/>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="13"/>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3"/>
-  <hyperlinks>
-    <hyperlink ref="A118" r:id="rId1" location="fn-1" display="https://qiita.com/sskre/items/0bd048744ea2f830682e - fn-1" xr:uid="{047BE0B8-9A0D-4A1E-802F-7EEE2BF06DA7}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA8CB5A-8AF9-428F-BF72-A4650EA2714E}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:B108"/>
@@ -11837,10 +10330,10 @@
       </c>
     </row>
     <row r="68" spans="1:2" ht="234" customHeight="1">
-      <c r="A68" s="44" t="s">
+      <c r="A68" s="48" t="s">
         <v>448</v>
       </c>
-      <c r="B68" s="44"/>
+      <c r="B68" s="48"/>
     </row>
     <row r="69" spans="1:2" ht="164.25" customHeight="1">
       <c r="A69" s="32" t="s">
@@ -12006,7 +10499,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED49263E-B0E6-4B40-8C98-8489AC780DBF}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C219"/>
@@ -12586,4 +11079,2582 @@
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52820001-5FDD-4FE0-88DB-40598CB6E06D}">
+  <dimension ref="A1:A22"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A933EA-8619-44FF-B324-B22BEE6396FB}">
+  <dimension ref="A1:I75"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
+    <col min="2" max="2" width="25.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="21" t="s">
+        <v>629</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="35" t="s">
+        <v>621</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>622</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="41" t="s">
+        <v>643</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="41" t="s">
+        <v>644</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>645</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>646</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="35" t="s">
+        <v>647</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>623</v>
+      </c>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>624</v>
+      </c>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="19" t="s">
+        <v>625</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>626</v>
+      </c>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+    </row>
+    <row r="21" spans="1:9" ht="37.5">
+      <c r="A21" s="19" t="s">
+        <v>627</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>628</v>
+      </c>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+    </row>
+    <row r="23" spans="1:9" ht="39.75">
+      <c r="A23" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="18" t="s">
+        <v>631</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="19" t="s">
+        <v>633</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="19" t="s">
+        <v>625</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="19" t="s">
+        <v>636</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="39.75">
+      <c r="A30" s="1" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="22.5">
+      <c r="A32" s="4" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="22.5">
+      <c r="A36" s="4" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="39.75">
+      <c r="A47" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="3"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="3" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="3" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="3" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="30">
+      <c r="A57" s="5" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="3"/>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="3" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="3" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="3" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="3" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="39.75">
+      <c r="A68" s="1" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="3"/>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="3" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="3" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="3" t="s">
+        <v>673</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A6B54C0-84BD-40BC-AEE9-70FBD3941C49}">
+  <dimension ref="A2:A9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="42" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="42" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="42" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="42" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="42" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="42" t="s">
+        <v>680</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5CDBE3-750C-4C0D-8AAF-43745D6A6F72}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:A126"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="39.75">
+      <c r="A13" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="22.5">
+      <c r="A17" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="22.5">
+      <c r="A26" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="22.5">
+      <c r="A34" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="22.5">
+      <c r="A42" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="39.75">
+      <c r="A51" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="30">
+      <c r="A53" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="30">
+      <c r="A61" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="3"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="30">
+      <c r="A84" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="30">
+      <c r="A91" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="30">
+      <c r="A105" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F76542-7475-450B-8480-EFB6EF4C355E}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:A61"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="39.75">
+      <c r="A7" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="30">
+      <c r="A16" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="30">
+      <c r="A28" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="30">
+      <c r="A40" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="30">
+      <c r="A54" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E709E9D4-AB6E-4CC2-8E0F-A5793B336BEE}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:A149"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="39.75">
+      <c r="A1" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="30">
+      <c r="A3" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="30">
+      <c r="A27" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="30">
+      <c r="A46" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="30">
+      <c r="A60" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="39.75">
+      <c r="A69" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="30">
+      <c r="A75" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="30">
+      <c r="A76" s="5"/>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="39.75">
+      <c r="A81" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="30">
+      <c r="A90" s="5"/>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="30">
+      <c r="A114" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5098A92-C5C0-4353-AB1F-30D7DE2F67BE}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A2:I93"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="1:9" ht="39.75">
+      <c r="A2" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="30">
+      <c r="A4" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="39.75">
+      <c r="A9" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="39.75">
+      <c r="A15" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="I18" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="I19" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="I20" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="30">
+      <c r="A21" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="30">
+      <c r="A71" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626DB163-BD8B-468F-83A9-4D70FEBCA709}">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A2:A124"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="10" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="25.5">
+      <c r="A11" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="25.5">
+      <c r="A24" s="8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="25.5">
+      <c r="A38" s="8"/>
+    </row>
+    <row r="39" spans="1:1" ht="25.5">
+      <c r="A39" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="11" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="3"/>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="3"/>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="3"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="3"/>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="3"/>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="17" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="2"/>
+    </row>
+    <row r="112" spans="1:1" ht="26.25">
+      <c r="A112" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="13" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="16" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="13"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="26.25">
+      <c r="A117" s="12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="13"/>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="13"/>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <hyperlinks>
+    <hyperlink ref="A118" r:id="rId1" location="fn-1" display="https://qiita.com/sskre/items/0bd048744ea2f830682e - fn-1" xr:uid="{047BE0B8-9A0D-4A1E-802F-7EEE2BF06DA7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/実装メモ.xlsx
+++ b/実装メモ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\docker_cms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE810CB-774A-46CF-84F0-E05D9D725BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD68C19-7D8A-4558-B9BB-0DD195EBE502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
   </bookViews>
   <sheets>
     <sheet name="構成図" sheetId="9" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="704">
   <si>
     <t>Route::get('/survey/{id}', [SurveyController::class, 'show']);</t>
   </si>
@@ -3010,9 +3010,6 @@
     <phoneticPr fontId="34"/>
   </si>
   <si>
-    <t>php artisan make:migration add_vote_id_to_survey_comments_table</t>
-  </si>
-  <si>
     <t>public function up()</t>
   </si>
   <si>
@@ -3045,6 +3042,82 @@
       <t>ヘンコウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>php artisan make:migration add_vote_id_to_survey_comments_table</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>フロント共通のヘッダに組み込まれる共通CSSのリンクや定義などがある</t>
+    <rPh sb="4" eb="6">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>resources\views\filament\resources\survey-resource\pages\view-survey-results.blade.php</t>
+  </si>
+  <si>
+    <t>↑実際は</t>
+    <rPh sb="1" eb="3">
+      <t>ジッサイ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>app\Filament\Resources\SurveyResource\Pages\ViewSurveyResults.php</t>
+  </si>
+  <si>
+    <t>の表示</t>
+    <rPh sb="1" eb="3">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>データ元</t>
+    <rPh sb="3" eb="4">
+      <t>モト</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>アンケート結果画面のデータ抽出</t>
+    <rPh sb="5" eb="7">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>チュウシュツ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>のresultの内容や順番を作成</t>
+    <rPh sb="8" eb="10">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
   </si>
 </sst>
 </file>
@@ -3613,6 +3686,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3627,6 +3707,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3635,20 +3722,6 @@
       <fill>
         <patternFill>
           <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3676,6 +3749,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3683,6 +3763,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3690,6 +3777,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3711,6 +3805,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3753,6 +3854,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3760,6 +3875,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3781,6 +3910,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3809,6 +3945,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3830,6 +3973,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -3970,6 +4120,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4005,6 +4162,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4019,6 +4183,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4061,6 +4232,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4103,6 +4281,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4208,6 +4393,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4215,6 +4407,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4243,6 +4442,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4271,6 +4477,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4327,6 +4540,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4376,6 +4596,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4565,6 +4792,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4614,6 +4848,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4670,6 +4911,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4677,6 +4925,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4733,6 +4988,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4761,6 +5023,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4782,6 +5051,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -4852,6 +5142,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -4860,230 +5157,6 @@
       <fill>
         <patternFill>
           <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5425,7 +5498,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13CDE890-F993-425A-B129-8B17D7811949}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:X458"/>
+  <dimension ref="A1:AG458"/>
   <sheetFormatPr defaultColWidth="4.375" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.375" style="38" customWidth="1"/>
@@ -6191,7 +6264,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:33">
       <c r="A33" s="34"/>
       <c r="B33" s="35" t="s">
         <v>474</v>
@@ -6212,7 +6285,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:33">
       <c r="A34" s="34"/>
       <c r="B34" s="35" t="s">
         <v>474</v>
@@ -6227,7 +6300,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:33">
       <c r="A35" s="34"/>
       <c r="B35" s="35" t="s">
         <v>474</v>
@@ -6245,7 +6318,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:33">
       <c r="A36" s="34"/>
       <c r="B36" s="35" t="s">
         <v>474</v>
@@ -6266,7 +6339,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:33">
       <c r="A37" s="34"/>
       <c r="B37" s="35" t="s">
         <v>474</v>
@@ -6287,7 +6360,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:33">
       <c r="A38" s="34"/>
       <c r="B38" s="35" t="s">
         <v>474</v>
@@ -6308,7 +6381,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:33">
       <c r="A39" s="34"/>
       <c r="B39" s="35" t="s">
         <v>474</v>
@@ -6325,11 +6398,17 @@
       <c r="G39" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="H39" s="35" t="s">
+      <c r="H39" s="39" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="Y39" s="35" t="s">
+        <v>702</v>
+      </c>
+      <c r="AG39" s="35" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33">
       <c r="A40" s="34"/>
       <c r="B40" s="35" t="s">
         <v>474</v>
@@ -6343,8 +6422,11 @@
       <c r="F40" s="35" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="AG40" s="35" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33">
       <c r="A41" s="34"/>
       <c r="B41" s="35" t="s">
         <v>474</v>
@@ -6362,7 +6444,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:33">
       <c r="A42" s="34"/>
       <c r="B42" s="35" t="s">
         <v>474</v>
@@ -6383,7 +6465,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:33">
       <c r="A43" s="34"/>
       <c r="B43" s="35" t="s">
         <v>474</v>
@@ -6404,7 +6486,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:33">
       <c r="A44" s="34"/>
       <c r="B44" s="35" t="s">
         <v>474</v>
@@ -6425,7 +6507,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:33">
       <c r="A45" s="34"/>
       <c r="B45" s="35" t="s">
         <v>474</v>
@@ -6440,7 +6522,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:33">
       <c r="A46" s="34"/>
       <c r="B46" s="35" t="s">
         <v>474</v>
@@ -6458,7 +6540,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:33">
       <c r="A47" s="34"/>
       <c r="B47" s="35" t="s">
         <v>474</v>
@@ -6479,7 +6561,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:33">
       <c r="A48" s="34"/>
       <c r="B48" s="35" t="s">
         <v>474</v>
@@ -6500,7 +6582,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:32">
       <c r="A49" s="34"/>
       <c r="B49" s="35" t="s">
         <v>474</v>
@@ -6521,7 +6603,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:32">
       <c r="A50" s="34"/>
       <c r="B50" s="35" t="s">
         <v>474</v>
@@ -6536,7 +6618,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:32">
       <c r="A51" s="34"/>
       <c r="B51" s="35" t="s">
         <v>474</v>
@@ -6554,7 +6636,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:32">
       <c r="A52" s="34"/>
       <c r="B52" s="35" t="s">
         <v>474</v>
@@ -6578,7 +6660,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:32">
       <c r="A53" s="34"/>
       <c r="B53" s="35" t="s">
         <v>474</v>
@@ -6592,8 +6674,14 @@
       <c r="F53" s="40" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="54" spans="1:19">
+      <c r="AC53" s="35" t="s">
+        <v>698</v>
+      </c>
+      <c r="AF53" s="35" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="54" spans="1:32">
       <c r="A54" s="34"/>
       <c r="B54" s="35" t="s">
         <v>474</v>
@@ -6608,7 +6696,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:32">
       <c r="A55" s="34"/>
       <c r="B55" s="35" t="s">
         <v>474</v>
@@ -6623,7 +6711,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:32">
       <c r="A56" s="34"/>
       <c r="B56" s="35" t="s">
         <v>474</v>
@@ -6638,7 +6726,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:32">
       <c r="A57" s="34"/>
       <c r="B57" s="35" t="s">
         <v>474</v>
@@ -6653,7 +6741,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:32">
       <c r="A58" s="34"/>
       <c r="B58" s="35" t="s">
         <v>474</v>
@@ -6668,7 +6756,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:32">
       <c r="A59" s="34"/>
       <c r="B59" s="35" t="s">
         <v>474</v>
@@ -6683,7 +6771,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:32">
       <c r="A60" s="34"/>
       <c r="B60" s="35" t="s">
         <v>474</v>
@@ -6698,7 +6786,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:32">
       <c r="A61" s="34"/>
       <c r="B61" s="35" t="s">
         <v>474</v>
@@ -6711,7 +6799,7 @@
       </c>
       <c r="F61" s="40"/>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:32">
       <c r="A62" s="34"/>
       <c r="B62" s="35" t="s">
         <v>474</v>
@@ -6729,7 +6817,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:32">
       <c r="A63" s="34"/>
       <c r="B63" s="35" t="s">
         <v>474</v>
@@ -6739,7 +6827,7 @@
       </c>
       <c r="F63" s="40"/>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:32">
       <c r="A64" s="34"/>
       <c r="B64" s="35" t="s">
         <v>474</v>
@@ -7901,7 +7989,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="145" spans="1:19">
+    <row r="145" spans="1:31">
       <c r="A145" s="34"/>
       <c r="B145" s="35" t="s">
         <v>474</v>
@@ -7925,7 +8013,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="146" spans="1:19">
+    <row r="146" spans="1:31">
       <c r="A146" s="34"/>
       <c r="B146" s="35" t="s">
         <v>474</v>
@@ -7954,8 +8042,17 @@
       <c r="S146" s="35" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="147" spans="1:19">
+      <c r="AA146" s="35" t="s">
+        <v>700</v>
+      </c>
+      <c r="AC146" s="35" t="s">
+        <v>701</v>
+      </c>
+      <c r="AE146" s="35" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="147" spans="1:31">
       <c r="A147" s="34"/>
       <c r="B147" s="35" t="s">
         <v>474</v>
@@ -7970,7 +8067,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="148" spans="1:19">
+    <row r="148" spans="1:31">
       <c r="A148" s="34"/>
       <c r="B148" s="35" t="s">
         <v>474</v>
@@ -7984,11 +8081,14 @@
       <c r="E148" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="F148" s="35" t="s">
+      <c r="F148" s="39" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="149" spans="1:19">
+      <c r="S148" s="35" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="149" spans="1:31">
       <c r="A149" s="34"/>
       <c r="B149" s="35" t="s">
         <v>474</v>
@@ -8006,7 +8106,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="150" spans="1:19">
+    <row r="150" spans="1:31">
       <c r="A150" s="34"/>
       <c r="B150" s="35" t="s">
         <v>474</v>
@@ -8018,7 +8118,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="151" spans="1:19">
+    <row r="151" spans="1:31">
       <c r="A151" s="34"/>
       <c r="B151" s="35" t="s">
         <v>474</v>
@@ -8036,7 +8136,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="152" spans="1:19">
+    <row r="152" spans="1:31">
       <c r="A152" s="34"/>
       <c r="B152" s="35" t="s">
         <v>474</v>
@@ -8045,7 +8145,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="153" spans="1:19">
+    <row r="153" spans="1:31">
       <c r="A153" s="34"/>
       <c r="B153" s="35" t="s">
         <v>474</v>
@@ -8054,7 +8154,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="154" spans="1:19">
+    <row r="154" spans="1:31">
       <c r="A154" s="34"/>
       <c r="B154" s="35" t="s">
         <v>474</v>
@@ -8069,7 +8169,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="155" spans="1:19">
+    <row r="155" spans="1:31">
       <c r="A155" s="34"/>
       <c r="B155" s="35" t="s">
         <v>474</v>
@@ -8087,7 +8187,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="156" spans="1:19">
+    <row r="156" spans="1:31">
       <c r="A156" s="34"/>
       <c r="B156" s="35" t="s">
         <v>474</v>
@@ -8105,7 +8205,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="157" spans="1:19">
+    <row r="157" spans="1:31">
       <c r="A157" s="34"/>
       <c r="B157" s="35" t="s">
         <v>474</v>
@@ -8120,7 +8220,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="158" spans="1:19">
+    <row r="158" spans="1:31">
       <c r="A158" s="34"/>
       <c r="B158" s="35" t="s">
         <v>474</v>
@@ -8138,7 +8238,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="159" spans="1:19">
+    <row r="159" spans="1:31">
       <c r="A159" s="34"/>
       <c r="B159" s="35" t="s">
         <v>474</v>
@@ -8156,7 +8256,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="160" spans="1:19">
+    <row r="160" spans="1:31">
       <c r="A160" s="34"/>
       <c r="B160" s="35" t="s">
         <v>474</v>
@@ -9368,11 +9468,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A191:A192 A194 A200">
-    <cfRule type="expression" dxfId="213" priority="1233" stopIfTrue="1">
+    <cfRule type="expression" dxfId="213" priority="1224" stopIfTrue="1">
+      <formula>OR($B172="├─",$B172="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="212" priority="1225" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="212" priority="1224" stopIfTrue="1">
-      <formula>OR($B172="├─",$B172="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="211" priority="1226" stopIfTrue="1">
       <formula>OR($B172="├─",$B172="└─")</formula>
@@ -9389,14 +9489,14 @@
     <cfRule type="expression" dxfId="207" priority="1230" stopIfTrue="1">
       <formula>OR($B172="├─",$B172="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="206" priority="1225" stopIfTrue="1">
+    <cfRule type="expression" dxfId="206" priority="1231" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="205" priority="1231" stopIfTrue="1">
+    <cfRule type="expression" dxfId="205" priority="1232" stopIfTrue="1">
+      <formula>OR($B172="├─",$B172="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="204" priority="1233" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="204" priority="1232" stopIfTrue="1">
-      <formula>OR($B172="├─",$B172="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="203" priority="1234" stopIfTrue="1">
       <formula>OR($B172="├─",$B172="└─")</formula>
@@ -9406,11 +9506,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A191:A192 A194:A195 A197:A204">
-    <cfRule type="expression" dxfId="201" priority="1237" stopIfTrue="1">
+    <cfRule type="expression" dxfId="201" priority="1236" stopIfTrue="1">
+      <formula>OR($B172="├─",$B172="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="200" priority="1237" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="200" priority="1236" stopIfTrue="1">
-      <formula>OR($B172="├─",$B172="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A195 A197:A204">
@@ -9419,105 +9519,105 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A195 A203:A204">
-    <cfRule type="expression" dxfId="198" priority="1335" stopIfTrue="1">
+    <cfRule type="expression" dxfId="198" priority="1333" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="197" priority="1336" stopIfTrue="1">
+    <cfRule type="expression" dxfId="197" priority="1334" stopIfTrue="1">
       <formula>OR($B176="├─",$B176="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="196" priority="1337" stopIfTrue="1">
+    <cfRule type="expression" dxfId="196" priority="1335" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="195" priority="1338" stopIfTrue="1">
+    <cfRule type="expression" dxfId="195" priority="1336" stopIfTrue="1">
       <formula>OR($B176="├─",$B176="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="194" priority="1339" stopIfTrue="1">
+    <cfRule type="expression" dxfId="194" priority="1337" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="193" priority="1340" stopIfTrue="1">
+    <cfRule type="expression" dxfId="193" priority="1338" stopIfTrue="1">
       <formula>OR($B176="├─",$B176="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="192" priority="1341" stopIfTrue="1">
+    <cfRule type="expression" dxfId="192" priority="1339" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="191" priority="1342" stopIfTrue="1">
+    <cfRule type="expression" dxfId="191" priority="1340" stopIfTrue="1">
       <formula>OR($B176="├─",$B176="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="190" priority="1333" stopIfTrue="1">
+    <cfRule type="expression" dxfId="190" priority="1341" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="189" priority="1334" stopIfTrue="1">
+    <cfRule type="expression" dxfId="189" priority="1342" stopIfTrue="1">
       <formula>OR($B176="├─",$B176="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A195">
-    <cfRule type="expression" dxfId="188" priority="1345" stopIfTrue="1">
+    <cfRule type="expression" dxfId="188" priority="1344" stopIfTrue="1">
+      <formula>OR($B176="├─",$B176="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="187" priority="1345" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="187" priority="1344" stopIfTrue="1">
-      <formula>OR($B176="├─",$B176="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A199">
-    <cfRule type="expression" dxfId="186" priority="1409" stopIfTrue="1">
+    <cfRule type="expression" dxfId="186" priority="1392" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="185" priority="1393" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="1410" stopIfTrue="1">
+    <cfRule type="expression" dxfId="184" priority="1394" stopIfTrue="1">
       <formula>OR($B180="├─",$B180="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="1392" stopIfTrue="1">
+    <cfRule type="expression" dxfId="183" priority="1395" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="182" priority="1396" stopIfTrue="1">
       <formula>OR($B180="├─",$B180="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="183" priority="1411" stopIfTrue="1">
+    <cfRule type="expression" dxfId="181" priority="1397" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="182" priority="1395" stopIfTrue="1">
+    <cfRule type="expression" dxfId="180" priority="1398" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="179" priority="1399" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="1396" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="1400" stopIfTrue="1">
       <formula>OR($B180="├─",$B180="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="180" priority="1393" stopIfTrue="1">
+    <cfRule type="expression" dxfId="177" priority="1401" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="179" priority="1397" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="1402" stopIfTrue="1">
+      <formula>OR($B180="├─",$B180="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="175" priority="1403" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="178" priority="1398" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="1404" stopIfTrue="1">
       <formula>OR($B180="├─",$B180="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="1399" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="1405" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="1400" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="1406" stopIfTrue="1">
       <formula>OR($B180="├─",$B180="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="175" priority="1401" stopIfTrue="1">
+    <cfRule type="expression" dxfId="171" priority="1407" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="1402" stopIfTrue="1">
+    <cfRule type="expression" dxfId="170" priority="1408" stopIfTrue="1">
       <formula>OR($B180="├─",$B180="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="1403" stopIfTrue="1">
+    <cfRule type="expression" dxfId="169" priority="1409" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="1404" stopIfTrue="1">
+    <cfRule type="expression" dxfId="168" priority="1410" stopIfTrue="1">
       <formula>OR($B180="├─",$B180="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="171" priority="1405" stopIfTrue="1">
+    <cfRule type="expression" dxfId="167" priority="1411" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="170" priority="1394" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="169" priority="1406" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="168" priority="1407" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="167" priority="1408" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A199:A200">
@@ -9561,53 +9661,53 @@
     <cfRule type="expression" dxfId="155" priority="1505" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="154" priority="1507" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="1506" stopIfTrue="1">
+      <formula>OR($B182="├─",$B182="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="153" priority="1507" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="1509" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="1508" stopIfTrue="1">
+      <formula>OR($B182="├─",$B182="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="151" priority="1509" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="152" priority="1510" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="1510" stopIfTrue="1">
       <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="151" priority="1511" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="1511" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="1512" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="1512" stopIfTrue="1">
       <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="1513" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="1513" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="1514" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="1514" stopIfTrue="1">
       <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="147" priority="1515" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="1515" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="1508" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="1516" stopIfTrue="1">
       <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="1516" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="1517" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="142" priority="1518" stopIfTrue="1">
       <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="1517" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="1519" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="143" priority="1518" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="1520" stopIfTrue="1">
       <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="1519" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="1521" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="141" priority="1520" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="140" priority="1521" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="139" priority="1506" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A203">
@@ -9693,169 +9793,169 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A204">
-    <cfRule type="expression" dxfId="112" priority="1654" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="1650" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="111" priority="1670" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="1651" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="110" priority="1652" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="1671" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="1653" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="1672" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="1654" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="1673" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="1655" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="1674" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="1656" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="1675" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="1657" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="1684" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="1658" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="1676" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="1659" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="1660" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="1677" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="1661" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="1678" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="1662" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="1679" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="1663" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="1680" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="1664" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="1681" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="1665" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="1682" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="1666" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="1683" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="1667" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="1689" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="1668" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="93" priority="1669" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="95" priority="1688" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="1670" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="1687" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="1671" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="1686" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="1672" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="1650" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="1673" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="1674" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="1651" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="1675" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="1652" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="1676" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="1653" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="1677" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="1685" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="1678" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="1679" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="1655" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="1680" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="1681" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="1656" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="1682" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="1657" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="1683" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="1658" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="1684" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="1659" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="1685" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="1660" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="1686" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="1661" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="1687" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="1662" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="1688" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="1663" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="1664" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="1665" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="1666" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="1667" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="74" priority="1668" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="1669" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="1689" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A204:A205">
-    <cfRule type="expression" dxfId="72" priority="1745" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="1732" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="1733" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="1744" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="1734" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="1743" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="1735" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="1742" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="1736" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="1741" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="1737" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="1740" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="66" priority="1738" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="1737" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="1739" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="1736" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="1740" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="1735" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="1741" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="1734" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="1742" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="1733" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="1743" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="1739" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="1744" stopIfTrue="1">
+      <formula>OR($B185="├─",$B185="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="1745" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="1732" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="58" priority="1746" stopIfTrue="1">
       <formula>OR($B185="├─",$B185="└─")</formula>
@@ -9871,68 +9971,68 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A205">
-    <cfRule type="expression" dxfId="54" priority="1788" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="1768" stopIfTrue="1">
       <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="1768" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="1769" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="1770" stopIfTrue="1">
       <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="1769" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="1771" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="1770" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="1772" stopIfTrue="1">
       <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="1771" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="1773" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="1772" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="1774" stopIfTrue="1">
       <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="1773" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="1775" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="1774" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="1776" stopIfTrue="1">
       <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="1775" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="1777" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="1776" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="1778" stopIfTrue="1">
       <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="1777" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="1779" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="1778" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="1780" stopIfTrue="1">
       <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="1779" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="1781" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="1780" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="1782" stopIfTrue="1">
       <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="1781" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="1783" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="1782" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="1784" stopIfTrue="1">
       <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="1783" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="1785" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="1784" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="1786" stopIfTrue="1">
       <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="1785" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="1787" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="1786" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="1788" stopIfTrue="1">
       <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="1787" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="33" priority="1789" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
@@ -9950,11 +10050,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A207">
-    <cfRule type="expression" dxfId="29" priority="1364" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="1363" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="1364" stopIfTrue="1">
       <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="1363" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A210:A458">
@@ -9990,17 +10090,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220:C222">
-    <cfRule type="expression" dxfId="19" priority="824" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="819" stopIfTrue="1">
+      <formula>OR($B220="├─",$B220="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="820" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="823" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="823" stopIfTrue="1">
       <formula>OR($B220="├─",$B220="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="820" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="824" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="819" stopIfTrue="1">
-      <formula>OR($B220="├─",$B220="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B190:E190 A190:A458">
@@ -10014,11 +10114,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:R1 T1:X1 A1:A3 S1:S3 B3:R3 T3:X3 A4:X100 A101:AN101 A102:X150 A151:R151 A152:X158 A159:R159 A160:X189">
-    <cfRule type="expression" dxfId="13" priority="802" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="801" stopIfTrue="1">
+      <formula>OR($B1="├─",$B1="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="802" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="801" stopIfTrue="1">
-      <formula>OR($B1="├─",$B1="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F205:F436">
@@ -10035,11 +10135,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K190:X204 G205:X433">
-    <cfRule type="expression" dxfId="8" priority="376" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="375" stopIfTrue="1">
+      <formula>OR($B206="├─",$B206="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="376" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="375" stopIfTrue="1">
-      <formula>OR($B206="├─",$B206="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S159:X159">
@@ -10051,11 +10151,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y98:Z98">
-    <cfRule type="expression" dxfId="4" priority="356" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="355" stopIfTrue="1">
+      <formula>OR($B144="├─",$B144="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="356" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="355" stopIfTrue="1">
-      <formula>OR($B144="├─",$B144="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y68:AK68 B202:C203 B205:C206 B211:C224">
@@ -11088,12 +11188,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -11103,7 +11203,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -11113,27 +11213,27 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -11148,7 +11248,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -11158,17 +11258,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="21" spans="1:1">

--- a/実装メモ.xlsx
+++ b/実装メモ.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\docker_cms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD68C19-7D8A-4558-B9BB-0DD195EBE502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CC976B-DDE6-4908-8C03-2D7591037F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
   </bookViews>
   <sheets>
     <sheet name="構成図" sheetId="9" r:id="rId1"/>
-    <sheet name="投票コメントテーブルに投票IDを加える変更" sheetId="12" r:id="rId2"/>
-    <sheet name="入力チェック(Livewire)" sheetId="10" r:id="rId3"/>
-    <sheet name="エラー文言" sheetId="11" r:id="rId4"/>
-    <sheet name="アンケート機能_概要" sheetId="2" r:id="rId5"/>
-    <sheet name="アンケート機能_マイグレーション" sheetId="3" r:id="rId6"/>
-    <sheet name="アンケート機能_model" sheetId="4" r:id="rId7"/>
-    <sheet name="アンケート機能_フロント" sheetId="5" r:id="rId8"/>
-    <sheet name="番外編" sheetId="6" r:id="rId9"/>
-    <sheet name="アンケート結果_管理画面" sheetId="7" r:id="rId10"/>
-    <sheet name="filmentの構造に関する疑問" sheetId="8" r:id="rId11"/>
+    <sheet name="ファイルのアップロード" sheetId="13" r:id="rId2"/>
+    <sheet name="投票コメントテーブルに投票IDを加える変更" sheetId="12" r:id="rId3"/>
+    <sheet name="入力チェック(Livewire)" sheetId="10" r:id="rId4"/>
+    <sheet name="エラー文言" sheetId="11" r:id="rId5"/>
+    <sheet name="アンケート機能_概要" sheetId="2" r:id="rId6"/>
+    <sheet name="アンケート機能_マイグレーション" sheetId="3" r:id="rId7"/>
+    <sheet name="アンケート機能_model" sheetId="4" r:id="rId8"/>
+    <sheet name="アンケート機能_フロント" sheetId="5" r:id="rId9"/>
+    <sheet name="番外編" sheetId="6" r:id="rId10"/>
+    <sheet name="アンケート結果_管理画面" sheetId="7" r:id="rId11"/>
+    <sheet name="filmentの構造に関する疑問" sheetId="8" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="716">
   <si>
     <t>Route::get('/survey/{id}', [SurveyController::class, 'show']);</t>
   </si>
@@ -3119,12 +3120,91 @@
     </rPh>
     <phoneticPr fontId="34"/>
   </si>
+  <si>
+    <t>survey</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>expired.blade.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>アンケート終了時の表示。</t>
+    <rPh sb="5" eb="8">
+      <t>シュウリョウジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>app\http\SurveyContoller で 判定させて表示する。</t>
+    <rPh sb="27" eb="29">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <r>
+      <t>           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8B949E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>// 期限切れチェック</t>
+    </r>
+  </si>
+  <si>
+    <t>    }</t>
+  </si>
+  <si>
+    <t>    if ($survey-&gt;expires_at &amp;&amp; now()-&gt;gt($survey-&gt;expires_at)) {</t>
+  </si>
+  <si>
+    <t>        return view('survey.expired', compact('survey'));</t>
+  </si>
+  <si>
+    <t>アンケート編集画面の詳細なPG</t>
+    <rPh sb="5" eb="9">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>filmentからのファイルアップロード</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>前提として</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>config/filesystems.php に定義が必要</t>
+    <rPh sb="27" eb="29">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3409,6 +3489,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3418,7 +3504,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -3507,6 +3593,77 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3519,7 +3676,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3655,6 +3812,24 @@
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -5498,7 +5673,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13CDE890-F993-425A-B129-8B17D7811949}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AG458"/>
+  <dimension ref="A1:BA460"/>
   <sheetFormatPr defaultColWidth="4.375" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.375" style="38" customWidth="1"/>
@@ -6356,8 +6531,11 @@
       <c r="G37" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="H37" s="35" t="s">
+      <c r="H37" s="39" t="s">
         <v>544</v>
+      </c>
+      <c r="Y37" s="35" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="38" spans="1:33">
@@ -7989,7 +8167,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="145" spans="1:31">
+    <row r="145" spans="1:53">
       <c r="A145" s="34"/>
       <c r="B145" s="35" t="s">
         <v>474</v>
@@ -8013,7 +8191,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="146" spans="1:31">
+    <row r="146" spans="1:53">
       <c r="A146" s="34"/>
       <c r="B146" s="35" t="s">
         <v>474</v>
@@ -8052,7 +8230,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="147" spans="1:31">
+    <row r="147" spans="1:53">
       <c r="A147" s="34"/>
       <c r="B147" s="35" t="s">
         <v>474</v>
@@ -8067,7 +8245,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="148" spans="1:31">
+    <row r="148" spans="1:53">
       <c r="A148" s="34"/>
       <c r="B148" s="35" t="s">
         <v>474</v>
@@ -8088,7 +8266,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="149" spans="1:31">
+    <row r="149" spans="1:53">
       <c r="A149" s="34"/>
       <c r="B149" s="35" t="s">
         <v>474</v>
@@ -8106,7 +8284,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="150" spans="1:31">
+    <row r="150" spans="1:53">
       <c r="A150" s="34"/>
       <c r="B150" s="35" t="s">
         <v>474</v>
@@ -8118,7 +8296,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="151" spans="1:31">
+    <row r="151" spans="1:53">
       <c r="A151" s="34"/>
       <c r="B151" s="35" t="s">
         <v>474</v>
@@ -8136,7 +8314,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="152" spans="1:31">
+    <row r="152" spans="1:53">
       <c r="A152" s="34"/>
       <c r="B152" s="35" t="s">
         <v>474</v>
@@ -8145,7 +8323,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="153" spans="1:31">
+    <row r="153" spans="1:53">
       <c r="A153" s="34"/>
       <c r="B153" s="35" t="s">
         <v>474</v>
@@ -8154,7 +8332,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="154" spans="1:31">
+    <row r="154" spans="1:53">
       <c r="A154" s="34"/>
       <c r="B154" s="35" t="s">
         <v>474</v>
@@ -8169,7 +8347,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="155" spans="1:31">
+    <row r="155" spans="1:53">
       <c r="A155" s="34"/>
       <c r="B155" s="35" t="s">
         <v>474</v>
@@ -8187,7 +8365,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="156" spans="1:31">
+    <row r="156" spans="1:53">
       <c r="A156" s="34"/>
       <c r="B156" s="35" t="s">
         <v>474</v>
@@ -8205,7 +8383,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="157" spans="1:31">
+    <row r="157" spans="1:53" ht="19.5" thickBot="1">
       <c r="A157" s="34"/>
       <c r="B157" s="35" t="s">
         <v>474</v>
@@ -8220,7 +8398,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="158" spans="1:31">
+    <row r="158" spans="1:53">
       <c r="A158" s="34"/>
       <c r="B158" s="35" t="s">
         <v>474</v>
@@ -8237,8 +8415,25 @@
       <c r="F158" s="35" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="159" spans="1:31">
+      <c r="AK158" s="49"/>
+      <c r="AL158" s="37"/>
+      <c r="AM158" s="37"/>
+      <c r="AN158" s="37"/>
+      <c r="AO158" s="37"/>
+      <c r="AP158" s="37"/>
+      <c r="AQ158" s="37"/>
+      <c r="AR158" s="37"/>
+      <c r="AS158" s="37"/>
+      <c r="AT158" s="37"/>
+      <c r="AU158" s="37"/>
+      <c r="AV158" s="37"/>
+      <c r="AW158" s="37"/>
+      <c r="AX158" s="37"/>
+      <c r="AY158" s="37"/>
+      <c r="AZ158" s="37"/>
+      <c r="BA158" s="50"/>
+    </row>
+    <row r="159" spans="1:53">
       <c r="A159" s="34"/>
       <c r="B159" s="35" t="s">
         <v>474</v>
@@ -8249,14 +8444,30 @@
       <c r="D159" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="E159" s="39" t="s">
-        <v>613</v>
-      </c>
-      <c r="S159" s="35" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="160" spans="1:31">
+      <c r="E159" s="35" t="s">
+        <v>704</v>
+      </c>
+      <c r="AK159" s="51"/>
+      <c r="AL159" s="52" t="s">
+        <v>708</v>
+      </c>
+      <c r="AM159" s="53"/>
+      <c r="AN159" s="53"/>
+      <c r="AO159" s="53"/>
+      <c r="AP159" s="53"/>
+      <c r="AQ159" s="53"/>
+      <c r="AR159" s="53"/>
+      <c r="AS159" s="53"/>
+      <c r="AT159" s="53"/>
+      <c r="AU159" s="53"/>
+      <c r="AV159" s="53"/>
+      <c r="AW159" s="53"/>
+      <c r="AX159" s="53"/>
+      <c r="AY159" s="53"/>
+      <c r="AZ159" s="53"/>
+      <c r="BA159" s="54"/>
+    </row>
+    <row r="160" spans="1:53">
       <c r="A160" s="34"/>
       <c r="B160" s="35" t="s">
         <v>474</v>
@@ -8265,13 +8476,41 @@
         <v>477</v>
       </c>
       <c r="D160" s="35" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E160" s="35" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
+        <v>476</v>
+      </c>
+      <c r="F160" s="35" t="s">
+        <v>705</v>
+      </c>
+      <c r="S160" s="35" t="s">
+        <v>706</v>
+      </c>
+      <c r="Z160" s="35" t="s">
+        <v>707</v>
+      </c>
+      <c r="AK160" s="51"/>
+      <c r="AL160" s="57" t="s">
+        <v>710</v>
+      </c>
+      <c r="AM160" s="58"/>
+      <c r="AN160" s="58"/>
+      <c r="AO160" s="58"/>
+      <c r="AP160" s="58"/>
+      <c r="AQ160" s="58"/>
+      <c r="AR160" s="58"/>
+      <c r="AS160" s="58"/>
+      <c r="AT160" s="58"/>
+      <c r="AU160" s="58"/>
+      <c r="AV160" s="58"/>
+      <c r="AW160" s="58"/>
+      <c r="AX160" s="58"/>
+      <c r="AY160" s="58"/>
+      <c r="AZ160" s="58"/>
+      <c r="BA160" s="54"/>
+    </row>
+    <row r="161" spans="1:53">
       <c r="A161" s="34"/>
       <c r="B161" s="35" t="s">
         <v>474</v>
@@ -8280,115 +8519,156 @@
         <v>477</v>
       </c>
       <c r="D161" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="E161" s="35" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
+        <v>472</v>
+      </c>
+      <c r="E161" s="39" t="s">
+        <v>613</v>
+      </c>
+      <c r="S161" s="35" t="s">
+        <v>653</v>
+      </c>
+      <c r="AK161" s="51"/>
+      <c r="AL161" s="57" t="s">
+        <v>711</v>
+      </c>
+      <c r="AM161" s="58"/>
+      <c r="AN161" s="58"/>
+      <c r="AO161" s="58"/>
+      <c r="AP161" s="58"/>
+      <c r="AQ161" s="58"/>
+      <c r="AR161" s="58"/>
+      <c r="AS161" s="58"/>
+      <c r="AT161" s="58"/>
+      <c r="AU161" s="58"/>
+      <c r="AV161" s="58"/>
+      <c r="AW161" s="58"/>
+      <c r="AX161" s="58"/>
+      <c r="AY161" s="58"/>
+      <c r="AZ161" s="58"/>
+      <c r="BA161" s="54"/>
+    </row>
+    <row r="162" spans="1:53" ht="19.5" thickBot="1">
       <c r="A162" s="34"/>
       <c r="B162" s="35" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="163" spans="1:6">
+      <c r="C162" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D162" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="E162" s="35" t="s">
+        <v>614</v>
+      </c>
+      <c r="AK162" s="55"/>
+      <c r="AL162" s="59" t="s">
+        <v>709</v>
+      </c>
+      <c r="AM162" s="60"/>
+      <c r="AN162" s="60"/>
+      <c r="AO162" s="60"/>
+      <c r="AP162" s="60"/>
+      <c r="AQ162" s="60"/>
+      <c r="AR162" s="60"/>
+      <c r="AS162" s="60"/>
+      <c r="AT162" s="60"/>
+      <c r="AU162" s="60"/>
+      <c r="AV162" s="60"/>
+      <c r="AW162" s="60"/>
+      <c r="AX162" s="60"/>
+      <c r="AY162" s="60"/>
+      <c r="AZ162" s="60"/>
+      <c r="BA162" s="56"/>
+    </row>
+    <row r="163" spans="1:53">
       <c r="A163" s="34"/>
       <c r="B163" s="35" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="164" spans="1:6">
+      <c r="C163" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="D163" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E163" s="35" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="164" spans="1:53">
       <c r="A164" s="34"/>
       <c r="B164" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="C164" s="35" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="165" spans="1:53">
       <c r="A165" s="34"/>
       <c r="B165" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C165" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="D165" s="35" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
+    </row>
+    <row r="166" spans="1:53">
       <c r="A166" s="34"/>
       <c r="B166" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C166" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="D166" s="35" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="167" spans="1:53">
       <c r="A167" s="34"/>
       <c r="B167" s="35" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="168" spans="1:6">
+      <c r="C167" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D167" s="35" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="168" spans="1:53">
       <c r="A168" s="34"/>
       <c r="B168" s="35" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C168" s="35" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
+        <v>476</v>
+      </c>
+      <c r="D168" s="35" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="169" spans="1:53">
       <c r="A169" s="34"/>
       <c r="B169" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C169" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="D169" s="35" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
+    </row>
+    <row r="170" spans="1:53">
       <c r="A170" s="34"/>
       <c r="B170" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C170" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="D170" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="E170" s="35" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="171" spans="1:53">
       <c r="A171" s="34"/>
       <c r="B171" s="35" t="s">
         <v>474</v>
       </c>
       <c r="C171" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D171" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="E171" s="35" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="172" spans="1:53">
       <c r="A172" s="34"/>
       <c r="B172" s="35" t="s">
         <v>474</v>
@@ -8397,16 +8677,13 @@
         <v>474</v>
       </c>
       <c r="D172" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E172" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="F172" s="35" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:53">
       <c r="A173" s="34"/>
       <c r="B173" s="35" t="s">
         <v>474</v>
@@ -8415,13 +8692,13 @@
         <v>474</v>
       </c>
       <c r="D173" s="35" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E173" s="35" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="174" spans="1:53">
       <c r="A174" s="34"/>
       <c r="B174" s="35" t="s">
         <v>474</v>
@@ -8430,16 +8707,16 @@
         <v>474</v>
       </c>
       <c r="D174" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E174" s="35" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F174" s="35" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:53">
       <c r="A175" s="34"/>
       <c r="B175" s="35" t="s">
         <v>474</v>
@@ -8448,16 +8725,13 @@
         <v>474</v>
       </c>
       <c r="D175" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E175" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="F175" s="35" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="176" spans="1:53">
       <c r="A176" s="34"/>
       <c r="B176" s="35" t="s">
         <v>474</v>
@@ -8472,7 +8746,7 @@
         <v>472</v>
       </c>
       <c r="F176" s="35" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -8490,7 +8764,7 @@
         <v>472</v>
       </c>
       <c r="F177" s="35" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -8505,10 +8779,10 @@
         <v>477</v>
       </c>
       <c r="E178" s="35" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F178" s="35" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -8517,10 +8791,16 @@
         <v>474</v>
       </c>
       <c r="C179" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D179" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="E179" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="D179" s="35" t="s">
-        <v>510</v>
+      <c r="F179" s="35" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -8532,10 +8812,13 @@
         <v>474</v>
       </c>
       <c r="D180" s="35" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E180" s="35" t="s">
-        <v>487</v>
+        <v>476</v>
+      </c>
+      <c r="F180" s="35" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -8544,16 +8827,10 @@
         <v>474</v>
       </c>
       <c r="C181" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D181" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="E181" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="F181" s="35" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -8568,7 +8845,7 @@
         <v>472</v>
       </c>
       <c r="E182" s="35" t="s">
-        <v>512</v>
+        <v>487</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -8580,10 +8857,13 @@
         <v>474</v>
       </c>
       <c r="D183" s="35" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E183" s="35" t="s">
-        <v>513</v>
+        <v>476</v>
+      </c>
+      <c r="F183" s="35" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -8595,10 +8875,10 @@
         <v>474</v>
       </c>
       <c r="D184" s="35" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E184" s="35" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -8607,50 +8887,74 @@
         <v>474</v>
       </c>
       <c r="C185" s="35" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D185" s="35" t="s">
-        <v>514</v>
+        <v>472</v>
+      </c>
+      <c r="E185" s="35" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="34"/>
       <c r="B186" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C186" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D186" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="C186" s="35" t="s">
-        <v>515</v>
+      <c r="E186" s="35" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="34"/>
       <c r="B187" s="35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C187" s="35" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D187" s="35" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="34"/>
       <c r="B188" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C188" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="D188" s="35" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="34"/>
+      <c r="B189" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="C189" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D189" s="35" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="34"/>
+      <c r="B190" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="C190" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D190" s="35" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="34"/>
@@ -9455,6 +9759,12 @@
     </row>
     <row r="458" spans="1:1">
       <c r="A458" s="34"/>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459" s="34"/>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9462,658 +9772,658 @@
     <mergeCell ref="S2:X2"/>
   </mergeCells>
   <phoneticPr fontId="34"/>
-  <conditionalFormatting sqref="A190:A209">
+  <conditionalFormatting sqref="A192:A211">
     <cfRule type="expression" dxfId="214" priority="1332" stopIfTrue="1">
-      <formula>OR($B171="├─",$B171="└─")</formula>
+      <formula>OR($B173="├─",$B173="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A191:A192 A194 A200">
+  <conditionalFormatting sqref="A193:A194 A196 A202">
     <cfRule type="expression" dxfId="213" priority="1224" stopIfTrue="1">
-      <formula>OR($B172="├─",$B172="└─")</formula>
+      <formula>OR($B174="├─",$B174="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="212" priority="1225" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="211" priority="1226" stopIfTrue="1">
-      <formula>OR($B172="├─",$B172="└─")</formula>
+      <formula>OR($B174="├─",$B174="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="210" priority="1227" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="209" priority="1228" stopIfTrue="1">
-      <formula>OR($B172="├─",$B172="└─")</formula>
+      <formula>OR($B174="├─",$B174="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="208" priority="1229" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="207" priority="1230" stopIfTrue="1">
-      <formula>OR($B172="├─",$B172="└─")</formula>
+      <formula>OR($B174="├─",$B174="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="206" priority="1231" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="205" priority="1232" stopIfTrue="1">
-      <formula>OR($B172="├─",$B172="└─")</formula>
+      <formula>OR($B174="├─",$B174="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="204" priority="1233" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="203" priority="1234" stopIfTrue="1">
-      <formula>OR($B172="├─",$B172="└─")</formula>
+      <formula>OR($B174="├─",$B174="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="202" priority="1235" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A191:A192 A194:A195 A197:A204">
+  <conditionalFormatting sqref="A193:A194 A196:A197 A199:A206">
     <cfRule type="expression" dxfId="201" priority="1236" stopIfTrue="1">
-      <formula>OR($B172="├─",$B172="└─")</formula>
+      <formula>OR($B174="├─",$B174="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="200" priority="1237" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A195 A197:A204">
+  <conditionalFormatting sqref="A197 A199:A206">
     <cfRule type="expression" dxfId="199" priority="1343" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A195 A203:A204">
+  <conditionalFormatting sqref="A197 A205:A206">
     <cfRule type="expression" dxfId="198" priority="1333" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="197" priority="1334" stopIfTrue="1">
-      <formula>OR($B176="├─",$B176="└─")</formula>
+      <formula>OR($B178="├─",$B178="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="196" priority="1335" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="195" priority="1336" stopIfTrue="1">
-      <formula>OR($B176="├─",$B176="└─")</formula>
+      <formula>OR($B178="├─",$B178="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="194" priority="1337" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="193" priority="1338" stopIfTrue="1">
-      <formula>OR($B176="├─",$B176="└─")</formula>
+      <formula>OR($B178="├─",$B178="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="192" priority="1339" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="191" priority="1340" stopIfTrue="1">
-      <formula>OR($B176="├─",$B176="└─")</formula>
+      <formula>OR($B178="├─",$B178="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="190" priority="1341" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="189" priority="1342" stopIfTrue="1">
-      <formula>OR($B176="├─",$B176="└─")</formula>
+      <formula>OR($B178="├─",$B178="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A195">
+  <conditionalFormatting sqref="A197">
     <cfRule type="expression" dxfId="188" priority="1344" stopIfTrue="1">
-      <formula>OR($B176="├─",$B176="└─")</formula>
+      <formula>OR($B178="├─",$B178="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="187" priority="1345" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A199">
+  <conditionalFormatting sqref="A201">
     <cfRule type="expression" dxfId="186" priority="1392" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="185" priority="1393" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="184" priority="1394" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="183" priority="1395" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="182" priority="1396" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="181" priority="1397" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="180" priority="1398" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="179" priority="1399" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="178" priority="1400" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="177" priority="1401" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="176" priority="1402" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="175" priority="1403" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="174" priority="1404" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="173" priority="1405" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="172" priority="1406" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="171" priority="1407" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="170" priority="1408" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="169" priority="1409" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="168" priority="1410" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="167" priority="1411" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A199:A200">
+  <conditionalFormatting sqref="A201:A202">
     <cfRule type="expression" dxfId="166" priority="1432" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="165" priority="1433" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="164" priority="1434" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="163" priority="1435" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="162" priority="1436" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="161" priority="1437" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A199:A201">
+  <conditionalFormatting sqref="A201:A203">
     <cfRule type="expression" dxfId="160" priority="1438" stopIfTrue="1">
-      <formula>OR($B180="├─",$B180="└─")</formula>
+      <formula>OR($B182="├─",$B182="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="159" priority="1439" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A201">
+  <conditionalFormatting sqref="A203">
     <cfRule type="expression" dxfId="158" priority="1502" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
+      <formula>OR($B184="├─",$B184="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="157" priority="1503" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="156" priority="1504" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
+      <formula>OR($B184="├─",$B184="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="155" priority="1505" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="154" priority="1506" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
+      <formula>OR($B184="├─",$B184="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="153" priority="1507" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="152" priority="1508" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
+      <formula>OR($B184="├─",$B184="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="151" priority="1509" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="150" priority="1510" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
+      <formula>OR($B184="├─",$B184="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="149" priority="1511" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="148" priority="1512" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
+      <formula>OR($B184="├─",$B184="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="147" priority="1513" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="146" priority="1514" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
+      <formula>OR($B184="├─",$B184="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="145" priority="1515" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="144" priority="1516" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
+      <formula>OR($B184="├─",$B184="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="143" priority="1517" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="142" priority="1518" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
+      <formula>OR($B184="├─",$B184="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="141" priority="1519" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="140" priority="1520" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
+      <formula>OR($B184="├─",$B184="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="139" priority="1521" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A203">
+  <conditionalFormatting sqref="A205">
     <cfRule type="expression" dxfId="138" priority="1566" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="137" priority="1567" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="136" priority="1568" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="135" priority="1569" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="134" priority="1570" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="133" priority="1571" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="132" priority="1572" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="131" priority="1573" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="130" priority="1574" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="129" priority="1575" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="128" priority="1576" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="127" priority="1577" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="126" priority="1578" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="125" priority="1579" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="124" priority="1580" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="123" priority="1581" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="122" priority="1582" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="121" priority="1583" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="120" priority="1584" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="119" priority="1585" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="118" priority="1586" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="117" priority="1587" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A203:A204">
+  <conditionalFormatting sqref="A205:A206">
     <cfRule type="expression" dxfId="116" priority="1330" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="115" priority="1331" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="114" priority="1588" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
+      <formula>OR($B186="├─",$B186="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="113" priority="1589" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A204">
+  <conditionalFormatting sqref="A206">
     <cfRule type="expression" dxfId="112" priority="1650" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="111" priority="1651" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="110" priority="1652" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="109" priority="1653" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="108" priority="1654" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="107" priority="1655" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="1656" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="1657" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="104" priority="1658" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="103" priority="1659" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="102" priority="1660" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="1661" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="1662" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="99" priority="1663" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="98" priority="1664" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="97" priority="1665" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="96" priority="1666" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="95" priority="1667" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="94" priority="1668" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="93" priority="1669" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="92" priority="1670" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="91" priority="1671" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="90" priority="1672" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="89" priority="1673" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="88" priority="1674" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="87" priority="1675" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="86" priority="1676" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="85" priority="1677" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="84" priority="1678" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="83" priority="1679" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="82" priority="1680" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="81" priority="1681" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="80" priority="1682" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="79" priority="1683" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="78" priority="1684" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="77" priority="1685" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="76" priority="1686" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="75" priority="1687" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="74" priority="1688" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="73" priority="1689" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A204:A205">
+  <conditionalFormatting sqref="A206:A207">
     <cfRule type="expression" dxfId="72" priority="1732" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="71" priority="1733" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="70" priority="1734" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="69" priority="1735" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="68" priority="1736" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="67" priority="1737" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="66" priority="1738" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="65" priority="1739" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="64" priority="1740" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="63" priority="1741" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="62" priority="1742" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="61" priority="1743" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="60" priority="1744" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="59" priority="1745" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="58" priority="1746" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="57" priority="1747" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="56" priority="1748" stopIfTrue="1">
-      <formula>OR($B185="├─",$B185="└─")</formula>
+      <formula>OR($B187="├─",$B187="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="55" priority="1749" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A205">
+  <conditionalFormatting sqref="A207">
     <cfRule type="expression" dxfId="54" priority="1768" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="53" priority="1769" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="1770" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="51" priority="1771" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="50" priority="1772" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="49" priority="1773" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="48" priority="1774" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="1775" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="46" priority="1776" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="45" priority="1777" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="44" priority="1778" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="43" priority="1779" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="42" priority="1780" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="41" priority="1781" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="1782" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="39" priority="1783" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="38" priority="1784" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="37" priority="1785" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="36" priority="1786" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="35" priority="1787" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="34" priority="1788" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="33" priority="1789" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="32" priority="1790" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
+      <formula>OR($B188="├─",$B188="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="31" priority="1791" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A207 B201:E449">
+  <conditionalFormatting sqref="A209 B203:E451">
     <cfRule type="expression" dxfId="30" priority="1365" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A207">
+  <conditionalFormatting sqref="A209">
     <cfRule type="expression" dxfId="29" priority="1363" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="28" priority="1364" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
+      <formula>OR($B190="├─",$B190="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A210:A458">
+  <conditionalFormatting sqref="A212:A460">
     <cfRule type="expression" dxfId="27" priority="2069" stopIfTrue="1">
-      <formula>OR($B201="├─",$B201="└─")</formula>
+      <formula>OR($B203="├─",$B203="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A211:A212 A214:A215 A220:A233">
+  <conditionalFormatting sqref="A213:A214 A216:A217 A222:A235">
     <cfRule type="expression" dxfId="26" priority="1919" stopIfTrue="1">
-      <formula>OR($B202="├─",$B202="└─")</formula>
+      <formula>OR($B204="├─",$B204="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="25" priority="1920" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A229:A231">
+  <conditionalFormatting sqref="A231:A233">
     <cfRule type="expression" dxfId="24" priority="2045" stopIfTrue="1">
-      <formula>OR($B220="├─",$B220="└─")</formula>
+      <formula>OR($B222="├─",$B222="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="2046" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2047" stopIfTrue="1">
-      <formula>OR($B220="├─",$B220="└─")</formula>
+      <formula>OR($B222="├─",$B222="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="21" priority="2048" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B211:C224 Y68:AK68 B202:C203 B205:C206">
+  <conditionalFormatting sqref="B213:C226 Y68:AK68 B204:C205 B207:C208">
     <cfRule type="expression" dxfId="20" priority="881" stopIfTrue="1">
       <formula>OR($B68="├─",$B68="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B220:C222">
+  <conditionalFormatting sqref="B222:C224">
     <cfRule type="expression" dxfId="19" priority="819" stopIfTrue="1">
-      <formula>OR($B220="├─",$B220="└─")</formula>
+      <formula>OR($B222="├─",$B222="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="18" priority="820" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="823" stopIfTrue="1">
-      <formula>OR($B220="├─",$B220="└─")</formula>
+      <formula>OR($B222="├─",$B222="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="824" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B190:E190 A190:A458">
+  <conditionalFormatting sqref="B192:E192 A192:A460">
     <cfRule type="expression" dxfId="15" priority="890" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B201:E449 B190:E190">
+  <conditionalFormatting sqref="B203:E451 B192:E192">
     <cfRule type="expression" dxfId="14" priority="889" stopIfTrue="1">
-      <formula>OR($B190="├─",$B190="└─")</formula>
+      <formula>OR($B192="├─",$B192="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:R1 T1:X1 A1:A3 S1:S3 B3:R3 T3:X3 A4:X100 A101:AN101 A102:X150 A151:R151 A152:X158 A159:R159 A160:X189">
+  <conditionalFormatting sqref="B1:R1 T1:X1 A1:A3 S1:S3 B3:R3 T3:X3 A4:X100 A101:AN101 A102:X150 A151:R151 A161:R161 A162:X191 A152:X160">
     <cfRule type="expression" dxfId="13" priority="801" stopIfTrue="1">
       <formula>OR($B1="├─",$B1="└─")</formula>
     </cfRule>
@@ -10121,28 +10431,28 @@
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F205:F436">
+  <conditionalFormatting sqref="F207:F438">
     <cfRule type="expression" dxfId="11" priority="938" stopIfTrue="1">
-      <formula>OR($B218="├─",$B218="└─")</formula>
+      <formula>OR($B220="├─",$B220="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="939" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G434:X65628 F437:F65631 B450:E65644">
+  <conditionalFormatting sqref="G436:X65630 F439:F65633 B452:E65646">
     <cfRule type="expression" dxfId="9" priority="893" stopIfTrue="1">
-      <formula>OR(B434="│",B434="├─",B434="└─")</formula>
+      <formula>OR(B436="│",B436="├─",B436="└─")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K190:X204 G205:X433">
+  <conditionalFormatting sqref="K192:X206 G207:X435">
     <cfRule type="expression" dxfId="8" priority="375" stopIfTrue="1">
-      <formula>OR($B206="├─",$B206="└─")</formula>
+      <formula>OR($B208="├─",$B208="└─")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="376" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S159:X159">
+  <conditionalFormatting sqref="S161:X161">
     <cfRule type="expression" dxfId="6" priority="2080" stopIfTrue="1">
       <formula>OR($B151="├─",$B151="└─")</formula>
     </cfRule>
@@ -10158,7 +10468,7 @@
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y68:AK68 B202:C203 B205:C206 B211:C224">
+  <conditionalFormatting sqref="Y68:AK68 B204:C205 B207:C208 B213:C226">
     <cfRule type="expression" dxfId="2" priority="882" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -10180,6 +10490,466 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626DB163-BD8B-468F-83A9-4D70FEBCA709}">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A2:A124"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="10" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="25.5">
+      <c r="A11" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="25.5">
+      <c r="A24" s="8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="25.5">
+      <c r="A38" s="8"/>
+    </row>
+    <row r="39" spans="1:1" ht="25.5">
+      <c r="A39" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="11" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="3"/>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="3"/>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="3"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="3"/>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="3"/>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="17" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="2"/>
+    </row>
+    <row r="112" spans="1:1" ht="26.25">
+      <c r="A112" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="13" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="16" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="13"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="26.25">
+      <c r="A117" s="12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="13"/>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="13"/>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <hyperlinks>
+    <hyperlink ref="A118" r:id="rId1" location="fn-1" display="https://qiita.com/sskre/items/0bd048744ea2f830682e - fn-1" xr:uid="{047BE0B8-9A0D-4A1E-802F-7EEE2BF06DA7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA8CB5A-8AF9-428F-BF72-A4650EA2714E}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:B108"/>
@@ -10599,7 +11369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED49263E-B0E6-4B40-8C98-8489AC780DBF}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C219"/>
@@ -11182,6 +11952,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06CDD67F-0277-4276-92C9-CC229FE3D506}">
+  <dimension ref="A2:A5"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>715</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52820001-5FDD-4FE0-88DB-40598CB6E06D}">
   <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -11287,7 +12083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A933EA-8619-44FF-B324-B22BEE6396FB}">
   <dimension ref="A1:I75"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -11722,7 +12518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A6B54C0-84BD-40BC-AEE9-70FBD3941C49}">
   <dimension ref="A2:A9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -11768,7 +12564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5CDBE3-750C-4C0D-8AAF-43745D6A6F72}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:A126"/>
@@ -12188,7 +12984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F76542-7475-450B-8480-EFB6EF4C355E}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:A61"/>
@@ -12405,7 +13201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E709E9D4-AB6E-4CC2-8E0F-A5793B336BEE}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:A149"/>
@@ -12943,7 +13739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5098A92-C5C0-4353-AB1F-30D7DE2F67BE}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A2:I93"/>
@@ -13297,464 +14093,4 @@
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626DB163-BD8B-468F-83A9-4D70FEBCA709}">
-  <sheetPr codeName="Sheet5"/>
-  <dimension ref="A2:A124"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="10" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="25.5">
-      <c r="A11" s="8" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="25.5">
-      <c r="A24" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="7" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" ht="25.5">
-      <c r="A38" s="8"/>
-    </row>
-    <row r="39" spans="1:1" ht="25.5">
-      <c r="A39" s="9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="10" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="11" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="3"/>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="3"/>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="3"/>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="3" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="3"/>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="3"/>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="17" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="2"/>
-    </row>
-    <row r="112" spans="1:1" ht="26.25">
-      <c r="A112" s="12" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="13" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="16" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="13"/>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="15" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" ht="26.25">
-      <c r="A117" s="12" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="14" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="13"/>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="13"/>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3"/>
-  <hyperlinks>
-    <hyperlink ref="A118" r:id="rId1" location="fn-1" display="https://qiita.com/sskre/items/0bd048744ea2f830682e - fn-1" xr:uid="{047BE0B8-9A0D-4A1E-802F-7EEE2BF06DA7}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/実装メモ.xlsx
+++ b/実装メモ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\docker_cms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CC976B-DDE6-4908-8C03-2D7591037F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEACC6B-2BDC-42E9-93D6-57334623DD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
   </bookViews>
   <sheets>
     <sheet name="構成図" sheetId="9" r:id="rId1"/>
@@ -3676,7 +3676,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3794,6 +3794,23 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="32" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3812,31 +3829,20 @@
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{F19A6957-2B34-4EDC-A43E-1512F220B8B2}"/>
   </cellStyles>
-  <dxfs count="215">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3855,20 +3861,6 @@
       <fill>
         <patternFill>
           <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3924,20 +3916,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor indexed="43"/>
         </patternFill>
       </fill>
@@ -3946,1399 +3924,6 @@
       <fill>
         <patternFill>
           <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="43"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5673,7 +4258,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13CDE890-F993-425A-B129-8B17D7811949}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:BA460"/>
+  <dimension ref="A1:BA194"/>
   <sheetFormatPr defaultColWidth="4.375" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.375" style="38" customWidth="1"/>
@@ -5810,34 +4395,34 @@
       <c r="A1" s="34"/>
     </row>
     <row r="2" spans="1:24" ht="19.5" thickBot="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="54" t="s">
         <v>470</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="46" t="s">
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="57" t="s">
         <v>372</v>
       </c>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="47"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="58"/>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="34"/>
@@ -8415,7 +7000,7 @@
       <c r="F158" s="35" t="s">
         <v>612</v>
       </c>
-      <c r="AK158" s="49"/>
+      <c r="AK158" s="43"/>
       <c r="AL158" s="37"/>
       <c r="AM158" s="37"/>
       <c r="AN158" s="37"/>
@@ -8431,7 +7016,7 @@
       <c r="AX158" s="37"/>
       <c r="AY158" s="37"/>
       <c r="AZ158" s="37"/>
-      <c r="BA158" s="50"/>
+      <c r="BA158" s="44"/>
     </row>
     <row r="159" spans="1:53">
       <c r="A159" s="34"/>
@@ -8447,25 +7032,11 @@
       <c r="E159" s="35" t="s">
         <v>704</v>
       </c>
-      <c r="AK159" s="51"/>
-      <c r="AL159" s="52" t="s">
+      <c r="AK159" s="45"/>
+      <c r="AL159" s="46" t="s">
         <v>708</v>
       </c>
-      <c r="AM159" s="53"/>
-      <c r="AN159" s="53"/>
-      <c r="AO159" s="53"/>
-      <c r="AP159" s="53"/>
-      <c r="AQ159" s="53"/>
-      <c r="AR159" s="53"/>
-      <c r="AS159" s="53"/>
-      <c r="AT159" s="53"/>
-      <c r="AU159" s="53"/>
-      <c r="AV159" s="53"/>
-      <c r="AW159" s="53"/>
-      <c r="AX159" s="53"/>
-      <c r="AY159" s="53"/>
-      <c r="AZ159" s="53"/>
-      <c r="BA159" s="54"/>
+      <c r="BA159" s="47"/>
     </row>
     <row r="160" spans="1:53">
       <c r="A160" s="34"/>
@@ -8490,25 +7061,25 @@
       <c r="Z160" s="35" t="s">
         <v>707</v>
       </c>
-      <c r="AK160" s="51"/>
-      <c r="AL160" s="57" t="s">
+      <c r="AK160" s="45"/>
+      <c r="AL160" s="50" t="s">
         <v>710</v>
       </c>
-      <c r="AM160" s="58"/>
-      <c r="AN160" s="58"/>
-      <c r="AO160" s="58"/>
-      <c r="AP160" s="58"/>
-      <c r="AQ160" s="58"/>
-      <c r="AR160" s="58"/>
-      <c r="AS160" s="58"/>
-      <c r="AT160" s="58"/>
-      <c r="AU160" s="58"/>
-      <c r="AV160" s="58"/>
-      <c r="AW160" s="58"/>
-      <c r="AX160" s="58"/>
-      <c r="AY160" s="58"/>
-      <c r="AZ160" s="58"/>
-      <c r="BA160" s="54"/>
+      <c r="AM160" s="51"/>
+      <c r="AN160" s="51"/>
+      <c r="AO160" s="51"/>
+      <c r="AP160" s="51"/>
+      <c r="AQ160" s="51"/>
+      <c r="AR160" s="51"/>
+      <c r="AS160" s="51"/>
+      <c r="AT160" s="51"/>
+      <c r="AU160" s="51"/>
+      <c r="AV160" s="51"/>
+      <c r="AW160" s="51"/>
+      <c r="AX160" s="51"/>
+      <c r="AY160" s="51"/>
+      <c r="AZ160" s="51"/>
+      <c r="BA160" s="47"/>
     </row>
     <row r="161" spans="1:53">
       <c r="A161" s="34"/>
@@ -8527,25 +7098,25 @@
       <c r="S161" s="35" t="s">
         <v>653</v>
       </c>
-      <c r="AK161" s="51"/>
-      <c r="AL161" s="57" t="s">
+      <c r="AK161" s="45"/>
+      <c r="AL161" s="50" t="s">
         <v>711</v>
       </c>
-      <c r="AM161" s="58"/>
-      <c r="AN161" s="58"/>
-      <c r="AO161" s="58"/>
-      <c r="AP161" s="58"/>
-      <c r="AQ161" s="58"/>
-      <c r="AR161" s="58"/>
-      <c r="AS161" s="58"/>
-      <c r="AT161" s="58"/>
-      <c r="AU161" s="58"/>
-      <c r="AV161" s="58"/>
-      <c r="AW161" s="58"/>
-      <c r="AX161" s="58"/>
-      <c r="AY161" s="58"/>
-      <c r="AZ161" s="58"/>
-      <c r="BA161" s="54"/>
+      <c r="AM161" s="51"/>
+      <c r="AN161" s="51"/>
+      <c r="AO161" s="51"/>
+      <c r="AP161" s="51"/>
+      <c r="AQ161" s="51"/>
+      <c r="AR161" s="51"/>
+      <c r="AS161" s="51"/>
+      <c r="AT161" s="51"/>
+      <c r="AU161" s="51"/>
+      <c r="AV161" s="51"/>
+      <c r="AW161" s="51"/>
+      <c r="AX161" s="51"/>
+      <c r="AY161" s="51"/>
+      <c r="AZ161" s="51"/>
+      <c r="BA161" s="47"/>
     </row>
     <row r="162" spans="1:53" ht="19.5" thickBot="1">
       <c r="A162" s="34"/>
@@ -8561,25 +7132,25 @@
       <c r="E162" s="35" t="s">
         <v>614</v>
       </c>
-      <c r="AK162" s="55"/>
-      <c r="AL162" s="59" t="s">
+      <c r="AK162" s="48"/>
+      <c r="AL162" s="52" t="s">
         <v>709</v>
       </c>
-      <c r="AM162" s="60"/>
-      <c r="AN162" s="60"/>
-      <c r="AO162" s="60"/>
-      <c r="AP162" s="60"/>
-      <c r="AQ162" s="60"/>
-      <c r="AR162" s="60"/>
-      <c r="AS162" s="60"/>
-      <c r="AT162" s="60"/>
-      <c r="AU162" s="60"/>
-      <c r="AV162" s="60"/>
-      <c r="AW162" s="60"/>
-      <c r="AX162" s="60"/>
-      <c r="AY162" s="60"/>
-      <c r="AZ162" s="60"/>
-      <c r="BA162" s="56"/>
+      <c r="AM162" s="53"/>
+      <c r="AN162" s="53"/>
+      <c r="AO162" s="53"/>
+      <c r="AP162" s="53"/>
+      <c r="AQ162" s="53"/>
+      <c r="AR162" s="53"/>
+      <c r="AS162" s="53"/>
+      <c r="AT162" s="53"/>
+      <c r="AU162" s="53"/>
+      <c r="AV162" s="53"/>
+      <c r="AW162" s="53"/>
+      <c r="AX162" s="53"/>
+      <c r="AY162" s="53"/>
+      <c r="AZ162" s="53"/>
+      <c r="BA162" s="49"/>
     </row>
     <row r="163" spans="1:53">
       <c r="A163" s="34"/>
@@ -8967,804 +7538,6 @@
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="34"/>
-    </row>
-    <row r="195" spans="1:1">
-      <c r="A195" s="34"/>
-    </row>
-    <row r="196" spans="1:1">
-      <c r="A196" s="34"/>
-    </row>
-    <row r="197" spans="1:1">
-      <c r="A197" s="34"/>
-    </row>
-    <row r="198" spans="1:1">
-      <c r="A198" s="34"/>
-    </row>
-    <row r="199" spans="1:1">
-      <c r="A199" s="34"/>
-    </row>
-    <row r="200" spans="1:1">
-      <c r="A200" s="34"/>
-    </row>
-    <row r="201" spans="1:1">
-      <c r="A201" s="34"/>
-    </row>
-    <row r="202" spans="1:1">
-      <c r="A202" s="34"/>
-    </row>
-    <row r="203" spans="1:1">
-      <c r="A203" s="34"/>
-    </row>
-    <row r="204" spans="1:1">
-      <c r="A204" s="34"/>
-    </row>
-    <row r="205" spans="1:1">
-      <c r="A205" s="34"/>
-    </row>
-    <row r="206" spans="1:1">
-      <c r="A206" s="34"/>
-    </row>
-    <row r="207" spans="1:1">
-      <c r="A207" s="34"/>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" s="34"/>
-    </row>
-    <row r="209" spans="1:1">
-      <c r="A209" s="34"/>
-    </row>
-    <row r="210" spans="1:1">
-      <c r="A210" s="34"/>
-    </row>
-    <row r="211" spans="1:1">
-      <c r="A211" s="34"/>
-    </row>
-    <row r="212" spans="1:1">
-      <c r="A212" s="34"/>
-    </row>
-    <row r="213" spans="1:1">
-      <c r="A213" s="34"/>
-    </row>
-    <row r="214" spans="1:1">
-      <c r="A214" s="34"/>
-    </row>
-    <row r="215" spans="1:1">
-      <c r="A215" s="34"/>
-    </row>
-    <row r="216" spans="1:1">
-      <c r="A216" s="34"/>
-    </row>
-    <row r="217" spans="1:1">
-      <c r="A217" s="34"/>
-    </row>
-    <row r="218" spans="1:1">
-      <c r="A218" s="34"/>
-    </row>
-    <row r="219" spans="1:1">
-      <c r="A219" s="34"/>
-    </row>
-    <row r="220" spans="1:1">
-      <c r="A220" s="34"/>
-    </row>
-    <row r="221" spans="1:1">
-      <c r="A221" s="34"/>
-    </row>
-    <row r="222" spans="1:1">
-      <c r="A222" s="34"/>
-    </row>
-    <row r="223" spans="1:1">
-      <c r="A223" s="34"/>
-    </row>
-    <row r="224" spans="1:1">
-      <c r="A224" s="34"/>
-    </row>
-    <row r="225" spans="1:1">
-      <c r="A225" s="34"/>
-    </row>
-    <row r="226" spans="1:1">
-      <c r="A226" s="34"/>
-    </row>
-    <row r="227" spans="1:1">
-      <c r="A227" s="34"/>
-    </row>
-    <row r="228" spans="1:1">
-      <c r="A228" s="34"/>
-    </row>
-    <row r="229" spans="1:1">
-      <c r="A229" s="34"/>
-    </row>
-    <row r="230" spans="1:1">
-      <c r="A230" s="34"/>
-    </row>
-    <row r="231" spans="1:1">
-      <c r="A231" s="34"/>
-    </row>
-    <row r="232" spans="1:1">
-      <c r="A232" s="34"/>
-    </row>
-    <row r="233" spans="1:1">
-      <c r="A233" s="34"/>
-    </row>
-    <row r="234" spans="1:1">
-      <c r="A234" s="34"/>
-    </row>
-    <row r="235" spans="1:1">
-      <c r="A235" s="34"/>
-    </row>
-    <row r="236" spans="1:1">
-      <c r="A236" s="34"/>
-    </row>
-    <row r="237" spans="1:1">
-      <c r="A237" s="34"/>
-    </row>
-    <row r="238" spans="1:1">
-      <c r="A238" s="34"/>
-    </row>
-    <row r="239" spans="1:1">
-      <c r="A239" s="34"/>
-    </row>
-    <row r="240" spans="1:1">
-      <c r="A240" s="34"/>
-    </row>
-    <row r="241" spans="1:1">
-      <c r="A241" s="34"/>
-    </row>
-    <row r="242" spans="1:1">
-      <c r="A242" s="34"/>
-    </row>
-    <row r="243" spans="1:1">
-      <c r="A243" s="34"/>
-    </row>
-    <row r="244" spans="1:1">
-      <c r="A244" s="34"/>
-    </row>
-    <row r="245" spans="1:1">
-      <c r="A245" s="34"/>
-    </row>
-    <row r="246" spans="1:1">
-      <c r="A246" s="34"/>
-    </row>
-    <row r="247" spans="1:1">
-      <c r="A247" s="34"/>
-    </row>
-    <row r="248" spans="1:1">
-      <c r="A248" s="34"/>
-    </row>
-    <row r="249" spans="1:1">
-      <c r="A249" s="34"/>
-    </row>
-    <row r="250" spans="1:1">
-      <c r="A250" s="34"/>
-    </row>
-    <row r="251" spans="1:1">
-      <c r="A251" s="34"/>
-    </row>
-    <row r="252" spans="1:1">
-      <c r="A252" s="34"/>
-    </row>
-    <row r="253" spans="1:1">
-      <c r="A253" s="34"/>
-    </row>
-    <row r="254" spans="1:1">
-      <c r="A254" s="34"/>
-    </row>
-    <row r="255" spans="1:1">
-      <c r="A255" s="34"/>
-    </row>
-    <row r="256" spans="1:1">
-      <c r="A256" s="34"/>
-    </row>
-    <row r="257" spans="1:1">
-      <c r="A257" s="34"/>
-    </row>
-    <row r="258" spans="1:1">
-      <c r="A258" s="34"/>
-    </row>
-    <row r="259" spans="1:1">
-      <c r="A259" s="34"/>
-    </row>
-    <row r="260" spans="1:1">
-      <c r="A260" s="34"/>
-    </row>
-    <row r="261" spans="1:1">
-      <c r="A261" s="34"/>
-    </row>
-    <row r="262" spans="1:1">
-      <c r="A262" s="34"/>
-    </row>
-    <row r="263" spans="1:1">
-      <c r="A263" s="34"/>
-    </row>
-    <row r="264" spans="1:1">
-      <c r="A264" s="34"/>
-    </row>
-    <row r="265" spans="1:1">
-      <c r="A265" s="34"/>
-    </row>
-    <row r="266" spans="1:1">
-      <c r="A266" s="34"/>
-    </row>
-    <row r="267" spans="1:1">
-      <c r="A267" s="34"/>
-    </row>
-    <row r="268" spans="1:1">
-      <c r="A268" s="34"/>
-    </row>
-    <row r="269" spans="1:1">
-      <c r="A269" s="34"/>
-    </row>
-    <row r="270" spans="1:1">
-      <c r="A270" s="34"/>
-    </row>
-    <row r="271" spans="1:1">
-      <c r="A271" s="34"/>
-    </row>
-    <row r="272" spans="1:1">
-      <c r="A272" s="34"/>
-    </row>
-    <row r="273" spans="1:1">
-      <c r="A273" s="34"/>
-    </row>
-    <row r="274" spans="1:1">
-      <c r="A274" s="34"/>
-    </row>
-    <row r="275" spans="1:1">
-      <c r="A275" s="34"/>
-    </row>
-    <row r="276" spans="1:1">
-      <c r="A276" s="34"/>
-    </row>
-    <row r="277" spans="1:1">
-      <c r="A277" s="34"/>
-    </row>
-    <row r="278" spans="1:1">
-      <c r="A278" s="34"/>
-    </row>
-    <row r="279" spans="1:1">
-      <c r="A279" s="34"/>
-    </row>
-    <row r="280" spans="1:1">
-      <c r="A280" s="34"/>
-    </row>
-    <row r="281" spans="1:1">
-      <c r="A281" s="34"/>
-    </row>
-    <row r="282" spans="1:1">
-      <c r="A282" s="34"/>
-    </row>
-    <row r="283" spans="1:1">
-      <c r="A283" s="34"/>
-    </row>
-    <row r="284" spans="1:1">
-      <c r="A284" s="34"/>
-    </row>
-    <row r="285" spans="1:1">
-      <c r="A285" s="34"/>
-    </row>
-    <row r="286" spans="1:1">
-      <c r="A286" s="34"/>
-    </row>
-    <row r="287" spans="1:1">
-      <c r="A287" s="34"/>
-    </row>
-    <row r="288" spans="1:1">
-      <c r="A288" s="34"/>
-    </row>
-    <row r="289" spans="1:1">
-      <c r="A289" s="34"/>
-    </row>
-    <row r="290" spans="1:1">
-      <c r="A290" s="34"/>
-    </row>
-    <row r="291" spans="1:1">
-      <c r="A291" s="34"/>
-    </row>
-    <row r="292" spans="1:1">
-      <c r="A292" s="34"/>
-    </row>
-    <row r="293" spans="1:1">
-      <c r="A293" s="34"/>
-    </row>
-    <row r="294" spans="1:1">
-      <c r="A294" s="34"/>
-    </row>
-    <row r="295" spans="1:1">
-      <c r="A295" s="34"/>
-    </row>
-    <row r="296" spans="1:1">
-      <c r="A296" s="34"/>
-    </row>
-    <row r="297" spans="1:1">
-      <c r="A297" s="34"/>
-    </row>
-    <row r="298" spans="1:1">
-      <c r="A298" s="34"/>
-    </row>
-    <row r="299" spans="1:1">
-      <c r="A299" s="34"/>
-    </row>
-    <row r="300" spans="1:1">
-      <c r="A300" s="34"/>
-    </row>
-    <row r="301" spans="1:1">
-      <c r="A301" s="34"/>
-    </row>
-    <row r="302" spans="1:1">
-      <c r="A302" s="34"/>
-    </row>
-    <row r="303" spans="1:1">
-      <c r="A303" s="34"/>
-    </row>
-    <row r="304" spans="1:1">
-      <c r="A304" s="34"/>
-    </row>
-    <row r="305" spans="1:1">
-      <c r="A305" s="34"/>
-    </row>
-    <row r="306" spans="1:1">
-      <c r="A306" s="34"/>
-    </row>
-    <row r="307" spans="1:1">
-      <c r="A307" s="34"/>
-    </row>
-    <row r="308" spans="1:1">
-      <c r="A308" s="34"/>
-    </row>
-    <row r="309" spans="1:1">
-      <c r="A309" s="34"/>
-    </row>
-    <row r="310" spans="1:1">
-      <c r="A310" s="34"/>
-    </row>
-    <row r="311" spans="1:1">
-      <c r="A311" s="34"/>
-    </row>
-    <row r="312" spans="1:1">
-      <c r="A312" s="34"/>
-    </row>
-    <row r="313" spans="1:1">
-      <c r="A313" s="34"/>
-    </row>
-    <row r="314" spans="1:1">
-      <c r="A314" s="34"/>
-    </row>
-    <row r="315" spans="1:1">
-      <c r="A315" s="34"/>
-    </row>
-    <row r="316" spans="1:1">
-      <c r="A316" s="34"/>
-    </row>
-    <row r="317" spans="1:1">
-      <c r="A317" s="34"/>
-    </row>
-    <row r="318" spans="1:1">
-      <c r="A318" s="34"/>
-    </row>
-    <row r="319" spans="1:1">
-      <c r="A319" s="34"/>
-    </row>
-    <row r="320" spans="1:1">
-      <c r="A320" s="34"/>
-    </row>
-    <row r="321" spans="1:1">
-      <c r="A321" s="34"/>
-    </row>
-    <row r="322" spans="1:1">
-      <c r="A322" s="34"/>
-    </row>
-    <row r="323" spans="1:1">
-      <c r="A323" s="34"/>
-    </row>
-    <row r="324" spans="1:1">
-      <c r="A324" s="34"/>
-    </row>
-    <row r="325" spans="1:1">
-      <c r="A325" s="34"/>
-    </row>
-    <row r="326" spans="1:1">
-      <c r="A326" s="34"/>
-    </row>
-    <row r="327" spans="1:1">
-      <c r="A327" s="34"/>
-    </row>
-    <row r="328" spans="1:1">
-      <c r="A328" s="34"/>
-    </row>
-    <row r="329" spans="1:1">
-      <c r="A329" s="34"/>
-    </row>
-    <row r="330" spans="1:1">
-      <c r="A330" s="34"/>
-    </row>
-    <row r="331" spans="1:1">
-      <c r="A331" s="34"/>
-    </row>
-    <row r="332" spans="1:1">
-      <c r="A332" s="34"/>
-    </row>
-    <row r="333" spans="1:1">
-      <c r="A333" s="34"/>
-    </row>
-    <row r="334" spans="1:1">
-      <c r="A334" s="34"/>
-    </row>
-    <row r="335" spans="1:1">
-      <c r="A335" s="34"/>
-    </row>
-    <row r="336" spans="1:1">
-      <c r="A336" s="34"/>
-    </row>
-    <row r="337" spans="1:1">
-      <c r="A337" s="34"/>
-    </row>
-    <row r="338" spans="1:1">
-      <c r="A338" s="34"/>
-    </row>
-    <row r="339" spans="1:1">
-      <c r="A339" s="34"/>
-    </row>
-    <row r="340" spans="1:1">
-      <c r="A340" s="34"/>
-    </row>
-    <row r="341" spans="1:1">
-      <c r="A341" s="34"/>
-    </row>
-    <row r="342" spans="1:1">
-      <c r="A342" s="34"/>
-    </row>
-    <row r="343" spans="1:1">
-      <c r="A343" s="34"/>
-    </row>
-    <row r="344" spans="1:1">
-      <c r="A344" s="34"/>
-    </row>
-    <row r="345" spans="1:1">
-      <c r="A345" s="34"/>
-    </row>
-    <row r="346" spans="1:1">
-      <c r="A346" s="34"/>
-    </row>
-    <row r="347" spans="1:1">
-      <c r="A347" s="34"/>
-    </row>
-    <row r="348" spans="1:1">
-      <c r="A348" s="34"/>
-    </row>
-    <row r="349" spans="1:1">
-      <c r="A349" s="34"/>
-    </row>
-    <row r="350" spans="1:1">
-      <c r="A350" s="34"/>
-    </row>
-    <row r="351" spans="1:1">
-      <c r="A351" s="34"/>
-    </row>
-    <row r="352" spans="1:1">
-      <c r="A352" s="34"/>
-    </row>
-    <row r="353" spans="1:1">
-      <c r="A353" s="34"/>
-    </row>
-    <row r="354" spans="1:1">
-      <c r="A354" s="34"/>
-    </row>
-    <row r="355" spans="1:1">
-      <c r="A355" s="34"/>
-    </row>
-    <row r="356" spans="1:1">
-      <c r="A356" s="34"/>
-    </row>
-    <row r="357" spans="1:1">
-      <c r="A357" s="34"/>
-    </row>
-    <row r="358" spans="1:1">
-      <c r="A358" s="34"/>
-    </row>
-    <row r="359" spans="1:1">
-      <c r="A359" s="34"/>
-    </row>
-    <row r="360" spans="1:1">
-      <c r="A360" s="34"/>
-    </row>
-    <row r="361" spans="1:1">
-      <c r="A361" s="34"/>
-    </row>
-    <row r="362" spans="1:1">
-      <c r="A362" s="34"/>
-    </row>
-    <row r="363" spans="1:1">
-      <c r="A363" s="34"/>
-    </row>
-    <row r="364" spans="1:1">
-      <c r="A364" s="34"/>
-    </row>
-    <row r="365" spans="1:1">
-      <c r="A365" s="34"/>
-    </row>
-    <row r="366" spans="1:1">
-      <c r="A366" s="34"/>
-    </row>
-    <row r="367" spans="1:1">
-      <c r="A367" s="34"/>
-    </row>
-    <row r="368" spans="1:1">
-      <c r="A368" s="34"/>
-    </row>
-    <row r="369" spans="1:1">
-      <c r="A369" s="34"/>
-    </row>
-    <row r="370" spans="1:1">
-      <c r="A370" s="34"/>
-    </row>
-    <row r="371" spans="1:1">
-      <c r="A371" s="34"/>
-    </row>
-    <row r="372" spans="1:1">
-      <c r="A372" s="34"/>
-    </row>
-    <row r="373" spans="1:1">
-      <c r="A373" s="34"/>
-    </row>
-    <row r="374" spans="1:1">
-      <c r="A374" s="34"/>
-    </row>
-    <row r="375" spans="1:1">
-      <c r="A375" s="34"/>
-    </row>
-    <row r="376" spans="1:1">
-      <c r="A376" s="34"/>
-    </row>
-    <row r="377" spans="1:1">
-      <c r="A377" s="34"/>
-    </row>
-    <row r="378" spans="1:1">
-      <c r="A378" s="34"/>
-    </row>
-    <row r="379" spans="1:1">
-      <c r="A379" s="34"/>
-    </row>
-    <row r="380" spans="1:1">
-      <c r="A380" s="34"/>
-    </row>
-    <row r="381" spans="1:1">
-      <c r="A381" s="34"/>
-    </row>
-    <row r="382" spans="1:1">
-      <c r="A382" s="34"/>
-    </row>
-    <row r="383" spans="1:1">
-      <c r="A383" s="34"/>
-    </row>
-    <row r="384" spans="1:1">
-      <c r="A384" s="34"/>
-    </row>
-    <row r="385" spans="1:1">
-      <c r="A385" s="34"/>
-    </row>
-    <row r="386" spans="1:1">
-      <c r="A386" s="34"/>
-    </row>
-    <row r="387" spans="1:1">
-      <c r="A387" s="34"/>
-    </row>
-    <row r="388" spans="1:1">
-      <c r="A388" s="34"/>
-    </row>
-    <row r="389" spans="1:1">
-      <c r="A389" s="34"/>
-    </row>
-    <row r="390" spans="1:1">
-      <c r="A390" s="34"/>
-    </row>
-    <row r="391" spans="1:1">
-      <c r="A391" s="34"/>
-    </row>
-    <row r="392" spans="1:1">
-      <c r="A392" s="34"/>
-    </row>
-    <row r="393" spans="1:1">
-      <c r="A393" s="34"/>
-    </row>
-    <row r="394" spans="1:1">
-      <c r="A394" s="34"/>
-    </row>
-    <row r="395" spans="1:1">
-      <c r="A395" s="34"/>
-    </row>
-    <row r="396" spans="1:1">
-      <c r="A396" s="34"/>
-    </row>
-    <row r="397" spans="1:1">
-      <c r="A397" s="34"/>
-    </row>
-    <row r="398" spans="1:1">
-      <c r="A398" s="34"/>
-    </row>
-    <row r="399" spans="1:1">
-      <c r="A399" s="34"/>
-    </row>
-    <row r="400" spans="1:1">
-      <c r="A400" s="34"/>
-    </row>
-    <row r="401" spans="1:1">
-      <c r="A401" s="34"/>
-    </row>
-    <row r="402" spans="1:1">
-      <c r="A402" s="34"/>
-    </row>
-    <row r="403" spans="1:1">
-      <c r="A403" s="34"/>
-    </row>
-    <row r="404" spans="1:1">
-      <c r="A404" s="34"/>
-    </row>
-    <row r="405" spans="1:1">
-      <c r="A405" s="34"/>
-    </row>
-    <row r="406" spans="1:1">
-      <c r="A406" s="34"/>
-    </row>
-    <row r="407" spans="1:1">
-      <c r="A407" s="34"/>
-    </row>
-    <row r="408" spans="1:1">
-      <c r="A408" s="34"/>
-    </row>
-    <row r="409" spans="1:1">
-      <c r="A409" s="34"/>
-    </row>
-    <row r="410" spans="1:1">
-      <c r="A410" s="34"/>
-    </row>
-    <row r="411" spans="1:1">
-      <c r="A411" s="34"/>
-    </row>
-    <row r="412" spans="1:1">
-      <c r="A412" s="34"/>
-    </row>
-    <row r="413" spans="1:1">
-      <c r="A413" s="34"/>
-    </row>
-    <row r="414" spans="1:1">
-      <c r="A414" s="34"/>
-    </row>
-    <row r="415" spans="1:1">
-      <c r="A415" s="34"/>
-    </row>
-    <row r="416" spans="1:1">
-      <c r="A416" s="34"/>
-    </row>
-    <row r="417" spans="1:1">
-      <c r="A417" s="34"/>
-    </row>
-    <row r="418" spans="1:1">
-      <c r="A418" s="34"/>
-    </row>
-    <row r="419" spans="1:1">
-      <c r="A419" s="34"/>
-    </row>
-    <row r="420" spans="1:1">
-      <c r="A420" s="34"/>
-    </row>
-    <row r="421" spans="1:1">
-      <c r="A421" s="34"/>
-    </row>
-    <row r="422" spans="1:1">
-      <c r="A422" s="34"/>
-    </row>
-    <row r="423" spans="1:1">
-      <c r="A423" s="34"/>
-    </row>
-    <row r="424" spans="1:1">
-      <c r="A424" s="34"/>
-    </row>
-    <row r="425" spans="1:1">
-      <c r="A425" s="34"/>
-    </row>
-    <row r="426" spans="1:1">
-      <c r="A426" s="34"/>
-    </row>
-    <row r="427" spans="1:1">
-      <c r="A427" s="34"/>
-    </row>
-    <row r="428" spans="1:1">
-      <c r="A428" s="34"/>
-    </row>
-    <row r="429" spans="1:1">
-      <c r="A429" s="34"/>
-    </row>
-    <row r="430" spans="1:1">
-      <c r="A430" s="34"/>
-    </row>
-    <row r="431" spans="1:1">
-      <c r="A431" s="34"/>
-    </row>
-    <row r="432" spans="1:1">
-      <c r="A432" s="34"/>
-    </row>
-    <row r="433" spans="1:1">
-      <c r="A433" s="34"/>
-    </row>
-    <row r="434" spans="1:1">
-      <c r="A434" s="34"/>
-    </row>
-    <row r="435" spans="1:1">
-      <c r="A435" s="34"/>
-    </row>
-    <row r="436" spans="1:1">
-      <c r="A436" s="34"/>
-    </row>
-    <row r="437" spans="1:1">
-      <c r="A437" s="34"/>
-    </row>
-    <row r="438" spans="1:1">
-      <c r="A438" s="34"/>
-    </row>
-    <row r="439" spans="1:1">
-      <c r="A439" s="34"/>
-    </row>
-    <row r="440" spans="1:1">
-      <c r="A440" s="34"/>
-    </row>
-    <row r="441" spans="1:1">
-      <c r="A441" s="34"/>
-    </row>
-    <row r="442" spans="1:1">
-      <c r="A442" s="34"/>
-    </row>
-    <row r="443" spans="1:1">
-      <c r="A443" s="34"/>
-    </row>
-    <row r="444" spans="1:1">
-      <c r="A444" s="34"/>
-    </row>
-    <row r="445" spans="1:1">
-      <c r="A445" s="34"/>
-    </row>
-    <row r="446" spans="1:1">
-      <c r="A446" s="34"/>
-    </row>
-    <row r="447" spans="1:1">
-      <c r="A447" s="34"/>
-    </row>
-    <row r="448" spans="1:1">
-      <c r="A448" s="34"/>
-    </row>
-    <row r="449" spans="1:1">
-      <c r="A449" s="34"/>
-    </row>
-    <row r="450" spans="1:1">
-      <c r="A450" s="34"/>
-    </row>
-    <row r="451" spans="1:1">
-      <c r="A451" s="34"/>
-    </row>
-    <row r="452" spans="1:1">
-      <c r="A452" s="34"/>
-    </row>
-    <row r="453" spans="1:1">
-      <c r="A453" s="34"/>
-    </row>
-    <row r="454" spans="1:1">
-      <c r="A454" s="34"/>
-    </row>
-    <row r="455" spans="1:1">
-      <c r="A455" s="34"/>
-    </row>
-    <row r="456" spans="1:1">
-      <c r="A456" s="34"/>
-    </row>
-    <row r="457" spans="1:1">
-      <c r="A457" s="34"/>
-    </row>
-    <row r="458" spans="1:1">
-      <c r="A458" s="34"/>
-    </row>
-    <row r="459" spans="1:1">
-      <c r="A459" s="34"/>
-    </row>
-    <row r="460" spans="1:1">
-      <c r="A460" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9772,713 +7545,61 @@
     <mergeCell ref="S2:X2"/>
   </mergeCells>
   <phoneticPr fontId="34"/>
-  <conditionalFormatting sqref="A192:A211">
-    <cfRule type="expression" dxfId="214" priority="1332" stopIfTrue="1">
-      <formula>OR($B173="├─",$B173="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A193:A194 A196 A202">
-    <cfRule type="expression" dxfId="213" priority="1224" stopIfTrue="1">
-      <formula>OR($B174="├─",$B174="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="212" priority="1225" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="211" priority="1226" stopIfTrue="1">
-      <formula>OR($B174="├─",$B174="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="210" priority="1227" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="209" priority="1228" stopIfTrue="1">
-      <formula>OR($B174="├─",$B174="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="208" priority="1229" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="207" priority="1230" stopIfTrue="1">
-      <formula>OR($B174="├─",$B174="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="206" priority="1231" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="205" priority="1232" stopIfTrue="1">
-      <formula>OR($B174="├─",$B174="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="204" priority="1233" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="203" priority="1234" stopIfTrue="1">
-      <formula>OR($B174="├─",$B174="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="202" priority="1235" stopIfTrue="1">
+  <conditionalFormatting sqref="A191:A194">
+    <cfRule type="expression" dxfId="12" priority="1343" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A193:A194 A196:A197 A199:A206">
-    <cfRule type="expression" dxfId="201" priority="1236" stopIfTrue="1">
-      <formula>OR($B174="├─",$B174="└─")</formula>
+  <conditionalFormatting sqref="Y68:AK68">
+    <cfRule type="expression" dxfId="11" priority="881" stopIfTrue="1">
+      <formula>OR($B68="├─",$B68="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="200" priority="1237" stopIfTrue="1">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:R1 T1:X1 A1:A3 S1:S3 B3:R3 T3:X3 A4:X100 A101:AN101 A102:X150 A151:R151 A152:X160 A161:R161 A162:X190">
+    <cfRule type="expression" dxfId="10" priority="801" stopIfTrue="1">
+      <formula>OR($B1="├─",$B1="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="802" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A197 A199:A206">
-    <cfRule type="expression" dxfId="199" priority="1343" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A197 A205:A206">
-    <cfRule type="expression" dxfId="198" priority="1333" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="197" priority="1334" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="196" priority="1335" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="195" priority="1336" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="194" priority="1337" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="193" priority="1338" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="192" priority="1339" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="191" priority="1340" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="190" priority="1341" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="189" priority="1342" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A197">
-    <cfRule type="expression" dxfId="188" priority="1344" stopIfTrue="1">
-      <formula>OR($B178="├─",$B178="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="187" priority="1345" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A201">
-    <cfRule type="expression" dxfId="186" priority="1392" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="185" priority="1393" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="184" priority="1394" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="183" priority="1395" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="182" priority="1396" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="181" priority="1397" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="180" priority="1398" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="179" priority="1399" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="178" priority="1400" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="177" priority="1401" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="176" priority="1402" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="175" priority="1403" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="174" priority="1404" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="173" priority="1405" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="172" priority="1406" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="171" priority="1407" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="170" priority="1408" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="169" priority="1409" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="168" priority="1410" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="167" priority="1411" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A201:A202">
-    <cfRule type="expression" dxfId="166" priority="1432" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="165" priority="1433" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="164" priority="1434" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="163" priority="1435" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="162" priority="1436" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="161" priority="1437" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A201:A203">
-    <cfRule type="expression" dxfId="160" priority="1438" stopIfTrue="1">
-      <formula>OR($B182="├─",$B182="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="159" priority="1439" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A203">
-    <cfRule type="expression" dxfId="158" priority="1502" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="157" priority="1503" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="156" priority="1504" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="155" priority="1505" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="154" priority="1506" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="153" priority="1507" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="152" priority="1508" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="151" priority="1509" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="150" priority="1510" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="149" priority="1511" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="148" priority="1512" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="147" priority="1513" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="146" priority="1514" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="145" priority="1515" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="144" priority="1516" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="143" priority="1517" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="142" priority="1518" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="141" priority="1519" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="140" priority="1520" stopIfTrue="1">
-      <formula>OR($B184="├─",$B184="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="139" priority="1521" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A205">
-    <cfRule type="expression" dxfId="138" priority="1566" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="137" priority="1567" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="136" priority="1568" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="135" priority="1569" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="134" priority="1570" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="133" priority="1571" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="132" priority="1572" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="131" priority="1573" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="130" priority="1574" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="129" priority="1575" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="128" priority="1576" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="127" priority="1577" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="126" priority="1578" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="125" priority="1579" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="124" priority="1580" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="123" priority="1581" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="122" priority="1582" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="121" priority="1583" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="120" priority="1584" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="119" priority="1585" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="118" priority="1586" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="117" priority="1587" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A205:A206">
-    <cfRule type="expression" dxfId="116" priority="1330" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="115" priority="1331" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="114" priority="1588" stopIfTrue="1">
-      <formula>OR($B186="├─",$B186="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="113" priority="1589" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A206">
-    <cfRule type="expression" dxfId="112" priority="1650" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="111" priority="1651" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="110" priority="1652" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="109" priority="1653" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="108" priority="1654" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="107" priority="1655" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="106" priority="1656" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="105" priority="1657" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="104" priority="1658" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="103" priority="1659" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="1660" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="1661" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="100" priority="1662" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="99" priority="1663" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="98" priority="1664" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="97" priority="1665" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="1666" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="95" priority="1667" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="94" priority="1668" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="1669" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="92" priority="1670" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="1671" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="90" priority="1672" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="1673" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="1674" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="1675" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="1676" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="1677" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="1678" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="1679" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="1680" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="1681" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="1682" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="1683" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="1684" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="1685" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="1686" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="1687" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="74" priority="1688" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="1689" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A206:A207">
-    <cfRule type="expression" dxfId="72" priority="1732" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="1733" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="70" priority="1734" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="1735" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="1736" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="1737" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="1738" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="1739" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="1740" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="1741" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="1742" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="1743" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="1744" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="1745" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="1746" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="1747" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="1748" stopIfTrue="1">
-      <formula>OR($B187="├─",$B187="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="55" priority="1749" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A207">
-    <cfRule type="expression" dxfId="54" priority="1768" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="1769" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="1770" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="1771" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="1772" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="1773" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="1774" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="47" priority="1775" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="1776" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="1777" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="1778" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="1779" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="1780" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="41" priority="1781" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="1782" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="1783" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="1784" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="1785" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="1786" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="1787" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="1788" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="1789" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="1790" stopIfTrue="1">
-      <formula>OR($B188="├─",$B188="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="1791" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A209 B203:E451">
-    <cfRule type="expression" dxfId="30" priority="1365" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A209">
-    <cfRule type="expression" dxfId="29" priority="1363" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="1364" stopIfTrue="1">
-      <formula>OR($B190="├─",$B190="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A212:A460">
-    <cfRule type="expression" dxfId="27" priority="2069" stopIfTrue="1">
-      <formula>OR($B203="├─",$B203="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A213:A214 A216:A217 A222:A235">
-    <cfRule type="expression" dxfId="26" priority="1919" stopIfTrue="1">
-      <formula>OR($B204="├─",$B204="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="1920" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A231:A233">
-    <cfRule type="expression" dxfId="24" priority="2045" stopIfTrue="1">
-      <formula>OR($B222="├─",$B222="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="2046" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="2047" stopIfTrue="1">
-      <formula>OR($B222="├─",$B222="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="2048" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B213:C226 Y68:AK68 B204:C205 B207:C208">
-    <cfRule type="expression" dxfId="20" priority="881" stopIfTrue="1">
-      <formula>OR($B68="├─",$B68="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B222:C224">
-    <cfRule type="expression" dxfId="19" priority="819" stopIfTrue="1">
-      <formula>OR($B222="├─",$B222="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="820" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="823" stopIfTrue="1">
-      <formula>OR($B222="├─",$B222="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="824" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B192:E192 A192:A460">
-    <cfRule type="expression" dxfId="15" priority="890" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B203:E451 B192:E192">
-    <cfRule type="expression" dxfId="14" priority="889" stopIfTrue="1">
-      <formula>OR($B192="├─",$B192="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:R1 T1:X1 A1:A3 S1:S3 B3:R3 T3:X3 A4:X100 A101:AN101 A102:X150 A151:R151 A161:R161 A162:X191 A152:X160">
-    <cfRule type="expression" dxfId="13" priority="801" stopIfTrue="1">
-      <formula>OR($B1="├─",$B1="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="802" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F207:F438">
-    <cfRule type="expression" dxfId="11" priority="938" stopIfTrue="1">
-      <formula>OR($B220="├─",$B220="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="939" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G436:X65630 F439:F65633 B452:E65646">
-    <cfRule type="expression" dxfId="9" priority="893" stopIfTrue="1">
-      <formula>OR(B436="│",B436="├─",B436="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K192:X206 G207:X435">
-    <cfRule type="expression" dxfId="8" priority="375" stopIfTrue="1">
-      <formula>OR($B208="├─",$B208="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="376" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
+  <conditionalFormatting sqref="G191:X65364 F191:F65367 B191:E65380">
+    <cfRule type="expression" dxfId="8" priority="893" stopIfTrue="1">
+      <formula>OR(B191="│",B191="├─",B191="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S161:X161">
-    <cfRule type="expression" dxfId="6" priority="2080" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="2080" stopIfTrue="1">
       <formula>OR($B151="├─",$B151="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2081" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="2081" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y98:Z98">
-    <cfRule type="expression" dxfId="4" priority="355" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="355" stopIfTrue="1">
       <formula>OR($B144="├─",$B144="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="356" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="356" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y68:AK68 B204:C205 B207:C208 B213:C226">
-    <cfRule type="expression" dxfId="2" priority="882" stopIfTrue="1">
+  <conditionalFormatting sqref="Y68:AK68">
+    <cfRule type="expression" dxfId="3" priority="882" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA98:AK98">
-    <cfRule type="expression" dxfId="1" priority="2076" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2076" stopIfTrue="1">
       <formula>OR(#REF!="├─",#REF!="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2077" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="2077" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A191:A194">
+    <cfRule type="expression" dxfId="0" priority="2082" stopIfTrue="1">
+      <formula>OR(#REF!="├─",#REF!="└─")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11200,10 +8321,10 @@
       </c>
     </row>
     <row r="68" spans="1:2" ht="234" customHeight="1">
-      <c r="A68" s="48" t="s">
+      <c r="A68" s="59" t="s">
         <v>448</v>
       </c>
-      <c r="B68" s="48"/>
+      <c r="B68" s="59"/>
     </row>
     <row r="69" spans="1:2" ht="164.25" customHeight="1">
       <c r="A69" s="32" t="s">

--- a/実装メモ.xlsx
+++ b/実装メモ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\docker_cms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEACC6B-2BDC-42E9-93D6-57334623DD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12BA6BE9-3F91-4CC0-8F98-5D08709337DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8AD811FF-9DD2-48D3-AAE3-50C231EEB6F8}"/>
   </bookViews>
   <sheets>
     <sheet name="構成図" sheetId="9" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="712">
   <si>
     <t>Route::get('/survey/{id}', [SurveyController::class, 'show']);</t>
   </si>
@@ -2461,30 +2461,6 @@
     <phoneticPr fontId="34"/>
   </si>
   <si>
-    <t>Category.php</t>
-  </si>
-  <si>
-    <t>Menu.php</t>
-  </si>
-  <si>
-    <t>MenuItem.php</t>
-  </si>
-  <si>
-    <t>News.php</t>
-  </si>
-  <si>
-    <t>Page.php</t>
-  </si>
-  <si>
-    <t>Setting.php</t>
-  </si>
-  <si>
-    <t>Tag.php</t>
-  </si>
-  <si>
-    <t>User.php</t>
-  </si>
-  <si>
     <t>Providers</t>
     <phoneticPr fontId="34"/>
   </si>
@@ -3198,6 +3174,36 @@
       <t>ヒツヨウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>AdminPanelProvider.php</t>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>管理画面のデザインの簡易変更</t>
+    <rPh sb="0" eb="2">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>詳細：</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="34"/>
+  </si>
+  <si>
+    <t>https://www.google.com/search?q=filment+laravel+%E7%AE%A1%E7%90%86%E7%94%BB%E9%9D%A2%E3%81%AE%E3%83%87%E3%82%B6%E3%82%A4%E3%83%B3%E3%82%92%E8%87%AA%E7%94%B1%E3%81%AB%E5%A4%89%E3%81%88%E3%82%8B&amp;rlz=1C1VDKB_enJP1144JP1144&amp;oq=filment+laravel+%E7%AE%A1%E7%90%86%E7%94%BB%E9%9D%A2%E3%81%AE%E3%83%87%E3%82%B6%E3%82%A4%E3%83%B3%E3%82%92%E8%87%AA%E7%94%B1%E3%81%AB%E5%A4%89%E3%81%88%E3%82%8B&amp;gs_lcrp=EgZjaHJvbWUyBggAEEUYOTIJCAEQIRgKGKAB0gEJMTQ4MzRqMGo3qAIAsAIA&amp;sourceid=chrome&amp;ie=UTF-8</t>
   </si>
 </sst>
 </file>
@@ -3835,7 +3841,14 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{F19A6957-2B34-4EDC-A43E-1512F220B8B2}"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3861,6 +3874,13 @@
       <fill>
         <patternFill>
           <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="43"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4472,7 +4492,7 @@
         <v>475</v>
       </c>
       <c r="S6" s="35" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -4508,7 +4528,7 @@
         <v>527</v>
       </c>
       <c r="S8" s="35" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -5120,7 +5140,7 @@
         <v>544</v>
       </c>
       <c r="Y37" s="35" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
     </row>
     <row r="38" spans="1:33">
@@ -5165,10 +5185,10 @@
         <v>546</v>
       </c>
       <c r="Y39" s="35" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="AG39" s="35" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
     </row>
     <row r="40" spans="1:33">
@@ -5186,7 +5206,7 @@
         <v>484</v>
       </c>
       <c r="AG40" s="35" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
     </row>
     <row r="41" spans="1:33">
@@ -5420,7 +5440,7 @@
         <v>342</v>
       </c>
       <c r="S52" s="35" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
     </row>
     <row r="53" spans="1:32">
@@ -5438,10 +5458,10 @@
         <v>553</v>
       </c>
       <c r="AC53" s="35" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="AF53" s="35" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
     </row>
     <row r="54" spans="1:32">
@@ -5558,7 +5578,7 @@
         <v>472</v>
       </c>
       <c r="D61" s="35" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="F61" s="40"/>
     </row>
@@ -5574,10 +5594,10 @@
         <v>476</v>
       </c>
       <c r="E62" s="39" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="S62" s="35" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
     </row>
     <row r="63" spans="1:32">
@@ -5653,7 +5673,7 @@
         <v>565</v>
       </c>
       <c r="S67" s="35" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
     </row>
     <row r="68" spans="1:19">
@@ -5674,7 +5694,7 @@
         <v>472</v>
       </c>
       <c r="D69" s="35" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="70" spans="1:19">
@@ -5689,7 +5709,7 @@
         <v>567</v>
       </c>
       <c r="E70" s="35" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
     </row>
     <row r="71" spans="1:19">
@@ -5704,7 +5724,7 @@
         <v>567</v>
       </c>
       <c r="E71" s="35" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -5719,7 +5739,7 @@
         <v>567</v>
       </c>
       <c r="E72" s="35" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -5734,7 +5754,7 @@
         <v>567</v>
       </c>
       <c r="E73" s="35" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
     </row>
     <row r="74" spans="1:19">
@@ -5749,7 +5769,7 @@
         <v>567</v>
       </c>
       <c r="E74" s="35" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -5764,7 +5784,7 @@
         <v>567</v>
       </c>
       <c r="E75" s="35" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -5779,7 +5799,7 @@
         <v>567</v>
       </c>
       <c r="E76" s="35" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -5794,7 +5814,7 @@
         <v>567</v>
       </c>
       <c r="E77" s="39" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
     </row>
     <row r="78" spans="1:19">
@@ -5809,10 +5829,10 @@
         <v>567</v>
       </c>
       <c r="E78" s="39" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="S78" s="35" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
     </row>
     <row r="79" spans="1:19">
@@ -5827,7 +5847,7 @@
         <v>567</v>
       </c>
       <c r="E79" s="39" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="80" spans="1:19">
@@ -5842,10 +5862,10 @@
         <v>567</v>
       </c>
       <c r="E80" s="39" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30">
       <c r="A81" s="34"/>
       <c r="B81" s="35" t="s">
         <v>474</v>
@@ -5857,10 +5877,10 @@
         <v>567</v>
       </c>
       <c r="E81" s="35" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30">
       <c r="A82" s="34"/>
       <c r="B82" s="35" t="s">
         <v>474</v>
@@ -5872,10 +5892,10 @@
         <v>476</v>
       </c>
       <c r="E82" s="35" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30">
       <c r="A83" s="34"/>
       <c r="B83" s="35" t="s">
         <v>474</v>
@@ -5884,10 +5904,10 @@
         <v>476</v>
       </c>
       <c r="D83" s="35" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="84" spans="1:30">
       <c r="A84" s="34"/>
       <c r="B84" s="35" t="s">
         <v>474</v>
@@ -5902,160 +5922,98 @@
         <v>568</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:30">
       <c r="A85" s="34"/>
       <c r="B85" s="35" t="s">
         <v>474</v>
       </c>
       <c r="E85" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F85" s="35" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+        <v>476</v>
+      </c>
+      <c r="F85" s="39" t="s">
+        <v>708</v>
+      </c>
+      <c r="S85" s="39" t="s">
+        <v>709</v>
+      </c>
+      <c r="Z85" s="35" t="s">
+        <v>710</v>
+      </c>
+      <c r="AB85" s="35" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30">
       <c r="A86" s="34"/>
       <c r="B86" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="E86" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F86" s="35" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+    </row>
+    <row r="87" spans="1:30">
       <c r="A87" s="34"/>
       <c r="B87" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="E87" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F87" s="35" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+    </row>
+    <row r="88" spans="1:30">
       <c r="A88" s="34"/>
       <c r="B88" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="E88" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F88" s="35" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+    </row>
+    <row r="89" spans="1:30">
       <c r="A89" s="34"/>
       <c r="B89" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="E89" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F89" s="35" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+    </row>
+    <row r="90" spans="1:30">
       <c r="A90" s="34"/>
       <c r="B90" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="E90" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F90" s="35" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+    </row>
+    <row r="91" spans="1:30">
       <c r="A91" s="34"/>
       <c r="B91" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="E91" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F91" s="35" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+    </row>
+    <row r="92" spans="1:30">
       <c r="A92" s="34"/>
       <c r="B92" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="E92" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F92" s="35" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+    </row>
+    <row r="93" spans="1:30">
       <c r="A93" s="34"/>
       <c r="B93" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="E93" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F93" s="35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+      <c r="AD93"/>
+    </row>
+    <row r="94" spans="1:30">
       <c r="A94" s="34"/>
       <c r="B94" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="E94" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F94" s="35" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
+    </row>
+    <row r="95" spans="1:30">
       <c r="A95" s="34"/>
       <c r="B95" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="E95" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F95" s="35" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+    </row>
+    <row r="96" spans="1:30">
       <c r="A96" s="34"/>
       <c r="B96" s="35" t="s">
         <v>474</v>
-      </c>
-      <c r="E96" s="35" t="s">
-        <v>567</v>
-      </c>
-      <c r="F96" s="35" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="97" spans="1:19">
       <c r="A97" s="34"/>
       <c r="B97" s="35" t="s">
         <v>474</v>
-      </c>
-      <c r="E97" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="F97" s="35" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="98" spans="1:19">
@@ -6064,7 +6022,7 @@
         <v>472</v>
       </c>
       <c r="C98" s="35" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
     </row>
     <row r="99" spans="1:19">
@@ -6076,7 +6034,7 @@
         <v>476</v>
       </c>
       <c r="D99" s="35" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
     </row>
     <row r="100" spans="1:19">
@@ -6085,7 +6043,7 @@
         <v>472</v>
       </c>
       <c r="C100" s="35" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
     </row>
     <row r="101" spans="1:19">
@@ -6094,7 +6052,7 @@
         <v>472</v>
       </c>
       <c r="C101" s="35" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="Q101" s="34"/>
     </row>
@@ -6107,7 +6065,7 @@
         <v>567</v>
       </c>
       <c r="D102" s="35" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -6119,7 +6077,7 @@
         <v>567</v>
       </c>
       <c r="D103" s="35" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="S103" s="35" t="s">
         <v>562</v>
@@ -6134,7 +6092,7 @@
         <v>476</v>
       </c>
       <c r="D104" s="35" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="S104" s="35" t="s">
         <v>563</v>
@@ -6146,7 +6104,7 @@
         <v>518</v>
       </c>
       <c r="C105" s="35" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6158,10 +6116,10 @@
         <v>476</v>
       </c>
       <c r="D106" s="35" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="S106" s="35" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
     </row>
     <row r="107" spans="1:19">
@@ -6575,7 +6533,7 @@
         <v>472</v>
       </c>
       <c r="C133" s="35" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -6602,7 +6560,7 @@
         <v>476</v>
       </c>
       <c r="E135" s="35" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -6629,7 +6587,7 @@
         <v>472</v>
       </c>
       <c r="E137" s="35" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -6644,7 +6602,7 @@
         <v>476</v>
       </c>
       <c r="E138" s="35" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -6710,7 +6668,7 @@
         <v>476</v>
       </c>
       <c r="G142" s="35" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -6803,16 +6761,16 @@
         <v>342</v>
       </c>
       <c r="S146" s="35" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="AA146" s="35" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="AC146" s="35" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="AE146" s="35" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
     </row>
     <row r="147" spans="1:53">
@@ -6845,10 +6803,10 @@
         <v>472</v>
       </c>
       <c r="F148" s="39" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="S148" s="35" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
     </row>
     <row r="149" spans="1:53">
@@ -6866,7 +6824,7 @@
         <v>476</v>
       </c>
       <c r="F149" s="35" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
     </row>
     <row r="150" spans="1:53">
@@ -6878,7 +6836,7 @@
         <v>472</v>
       </c>
       <c r="E150" s="35" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
     </row>
     <row r="151" spans="1:53">
@@ -6893,10 +6851,10 @@
         <v>476</v>
       </c>
       <c r="F151" s="39" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="S151" s="35" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
     </row>
     <row r="152" spans="1:53">
@@ -6947,7 +6905,7 @@
         <v>472</v>
       </c>
       <c r="F155" s="35" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
     </row>
     <row r="156" spans="1:53">
@@ -6965,7 +6923,7 @@
         <v>476</v>
       </c>
       <c r="F156" s="35" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
     </row>
     <row r="157" spans="1:53" ht="19.5" thickBot="1">
@@ -6998,7 +6956,7 @@
         <v>476</v>
       </c>
       <c r="F158" s="35" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="AK158" s="43"/>
       <c r="AL158" s="37"/>
@@ -7030,11 +6988,11 @@
         <v>472</v>
       </c>
       <c r="E159" s="35" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="AK159" s="45"/>
       <c r="AL159" s="46" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="BA159" s="47"/>
     </row>
@@ -7053,17 +7011,17 @@
         <v>476</v>
       </c>
       <c r="F160" s="35" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="S160" s="35" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="Z160" s="35" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="AK160" s="45"/>
       <c r="AL160" s="50" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="AM160" s="51"/>
       <c r="AN160" s="51"/>
@@ -7093,14 +7051,14 @@
         <v>472</v>
       </c>
       <c r="E161" s="39" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="S161" s="35" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="AK161" s="45"/>
       <c r="AL161" s="50" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="AM161" s="51"/>
       <c r="AN161" s="51"/>
@@ -7130,11 +7088,11 @@
         <v>472</v>
       </c>
       <c r="E162" s="35" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="AK162" s="48"/>
       <c r="AL162" s="52" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="AM162" s="53"/>
       <c r="AN162" s="53"/>
@@ -7164,7 +7122,7 @@
         <v>476</v>
       </c>
       <c r="E163" s="35" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="164" spans="1:53">
@@ -7197,7 +7155,7 @@
         <v>472</v>
       </c>
       <c r="D167" s="35" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
     </row>
     <row r="168" spans="1:53">
@@ -7209,7 +7167,7 @@
         <v>476</v>
       </c>
       <c r="D168" s="35" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
     </row>
     <row r="169" spans="1:53">
@@ -7546,60 +7504,64 @@
   </mergeCells>
   <phoneticPr fontId="34"/>
   <conditionalFormatting sqref="A191:A194">
-    <cfRule type="expression" dxfId="12" priority="1343" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="1343" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2082" stopIfTrue="1">
+      <formula>OR(#REF!="├─",#REF!="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:R1 T1:X1 A1:A3 S1:S3 B3:R3 T3:X3 A101:AN101 A102:X150 A151:R151 A152:X160 A161:R161 A162:X190 A4:X84 G85:X85 A85:E85 A86:X100">
+    <cfRule type="expression" dxfId="12" priority="801" stopIfTrue="1">
+      <formula>OR($B1="├─",$B1="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="802" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G191:X65364 F191:F65367 B191:E65380">
+    <cfRule type="expression" dxfId="10" priority="893" stopIfTrue="1">
+      <formula>OR(B191="│",B191="├─",B191="└─")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S161:X161">
+    <cfRule type="expression" dxfId="9" priority="2080" stopIfTrue="1">
+      <formula>OR($B151="├─",$B151="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="2081" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y98:Z98">
+    <cfRule type="expression" dxfId="7" priority="355" stopIfTrue="1">
+      <formula>OR($B144="├─",$B144="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="356" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y68:AK68">
-    <cfRule type="expression" dxfId="11" priority="881" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="881" stopIfTrue="1">
       <formula>OR($B68="├─",$B68="└─")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:R1 T1:X1 A1:A3 S1:S3 B3:R3 T3:X3 A4:X100 A101:AN101 A102:X150 A151:R151 A152:X160 A161:R161 A162:X190">
-    <cfRule type="expression" dxfId="10" priority="801" stopIfTrue="1">
-      <formula>OR($B1="├─",$B1="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="802" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G191:X65364 F191:F65367 B191:E65380">
-    <cfRule type="expression" dxfId="8" priority="893" stopIfTrue="1">
-      <formula>OR(B191="│",B191="├─",B191="└─")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S161:X161">
-    <cfRule type="expression" dxfId="7" priority="2080" stopIfTrue="1">
-      <formula>OR($B151="├─",$B151="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2081" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y98:Z98">
-    <cfRule type="expression" dxfId="5" priority="355" stopIfTrue="1">
-      <formula>OR($B144="├─",$B144="└─")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="356" stopIfTrue="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y68:AK68">
-    <cfRule type="expression" dxfId="3" priority="882" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="882" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA98:AK98">
-    <cfRule type="expression" dxfId="2" priority="2076" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="2076" stopIfTrue="1">
       <formula>OR(#REF!="├─",#REF!="└─")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2077" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2077" stopIfTrue="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A191:A194">
-    <cfRule type="expression" dxfId="0" priority="2082" stopIfTrue="1">
-      <formula>OR(#REF!="├─",#REF!="└─")</formula>
+  <conditionalFormatting sqref="F85">
+    <cfRule type="expression" dxfId="1" priority="2085" stopIfTrue="1">
+      <formula>OR($B86="├─",$B86="└─")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2086" stopIfTrue="1">
+      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7633,12 +7595,12 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="10" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="25.5">
@@ -9079,17 +9041,17 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -9105,12 +9067,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -9120,7 +9082,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -9130,27 +9092,27 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -9165,7 +9127,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -9175,17 +9137,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -9215,7 +9177,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="21" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
@@ -9228,7 +9190,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="21" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="B2" s="35"/>
       <c r="C2" s="35"/>
@@ -9241,7 +9203,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B3" s="35"/>
       <c r="C3" s="35"/>
@@ -9254,7 +9216,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="35" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -9267,7 +9229,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="B5" s="35"/>
       <c r="C5" s="35"/>
@@ -9290,7 +9252,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="41" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="B7" s="35"/>
       <c r="C7" s="35"/>
@@ -9303,7 +9265,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="41" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B8" s="35"/>
       <c r="C8" s="35"/>
@@ -9326,7 +9288,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="B10" s="35"/>
       <c r="C10" s="35"/>
@@ -9349,7 +9311,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="B12" s="35"/>
       <c r="C12" s="35"/>
@@ -9362,7 +9324,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="35" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="B13" s="35"/>
       <c r="C13" s="35"/>
@@ -9408,7 +9370,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="C17" s="35"/>
       <c r="D17" s="35"/>
@@ -9432,7 +9394,7 @@
         <v>470</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="C19" s="35"/>
       <c r="D19" s="35"/>
@@ -9444,10 +9406,10 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="19" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="C20" s="35"/>
       <c r="D20" s="35"/>
@@ -9459,10 +9421,10 @@
     </row>
     <row r="21" spans="1:9" ht="37.5">
       <c r="A21" s="19" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C21" s="35"/>
       <c r="D21" s="35"/>
@@ -9474,74 +9436,74 @@
     </row>
     <row r="23" spans="1:9" ht="39.75">
       <c r="A23" s="1" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="18" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="19" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="19" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="19" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="39.75">
       <c r="A30" s="1" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="22.5">
       <c r="A32" s="4" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="22.5">
       <c r="A36" s="4" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="39.75">
       <c r="A47" s="1" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -9549,27 +9511,27 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="3" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="3" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="3" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="30">
       <c r="A57" s="5" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -9577,37 +9539,37 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="3" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="3" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="3" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="3" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="39.75">
       <c r="A68" s="1" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -9615,22 +9577,22 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="3" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="3" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="3" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="3" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -9646,37 +9608,37 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="42" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="42" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="42" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="42" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="42" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="42" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
     </row>
   </sheetData>
